--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5777,10 +5777,10 @@
         <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5580,10 +5580,10 @@
         <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.28</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5777,10 +5777,10 @@
         <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G31" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,139 +4544,139 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
         <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
         <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,139 +4741,139 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AT22" t="n">
         <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY22" t="n">
         <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI22" s="3" t="n">
         <v>46127.60416666666</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.28</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5580,10 +5580,10 @@
         <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5777,10 +5777,10 @@
         <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G31" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4343,143 +4343,143 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.6</v>
+        <v>7.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="R20" t="n">
-        <v>2.23</v>
+        <v>1.49</v>
       </c>
       <c r="S20" t="n">
-        <v>4.2</v>
+        <v>8.9</v>
       </c>
       <c r="T20" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="U20" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="V20" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="W20" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="X20" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="AA20" t="n">
         <v>1.03</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AG20" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AI20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.29</v>
+        <v>2.88</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="AO20" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AS20" t="n">
         <v>3.15</v>
       </c>
       <c r="AT20" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
         <v>2.33</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="AX20" t="n">
         <v>1.3</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>2.31</v>
+        <v>3.7</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.81</v>
+        <v>1.3</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BF20" t="n">
         <v>1.08</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH20" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="BI20" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4540,143 +4540,143 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BH21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,139 +4741,139 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
         <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
         <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
         <v>46127.60416666666</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4343,143 +4343,143 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>7.75</v>
+        <v>3.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="R20" t="n">
-        <v>1.49</v>
+        <v>2.23</v>
       </c>
       <c r="S20" t="n">
-        <v>8.9</v>
+        <v>4.2</v>
       </c>
       <c r="T20" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="U20" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="V20" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="X20" t="n">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z20" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA20" t="n">
         <v>1.03</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AG20" t="n">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AI20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.88</v>
+        <v>2.29</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="AO20" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AS20" t="n">
         <v>3.15</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="AU20" t="n">
         <v>2.33</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AX20" t="n">
         <v>1.3</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AZ20" t="n">
-        <v>3.7</v>
+        <v>2.31</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.3</v>
+        <v>1.81</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="BF20" t="n">
         <v>1.08</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="BH20" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="BI20" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4540,143 +4540,143 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BH21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,139 +4741,139 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AT22" t="n">
         <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY22" t="n">
         <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI22" s="3" t="n">
         <v>46127.60416666666</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G31" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4343,143 +4343,143 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BH20" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,139 +4544,139 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AT21" t="n">
         <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY21" t="n">
         <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4737,143 +4737,143 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>7.75</v>
+        <v>3.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="R22" t="n">
-        <v>1.49</v>
+        <v>2.23</v>
       </c>
       <c r="S22" t="n">
-        <v>8.9</v>
+        <v>4.2</v>
       </c>
       <c r="T22" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="U22" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="V22" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="W22" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="X22" t="n">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z22" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA22" t="n">
         <v>1.03</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AG22" t="n">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AI22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.88</v>
+        <v>2.29</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="AO22" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AS22" t="n">
         <v>3.15</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="AU22" t="n">
         <v>2.33</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AX22" t="n">
         <v>1.3</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AZ22" t="n">
-        <v>3.7</v>
+        <v>2.31</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.3</v>
+        <v>1.81</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BD22" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="BF22" t="n">
         <v>1.08</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="BH22" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="BI22" s="3" t="n">
         <v>46127.60416666666</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4540,143 +4540,143 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>7.75</v>
+        <v>3.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="R21" t="n">
-        <v>1.49</v>
+        <v>2.23</v>
       </c>
       <c r="S21" t="n">
-        <v>8.9</v>
+        <v>4.2</v>
       </c>
       <c r="T21" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="U21" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="V21" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="W21" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="X21" t="n">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA21" t="n">
         <v>1.03</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AG21" t="n">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AI21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.88</v>
+        <v>2.29</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AS21" t="n">
         <v>3.15</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="AU21" t="n">
         <v>2.33</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AX21" t="n">
         <v>1.3</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AZ21" t="n">
-        <v>3.7</v>
+        <v>2.31</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.3</v>
+        <v>1.81</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="BF21" t="n">
         <v>1.08</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="BH21" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4737,143 +4737,143 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.6</v>
+        <v>7.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="R22" t="n">
-        <v>2.23</v>
+        <v>1.49</v>
       </c>
       <c r="S22" t="n">
-        <v>4.2</v>
+        <v>8.9</v>
       </c>
       <c r="T22" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="U22" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="V22" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="W22" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="X22" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z22" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="AA22" t="n">
         <v>1.03</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AG22" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AI22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.29</v>
+        <v>2.88</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="AO22" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AS22" t="n">
         <v>3.15</v>
       </c>
       <c r="AT22" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
         <v>2.33</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="AX22" t="n">
         <v>1.3</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>2.31</v>
+        <v>3.7</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.81</v>
+        <v>1.3</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BD22" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BF22" t="n">
         <v>1.08</v>
       </c>
       <c r="BG22" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH22" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="BI22" s="3" t="n">
         <v>46127.60416666666</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4343,143 +4343,143 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BH20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BI20" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4540,143 +4540,143 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.6</v>
+        <v>7.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>2.23</v>
+        <v>1.49</v>
       </c>
       <c r="S21" t="n">
-        <v>4.2</v>
+        <v>8.9</v>
       </c>
       <c r="T21" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="U21" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="V21" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="W21" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="X21" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="AA21" t="n">
         <v>1.03</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AG21" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AI21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.29</v>
+        <v>2.88</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AS21" t="n">
         <v>3.15</v>
       </c>
       <c r="AT21" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
         <v>2.33</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="AX21" t="n">
         <v>1.3</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2.31</v>
+        <v>3.7</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.81</v>
+        <v>1.3</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BF21" t="n">
         <v>1.08</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH21" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,139 +4741,139 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
         <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
         <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
         <v>46127.60416666666</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5580,10 +5580,10 @@
         <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.28</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5777,10 +5777,10 @@
         <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4343,143 +4343,143 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BH20" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4540,143 +4540,143 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>7.75</v>
+        <v>3.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="R21" t="n">
-        <v>1.49</v>
+        <v>2.23</v>
       </c>
       <c r="S21" t="n">
-        <v>8.9</v>
+        <v>4.2</v>
       </c>
       <c r="T21" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="U21" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="V21" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="W21" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="X21" t="n">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA21" t="n">
         <v>1.03</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AG21" t="n">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AI21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.88</v>
+        <v>2.29</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AS21" t="n">
         <v>3.15</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="AU21" t="n">
         <v>2.33</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AX21" t="n">
         <v>1.3</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AZ21" t="n">
-        <v>3.7</v>
+        <v>2.31</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.3</v>
+        <v>1.81</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="BF21" t="n">
         <v>1.08</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="BH21" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,139 +4741,139 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AT22" t="n">
         <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY22" t="n">
         <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI22" s="3" t="n">
         <v>46127.60416666666</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.28</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5580,10 +5580,10 @@
         <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5777,10 +5777,10 @@
         <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G31" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>4.85</v>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>6.79</v>
       </c>
       <c r="S24" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5580,10 +5580,10 @@
         <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.28</v>
+        <v>5.13</v>
       </c>
       <c r="R27" t="n">
-        <v>4.73</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,16 +5771,16 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>4.98</v>
+        <v>1.94</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.84</v>
+        <v>3.71</v>
       </c>
       <c r="R18" t="n">
-        <v>1.55</v>
+        <v>3.82</v>
       </c>
       <c r="S18" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.94</v>
+        <v>4.98</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.71</v>
+        <v>4.84</v>
       </c>
       <c r="R19" t="n">
-        <v>3.82</v>
+        <v>1.55</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4343,143 +4343,143 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BH20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BI20" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4540,143 +4540,143 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BH21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.28</v>
+        <v>5.13</v>
       </c>
       <c r="R26" t="n">
-        <v>4.73</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,16 +5574,16 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.13</v>
+        <v>5.28</v>
       </c>
       <c r="R27" t="n">
-        <v>8.800000000000001</v>
+        <v>4.73</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,16 +5771,16 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6658,7 +6658,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P32" t="n">
@@ -6846,7 +6846,7 @@
         <v>0</v>
       </c>
       <c r="BI32" s="3" t="n">
-        <v>46127.83333333334</v>
+        <v>46127.875</v>
       </c>
     </row>
     <row r="33">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.94</v>
+        <v>4.98</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.71</v>
+        <v>4.84</v>
       </c>
       <c r="R18" t="n">
-        <v>3.82</v>
+        <v>1.55</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>4.98</v>
+        <v>1.94</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.84</v>
+        <v>3.71</v>
       </c>
       <c r="R19" t="n">
-        <v>1.55</v>
+        <v>3.82</v>
       </c>
       <c r="S19" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,139 +4544,139 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AT21" t="n">
         <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY21" t="n">
         <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,139 +4741,139 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
         <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
         <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
         <v>46127.60416666666</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.13</v>
+        <v>5.28</v>
       </c>
       <c r="R26" t="n">
-        <v>8.800000000000001</v>
+        <v>4.73</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,16 +5574,16 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.28</v>
+        <v>5.13</v>
       </c>
       <c r="R27" t="n">
-        <v>4.73</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,16 +5771,16 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4343,143 +4343,143 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.6</v>
+        <v>7.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="R20" t="n">
-        <v>2.23</v>
+        <v>1.49</v>
       </c>
       <c r="S20" t="n">
-        <v>4.2</v>
+        <v>8.9</v>
       </c>
       <c r="T20" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="U20" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="V20" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="W20" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="X20" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="AA20" t="n">
         <v>1.03</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AG20" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AI20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.29</v>
+        <v>2.88</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="AO20" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AS20" t="n">
         <v>3.15</v>
       </c>
       <c r="AT20" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
         <v>2.33</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="AX20" t="n">
         <v>1.3</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>2.31</v>
+        <v>3.7</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.81</v>
+        <v>1.3</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BF20" t="n">
         <v>1.08</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH20" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="BI20" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,139 +4544,139 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
         <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
         <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4737,143 +4737,143 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BH22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BI22" s="3" t="n">
         <v>46127.60416666666</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,139 +4347,139 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>7.75</v>
+        <v>4.5</v>
       </c>
       <c r="Q20" t="n">
         <v>3.4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.49</v>
+        <v>1.78</v>
       </c>
       <c r="S20" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
         <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
         <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4540,143 +4540,143 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BH21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4737,143 +4737,143 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.6</v>
+        <v>7.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="R22" t="n">
-        <v>2.23</v>
+        <v>1.49</v>
       </c>
       <c r="S22" t="n">
-        <v>4.2</v>
+        <v>8.9</v>
       </c>
       <c r="T22" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="U22" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="V22" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="W22" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="X22" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z22" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="AA22" t="n">
         <v>1.03</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AG22" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AI22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.29</v>
+        <v>2.88</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="AO22" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AS22" t="n">
         <v>3.15</v>
       </c>
       <c r="AT22" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
         <v>2.33</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="AX22" t="n">
         <v>1.3</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>2.31</v>
+        <v>3.7</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.81</v>
+        <v>1.3</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BD22" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BF22" t="n">
         <v>1.08</v>
       </c>
       <c r="BG22" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH22" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="BI22" s="3" t="n">
         <v>46127.60416666666</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2</v>
+      </c>
+      <c r="S24" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V24" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q24" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="R24" t="n">
-        <v>6.79</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>3</v>
+        <v>4.85</v>
       </c>
       <c r="R25" t="n">
-        <v>2</v>
+        <v>6.79</v>
       </c>
       <c r="S25" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>4.98</v>
+        <v>1.94</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.84</v>
+        <v>3.71</v>
       </c>
       <c r="R18" t="n">
-        <v>1.55</v>
+        <v>3.82</v>
       </c>
       <c r="S18" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.94</v>
+        <v>4.98</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.71</v>
+        <v>4.84</v>
       </c>
       <c r="R19" t="n">
-        <v>3.82</v>
+        <v>1.55</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4343,143 +4343,143 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="R20" t="n">
-        <v>1.78</v>
+        <v>2.23</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BH20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BI20" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4540,143 +4540,143 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>2.23</v>
+        <v>1.78</v>
       </c>
       <c r="S21" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BH21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>4.85</v>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>6.79</v>
       </c>
       <c r="S24" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V25" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q25" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="R25" t="n">
-        <v>6.79</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.28</v>
+        <v>5.13</v>
       </c>
       <c r="R26" t="n">
-        <v>4.73</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,16 +5574,16 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.13</v>
+        <v>5.28</v>
       </c>
       <c r="R27" t="n">
-        <v>8.800000000000001</v>
+        <v>4.73</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,16 +5771,16 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.94</v>
+        <v>4.98</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.71</v>
+        <v>4.84</v>
       </c>
       <c r="R18" t="n">
-        <v>3.82</v>
+        <v>1.55</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>4.98</v>
+        <v>1.94</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.84</v>
+        <v>3.71</v>
       </c>
       <c r="R19" t="n">
-        <v>1.55</v>
+        <v>3.82</v>
       </c>
       <c r="S19" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,139 +4544,139 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>4.5</v>
+        <v>7.75</v>
       </c>
       <c r="Q21" t="n">
         <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.78</v>
+        <v>1.49</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AT21" t="n">
         <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY21" t="n">
         <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,139 +4741,139 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>7.75</v>
+        <v>4.5</v>
       </c>
       <c r="Q22" t="n">
         <v>3.4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.49</v>
+        <v>1.78</v>
       </c>
       <c r="S22" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
         <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
         <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
         <v>46127.60416666666</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.13</v>
+        <v>5.28</v>
       </c>
       <c r="R26" t="n">
-        <v>8.800000000000001</v>
+        <v>4.73</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,16 +5574,16 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.28</v>
+        <v>5.13</v>
       </c>
       <c r="R27" t="n">
-        <v>4.73</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,16 +5771,16 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>4.98</v>
+        <v>1.94</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.84</v>
+        <v>3.71</v>
       </c>
       <c r="R18" t="n">
-        <v>1.55</v>
+        <v>3.82</v>
       </c>
       <c r="S18" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.94</v>
+        <v>4.98</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.71</v>
+        <v>4.84</v>
       </c>
       <c r="R19" t="n">
-        <v>3.82</v>
+        <v>1.55</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4343,143 +4343,143 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.6</v>
+        <v>7.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="R20" t="n">
-        <v>2.23</v>
+        <v>1.49</v>
       </c>
       <c r="S20" t="n">
-        <v>4.2</v>
+        <v>8.9</v>
       </c>
       <c r="T20" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="U20" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="V20" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="W20" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="X20" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="AA20" t="n">
         <v>1.03</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AG20" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AI20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.29</v>
+        <v>2.88</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="AO20" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AS20" t="n">
         <v>3.15</v>
       </c>
       <c r="AT20" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
         <v>2.33</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="AX20" t="n">
         <v>1.3</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>2.31</v>
+        <v>3.7</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.81</v>
+        <v>1.3</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BF20" t="n">
         <v>1.08</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH20" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="BI20" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4540,143 +4540,143 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>7.75</v>
+        <v>3.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="R21" t="n">
-        <v>1.49</v>
+        <v>2.23</v>
       </c>
       <c r="S21" t="n">
-        <v>8.9</v>
+        <v>4.2</v>
       </c>
       <c r="T21" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="U21" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="V21" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="W21" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="X21" t="n">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA21" t="n">
         <v>1.03</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AG21" t="n">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AI21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.88</v>
+        <v>2.29</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AS21" t="n">
         <v>3.15</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="AU21" t="n">
         <v>2.33</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AX21" t="n">
         <v>1.3</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AZ21" t="n">
-        <v>3.7</v>
+        <v>2.31</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.3</v>
+        <v>1.81</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="BF21" t="n">
         <v>1.08</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="BH21" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.28</v>
+        <v>5.13</v>
       </c>
       <c r="R26" t="n">
-        <v>4.73</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,16 +5574,16 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.13</v>
+        <v>5.28</v>
       </c>
       <c r="R27" t="n">
-        <v>8.800000000000001</v>
+        <v>4.73</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,16 +5771,16 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.94</v>
+        <v>4.98</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.71</v>
+        <v>4.84</v>
       </c>
       <c r="R18" t="n">
-        <v>3.82</v>
+        <v>1.55</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>4.98</v>
+        <v>1.94</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.84</v>
+        <v>3.71</v>
       </c>
       <c r="R19" t="n">
-        <v>1.55</v>
+        <v>3.82</v>
       </c>
       <c r="S19" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.13</v>
+        <v>5.28</v>
       </c>
       <c r="R26" t="n">
-        <v>8.800000000000001</v>
+        <v>4.73</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,16 +5574,16 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.28</v>
+        <v>5.13</v>
       </c>
       <c r="R27" t="n">
-        <v>4.73</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,16 +5771,16 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4343,143 +4343,143 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>7.75</v>
+        <v>3.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="R20" t="n">
-        <v>1.49</v>
+        <v>2.23</v>
       </c>
       <c r="S20" t="n">
-        <v>8.9</v>
+        <v>4.2</v>
       </c>
       <c r="T20" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="U20" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="V20" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="X20" t="n">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z20" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA20" t="n">
         <v>1.03</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AG20" t="n">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AI20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.88</v>
+        <v>2.29</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="AO20" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AS20" t="n">
         <v>3.15</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="AU20" t="n">
         <v>2.33</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AX20" t="n">
         <v>1.3</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AZ20" t="n">
-        <v>3.7</v>
+        <v>2.31</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.3</v>
+        <v>1.81</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="BF20" t="n">
         <v>1.08</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="BH20" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="BI20" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4540,143 +4540,143 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>2.23</v>
+        <v>1.78</v>
       </c>
       <c r="S21" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BH21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,139 +4741,139 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>4.5</v>
+        <v>7.75</v>
       </c>
       <c r="Q22" t="n">
         <v>3.4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.78</v>
+        <v>1.49</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AT22" t="n">
         <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY22" t="n">
         <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI22" s="3" t="n">
         <v>46127.60416666666</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.28</v>
+        <v>5.13</v>
       </c>
       <c r="R26" t="n">
-        <v>4.73</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,16 +5574,16 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.13</v>
+        <v>5.28</v>
       </c>
       <c r="R27" t="n">
-        <v>8.800000000000001</v>
+        <v>4.73</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,16 +5771,16 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,139 +4544,139 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>4.5</v>
+        <v>7.75</v>
       </c>
       <c r="Q21" t="n">
         <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.78</v>
+        <v>1.49</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AT21" t="n">
         <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY21" t="n">
         <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,139 +4741,139 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>7.75</v>
+        <v>4.5</v>
       </c>
       <c r="Q22" t="n">
         <v>3.4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.49</v>
+        <v>1.78</v>
       </c>
       <c r="S22" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
         <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
         <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
         <v>46127.60416666666</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2</v>
+      </c>
+      <c r="S24" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V24" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q24" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="R24" t="n">
-        <v>6.79</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>3</v>
+        <v>4.85</v>
       </c>
       <c r="R25" t="n">
-        <v>2</v>
+        <v>6.79</v>
       </c>
       <c r="S25" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4343,143 +4343,143 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.6</v>
+        <v>7.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="R20" t="n">
-        <v>2.23</v>
+        <v>1.49</v>
       </c>
       <c r="S20" t="n">
-        <v>4.2</v>
+        <v>8.9</v>
       </c>
       <c r="T20" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="U20" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="V20" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="W20" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="X20" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="AA20" t="n">
         <v>1.03</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AG20" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AI20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.29</v>
+        <v>2.88</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="AO20" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AS20" t="n">
         <v>3.15</v>
       </c>
       <c r="AT20" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
         <v>2.33</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="AX20" t="n">
         <v>1.3</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>2.31</v>
+        <v>3.7</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.81</v>
+        <v>1.3</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BF20" t="n">
         <v>1.08</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH20" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="BI20" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4540,143 +4540,143 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>7.75</v>
+        <v>3.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="R21" t="n">
-        <v>1.49</v>
+        <v>2.23</v>
       </c>
       <c r="S21" t="n">
-        <v>8.9</v>
+        <v>4.2</v>
       </c>
       <c r="T21" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="U21" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="V21" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="W21" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="X21" t="n">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA21" t="n">
         <v>1.03</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AG21" t="n">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AI21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.88</v>
+        <v>2.29</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AS21" t="n">
         <v>3.15</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="AU21" t="n">
         <v>2.33</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AX21" t="n">
         <v>1.3</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AZ21" t="n">
-        <v>3.7</v>
+        <v>2.31</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.3</v>
+        <v>1.81</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="BF21" t="n">
         <v>1.08</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="BH21" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,139 +4347,139 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>7.75</v>
+        <v>4.5</v>
       </c>
       <c r="Q20" t="n">
         <v>3.4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.49</v>
+        <v>1.78</v>
       </c>
       <c r="S20" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
         <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
         <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,139 +4741,139 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>4.5</v>
+        <v>7.75</v>
       </c>
       <c r="Q22" t="n">
         <v>3.4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.78</v>
+        <v>1.49</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AT22" t="n">
         <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY22" t="n">
         <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI22" s="3" t="n">
         <v>46127.60416666666</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.13</v>
+        <v>5.28</v>
       </c>
       <c r="R26" t="n">
-        <v>8.800000000000001</v>
+        <v>4.73</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,16 +5574,16 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.28</v>
+        <v>5.13</v>
       </c>
       <c r="R27" t="n">
-        <v>4.73</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,16 +5771,16 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>4.98</v>
+        <v>1.94</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.84</v>
+        <v>3.71</v>
       </c>
       <c r="R18" t="n">
-        <v>1.55</v>
+        <v>3.82</v>
       </c>
       <c r="S18" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.94</v>
+        <v>4.98</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.71</v>
+        <v>4.84</v>
       </c>
       <c r="R19" t="n">
-        <v>3.82</v>
+        <v>1.55</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4343,143 +4343,143 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="R20" t="n">
-        <v>1.78</v>
+        <v>2.23</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BH20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BI20" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4540,143 +4540,143 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.6</v>
+        <v>7.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>2.23</v>
+        <v>1.49</v>
       </c>
       <c r="S21" t="n">
-        <v>4.2</v>
+        <v>8.9</v>
       </c>
       <c r="T21" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="U21" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="V21" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="W21" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="X21" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="AA21" t="n">
         <v>1.03</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AG21" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AI21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.29</v>
+        <v>2.88</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AS21" t="n">
         <v>3.15</v>
       </c>
       <c r="AT21" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
         <v>2.33</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="AX21" t="n">
         <v>1.3</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2.31</v>
+        <v>3.7</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.81</v>
+        <v>1.3</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BF21" t="n">
         <v>1.08</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH21" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,139 +4741,139 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>7.75</v>
+        <v>4.5</v>
       </c>
       <c r="Q22" t="n">
         <v>3.4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.49</v>
+        <v>1.78</v>
       </c>
       <c r="S22" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
         <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
         <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
         <v>46127.60416666666</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>4.85</v>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>6.79</v>
       </c>
       <c r="S24" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V25" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q25" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="R25" t="n">
-        <v>6.79</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.94</v>
+        <v>4.98</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.71</v>
+        <v>4.84</v>
       </c>
       <c r="R18" t="n">
-        <v>3.82</v>
+        <v>1.55</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>4.98</v>
+        <v>1.94</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.84</v>
+        <v>3.71</v>
       </c>
       <c r="R19" t="n">
-        <v>1.55</v>
+        <v>3.82</v>
       </c>
       <c r="S19" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4343,143 +4343,143 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.6</v>
+        <v>7.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="R20" t="n">
-        <v>2.23</v>
+        <v>1.49</v>
       </c>
       <c r="S20" t="n">
-        <v>4.2</v>
+        <v>8.9</v>
       </c>
       <c r="T20" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="U20" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="V20" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="W20" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="X20" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="AA20" t="n">
         <v>1.03</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AG20" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AI20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.29</v>
+        <v>2.88</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="AO20" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AS20" t="n">
         <v>3.15</v>
       </c>
       <c r="AT20" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
         <v>2.33</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="AX20" t="n">
         <v>1.3</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>2.31</v>
+        <v>3.7</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.81</v>
+        <v>1.3</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BF20" t="n">
         <v>1.08</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH20" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="BI20" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4540,143 +4540,143 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>7.75</v>
+        <v>3.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="R21" t="n">
-        <v>1.49</v>
+        <v>2.23</v>
       </c>
       <c r="S21" t="n">
-        <v>8.9</v>
+        <v>4.2</v>
       </c>
       <c r="T21" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="U21" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="V21" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="W21" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="X21" t="n">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA21" t="n">
         <v>1.03</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AG21" t="n">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AI21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.88</v>
+        <v>2.29</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AS21" t="n">
         <v>3.15</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="AU21" t="n">
         <v>2.33</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AX21" t="n">
         <v>1.3</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AZ21" t="n">
-        <v>3.7</v>
+        <v>2.31</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.3</v>
+        <v>1.81</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="BF21" t="n">
         <v>1.08</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="BH21" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,139 +4347,139 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>7.75</v>
+        <v>4.5</v>
       </c>
       <c r="Q20" t="n">
         <v>3.4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.49</v>
+        <v>1.78</v>
       </c>
       <c r="S20" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
         <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
         <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4540,143 +4540,143 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.6</v>
+        <v>7.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>2.23</v>
+        <v>1.49</v>
       </c>
       <c r="S21" t="n">
-        <v>4.2</v>
+        <v>8.9</v>
       </c>
       <c r="T21" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="U21" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="V21" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="W21" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="X21" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="AA21" t="n">
         <v>1.03</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AG21" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AI21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.29</v>
+        <v>2.88</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AS21" t="n">
         <v>3.15</v>
       </c>
       <c r="AT21" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
         <v>2.33</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="AX21" t="n">
         <v>1.3</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2.31</v>
+        <v>3.7</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.81</v>
+        <v>1.3</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BF21" t="n">
         <v>1.08</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH21" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4737,143 +4737,143 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="R22" t="n">
-        <v>1.78</v>
+        <v>2.23</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BH22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BI22" s="3" t="n">
         <v>46127.60416666666</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2</v>
+      </c>
+      <c r="S24" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V24" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q24" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="R24" t="n">
-        <v>6.79</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>3</v>
+        <v>4.85</v>
       </c>
       <c r="R25" t="n">
-        <v>2</v>
+        <v>6.79</v>
       </c>
       <c r="S25" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.28</v>
+        <v>5.13</v>
       </c>
       <c r="R26" t="n">
-        <v>4.73</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,16 +5574,16 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.13</v>
+        <v>5.28</v>
       </c>
       <c r="R27" t="n">
-        <v>8.800000000000001</v>
+        <v>4.73</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,16 +5771,16 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>4.98</v>
+        <v>1.94</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.84</v>
+        <v>3.71</v>
       </c>
       <c r="R18" t="n">
-        <v>1.55</v>
+        <v>3.82</v>
       </c>
       <c r="S18" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.94</v>
+        <v>4.98</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.71</v>
+        <v>4.84</v>
       </c>
       <c r="R19" t="n">
-        <v>3.82</v>
+        <v>1.55</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,139 +4347,139 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>4.5</v>
+        <v>7.75</v>
       </c>
       <c r="Q20" t="n">
         <v>3.4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.78</v>
+        <v>1.49</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AT20" t="n">
         <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY20" t="n">
         <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI20" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,139 +4544,139 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>7.75</v>
+        <v>4.5</v>
       </c>
       <c r="Q21" t="n">
         <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.49</v>
+        <v>1.78</v>
       </c>
       <c r="S21" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
         <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
         <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>4.85</v>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>6.79</v>
       </c>
       <c r="S24" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V25" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q25" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="R25" t="n">
-        <v>6.79</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.13</v>
+        <v>5.28</v>
       </c>
       <c r="R26" t="n">
-        <v>8.800000000000001</v>
+        <v>4.73</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,16 +5574,16 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.28</v>
+        <v>5.13</v>
       </c>
       <c r="R27" t="n">
-        <v>4.73</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,16 +5771,16 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -797,7 +797,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.28</v>
+        <v>5.13</v>
       </c>
       <c r="R26" t="n">
-        <v>4.73</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,16 +5574,16 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.13</v>
+        <v>5.28</v>
       </c>
       <c r="R27" t="n">
-        <v>8.800000000000001</v>
+        <v>4.73</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,16 +5771,16 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -797,7 +797,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,139 +4347,139 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>7.75</v>
+        <v>4.5</v>
       </c>
       <c r="Q20" t="n">
         <v>3.4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.49</v>
+        <v>1.78</v>
       </c>
       <c r="S20" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
         <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
         <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,139 +4544,139 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>4.5</v>
+        <v>7.75</v>
       </c>
       <c r="Q21" t="n">
         <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.78</v>
+        <v>1.49</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AT21" t="n">
         <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY21" t="n">
         <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2</v>
+      </c>
+      <c r="S24" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V24" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q24" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="R24" t="n">
-        <v>6.79</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>3</v>
+        <v>4.85</v>
       </c>
       <c r="R25" t="n">
-        <v>2</v>
+        <v>6.79</v>
       </c>
       <c r="S25" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -797,7 +797,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4343,143 +4343,143 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="R20" t="n">
-        <v>1.78</v>
+        <v>2.23</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BH20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BI20" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4737,143 +4737,143 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="R22" t="n">
-        <v>2.23</v>
+        <v>1.78</v>
       </c>
       <c r="S22" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BH22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
         <v>46127.60416666666</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>4.85</v>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>6.79</v>
       </c>
       <c r="S24" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V25" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q25" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="R25" t="n">
-        <v>6.79</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.94</v>
+        <v>4.98</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.71</v>
+        <v>4.84</v>
       </c>
       <c r="R18" t="n">
-        <v>3.82</v>
+        <v>1.55</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>4.98</v>
+        <v>1.94</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.84</v>
+        <v>3.71</v>
       </c>
       <c r="R19" t="n">
-        <v>1.55</v>
+        <v>3.82</v>
       </c>
       <c r="S19" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4343,143 +4343,143 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.6</v>
+        <v>7.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="R20" t="n">
-        <v>2.23</v>
+        <v>1.49</v>
       </c>
       <c r="S20" t="n">
-        <v>4.2</v>
+        <v>8.9</v>
       </c>
       <c r="T20" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="U20" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="V20" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="W20" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="X20" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="AA20" t="n">
         <v>1.03</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AG20" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AI20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.29</v>
+        <v>2.88</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="AO20" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AS20" t="n">
         <v>3.15</v>
       </c>
       <c r="AT20" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
         <v>2.33</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="AX20" t="n">
         <v>1.3</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>2.31</v>
+        <v>3.7</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.81</v>
+        <v>1.3</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BF20" t="n">
         <v>1.08</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH20" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="BI20" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,139 +4544,139 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>7.75</v>
+        <v>4.5</v>
       </c>
       <c r="Q21" t="n">
         <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.49</v>
+        <v>1.78</v>
       </c>
       <c r="S21" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
         <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
         <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,139 +4741,139 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="R22" t="n">
-        <v>1.78</v>
+        <v>2.23</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BH22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BI22" s="3" t="n">
         <v>46127.60416666666</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.13</v>
+        <v>5.28</v>
       </c>
       <c r="R26" t="n">
-        <v>8.800000000000001</v>
+        <v>4.73</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,16 +5574,16 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.28</v>
+        <v>5.13</v>
       </c>
       <c r="R27" t="n">
-        <v>4.73</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,16 +5771,16 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -801,64 +801,64 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R2" t="n">
         <v>2.6</v>
       </c>
       <c r="S2" t="n">
-        <v>3.26</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>2.22</v>
+        <v>2.02</v>
       </c>
       <c r="U2" t="n">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="V2" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W2" t="n">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="X2" t="n">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="AA2" t="n">
         <v>1.08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.49</v>
+        <v>3.55</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG2" t="n">
-        <v>3.41</v>
+        <v>3.3</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AI2" t="n">
-        <v>6.57</v>
+        <v>6.25</v>
       </c>
       <c r="AJ2" t="n">
         <v>1.11</v>
@@ -915,13 +915,13 @@
         <v>2.08</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BC2" t="n">
         <v>2.1</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.66</v>
+        <v>3.75</v>
       </c>
       <c r="BE2" t="n">
         <v>1.63</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,139 +4347,139 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>7.75</v>
+        <v>3.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="R20" t="n">
-        <v>1.49</v>
+        <v>2.23</v>
       </c>
       <c r="S20" t="n">
-        <v>8.9</v>
+        <v>4.2</v>
       </c>
       <c r="T20" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="U20" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="V20" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="X20" t="n">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z20" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA20" t="n">
         <v>1.03</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AG20" t="n">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AI20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.88</v>
+        <v>2.29</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="AO20" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AS20" t="n">
         <v>3.15</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="AU20" t="n">
         <v>2.33</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AX20" t="n">
         <v>1.3</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AZ20" t="n">
-        <v>3.7</v>
+        <v>2.31</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.3</v>
+        <v>1.81</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="BF20" t="n">
         <v>1.08</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="BH20" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="BI20" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,139 +4544,139 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>4.5</v>
+        <v>7.75</v>
       </c>
       <c r="Q21" t="n">
         <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.78</v>
+        <v>1.49</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AT21" t="n">
         <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY21" t="n">
         <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,139 +4741,139 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="R22" t="n">
-        <v>2.23</v>
+        <v>1.78</v>
       </c>
       <c r="S22" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BH22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
         <v>46127.60416666666</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.28</v>
+        <v>5.13</v>
       </c>
       <c r="R26" t="n">
-        <v>4.73</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,16 +5574,16 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.13</v>
+        <v>5.28</v>
       </c>
       <c r="R27" t="n">
-        <v>8.800000000000001</v>
+        <v>4.73</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,16 +5771,16 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3765,13 +3765,13 @@
         <v>3.79</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -3780,10 +3780,10 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -3795,40 +3795,40 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3873,13 +3873,13 @@
         <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BD17" t="n">
         <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BF17" t="n">
         <v>0</v>
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.6</v>
+        <v>3.79</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R20" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="S20" t="n">
         <v>4.2</v>
@@ -4371,10 +4371,10 @@
         <v>2.28</v>
       </c>
       <c r="X20" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z20" t="n">
         <v>8.800000000000001</v>
@@ -4383,7 +4383,7 @@
         <v>1.03</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AC20" t="n">
         <v>1.57</v>
@@ -4392,10 +4392,10 @@
         <v>2.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AG20" t="n">
         <v>5.75</v>
@@ -4410,37 +4410,37 @@
         <v>1.03</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AO20" t="n">
         <v>1.4</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.29</v>
+        <v>2.84</v>
       </c>
       <c r="AS20" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AT20" t="n">
-        <v>4.77</v>
+        <v>4.64</v>
       </c>
       <c r="AU20" t="n">
-        <v>2.33</v>
+        <v>2.47</v>
       </c>
       <c r="AV20" t="n">
         <v>1.91</v>
@@ -4449,10 +4449,10 @@
         <v>1.54</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AZ20" t="n">
         <v>2.31</v>
@@ -4461,13 +4461,13 @@
         <v>1.81</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="BC20" t="n">
         <v>2.8</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="BE20" t="n">
         <v>1.36</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,139 +4544,139 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>7.75</v>
+        <v>4.5</v>
       </c>
       <c r="Q21" t="n">
         <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.49</v>
+        <v>1.78</v>
       </c>
       <c r="S21" t="n">
-        <v>8.9</v>
+        <v>5.8</v>
       </c>
       <c r="T21" t="n">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="U21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC21" t="n">
         <v>2.2</v>
       </c>
-      <c r="V21" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="X21" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>2.82</v>
-      </c>
       <c r="BD21" t="n">
-        <v>2.62</v>
+        <v>3.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.35</v>
+        <v>1.66</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,139 +4741,139 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>4.5</v>
+        <v>7.75</v>
       </c>
       <c r="Q22" t="n">
         <v>3.4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.78</v>
+        <v>1.49</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AT22" t="n">
         <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY22" t="n">
         <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI22" s="3" t="n">
         <v>46127.60416666666</v>
@@ -5144,124 +5144,124 @@
         <v>6.79</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.13</v>
+        <v>5.28</v>
       </c>
       <c r="R26" t="n">
-        <v>8.800000000000001</v>
+        <v>4.73</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.73</v>
+        <v>1.28</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.98</v>
+        <v>3.75</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.28</v>
+        <v>5.13</v>
       </c>
       <c r="R27" t="n">
-        <v>4.73</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.83</v>
+        <v>2.84</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.87</v>
+        <v>1.42</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -1589,22 +1589,22 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="R6" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="S6" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="T6" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="U6" t="n">
-        <v>4.57</v>
+        <v>4.41</v>
       </c>
       <c r="V6" t="n">
         <v>1.28</v>
@@ -1613,10 +1613,10 @@
         <v>3.18</v>
       </c>
       <c r="X6" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Z6" t="n">
         <v>5.2</v>
@@ -1625,7 +1625,7 @@
         <v>1.11</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC6" t="n">
         <v>1.14</v>
@@ -1646,22 +1646,22 @@
         <v>1.44</v>
       </c>
       <c r="AI6" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AJ6" t="n">
         <v>1.14</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3759,10 +3759,10 @@
         <v>1.8</v>
       </c>
       <c r="Q17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R17" t="n">
         <v>3.7</v>
-      </c>
-      <c r="R17" t="n">
-        <v>3.79</v>
       </c>
       <c r="S17" t="n">
         <v>2.28</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,139 +4347,139 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.79</v>
+        <v>7.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="R20" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S20" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W20" t="n">
         <v>2.1</v>
-      </c>
-      <c r="S20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="U20" t="n">
-        <v>3</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="W20" t="n">
-        <v>2.28</v>
       </c>
       <c r="X20" t="n">
         <v>3.7</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="AA20" t="n">
         <v>1.03</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AE20" t="n">
         <v>2.7</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AG20" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AI20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.27</v>
+        <v>1.02</v>
       </c>
       <c r="AO20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BB20" t="n">
         <v>1.4</v>
       </c>
-      <c r="AP20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.37</v>
-      </c>
       <c r="BC20" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BF20" t="n">
         <v>1.08</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH20" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="BI20" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,139 +4544,139 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>4.5</v>
+        <v>3.79</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="R21" t="n">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="S21" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="T21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD21" t="n">
         <v>2.25</v>
       </c>
-      <c r="U21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="V21" t="n">
+      <c r="AE21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BB21" t="n">
         <v>1.37</v>
       </c>
-      <c r="W21" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AJ21" t="n">
+      <c r="BC21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BF21" t="n">
         <v>1.08</v>
       </c>
-      <c r="AK21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>1.15</v>
-      </c>
       <c r="BG21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BH21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,139 +4741,139 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>7.75</v>
+        <v>4.5</v>
       </c>
       <c r="Q22" t="n">
         <v>3.4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.49</v>
+        <v>1.78</v>
       </c>
       <c r="S22" t="n">
-        <v>8.9</v>
+        <v>5.8</v>
       </c>
       <c r="T22" t="n">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="U22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC22" t="n">
         <v>2.2</v>
       </c>
-      <c r="V22" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="X22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>2.82</v>
-      </c>
       <c r="BD22" t="n">
-        <v>2.62</v>
+        <v>3.6</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.35</v>
+        <v>1.66</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>10.9</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>14.8</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.28</v>
+        <v>5.13</v>
       </c>
       <c r="R26" t="n">
-        <v>4.73</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S26" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="T26" t="n">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="U26" t="n">
-        <v>4.33</v>
+        <v>6.65</v>
       </c>
       <c r="V26" t="n">
-        <v>1.13</v>
+        <v>1.34</v>
       </c>
       <c r="W26" t="n">
-        <v>5.4</v>
+        <v>3.24</v>
       </c>
       <c r="X26" t="n">
-        <v>1.87</v>
+        <v>2.55</v>
       </c>
       <c r="Y26" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK26" t="n">
         <v>2.02</v>
       </c>
-      <c r="Z26" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AK26" t="n">
+      <c r="AL26" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ26" t="n">
         <v>1.35</v>
       </c>
-      <c r="AL26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>1.4</v>
-      </c>
       <c r="BA26" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.47</v>
+        <v>1.91</v>
       </c>
       <c r="BD26" t="n">
-        <v>8.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE26" t="n">
-        <v>2.48</v>
+        <v>1.79</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.45</v>
+        <v>1.2</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.13</v>
+        <v>5.28</v>
       </c>
       <c r="R27" t="n">
-        <v>8.800000000000001</v>
+        <v>4.73</v>
       </c>
       <c r="S27" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="T27" t="n">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="U27" t="n">
-        <v>6.65</v>
+        <v>4.33</v>
       </c>
       <c r="V27" t="n">
-        <v>1.34</v>
+        <v>1.13</v>
       </c>
       <c r="W27" t="n">
-        <v>3.24</v>
+        <v>5.4</v>
       </c>
       <c r="X27" t="n">
-        <v>2.55</v>
+        <v>1.87</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.48</v>
+        <v>2.02</v>
       </c>
       <c r="Z27" t="n">
-        <v>6</v>
+        <v>3.36</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.23</v>
+        <v>1.03</v>
       </c>
       <c r="AD27" t="n">
-        <v>4.2</v>
+        <v>7.3</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.73</v>
+        <v>1.28</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.98</v>
+        <v>3.75</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.84</v>
+        <v>1.83</v>
       </c>
       <c r="AH27" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AJ27" t="n">
         <v>1.42</v>
       </c>
-      <c r="AI27" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AK27" t="n">
-        <v>2.02</v>
+        <v>1.35</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.78</v>
+        <v>3</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AN27" t="n">
-        <v>2.88</v>
+        <v>2.27</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AQ27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BF27" t="n">
         <v>1.45</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>1.2</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G30" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>4.98</v>
+        <v>1.94</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.84</v>
+        <v>3.71</v>
       </c>
       <c r="R18" t="n">
-        <v>1.55</v>
+        <v>3.82</v>
       </c>
       <c r="S18" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.94</v>
+        <v>4.98</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.71</v>
+        <v>4.84</v>
       </c>
       <c r="R19" t="n">
-        <v>3.82</v>
+        <v>1.55</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,139 +4347,139 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>7.75</v>
+        <v>3.79</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="R20" t="n">
-        <v>1.49</v>
+        <v>2.1</v>
       </c>
       <c r="S20" t="n">
-        <v>8.9</v>
+        <v>4.2</v>
       </c>
       <c r="T20" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="U20" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="V20" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="X20" t="n">
         <v>3.7</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z20" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA20" t="n">
         <v>1.03</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AE20" t="n">
         <v>2.7</v>
       </c>
       <c r="AF20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BE20" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>1.35</v>
       </c>
       <c r="BF20" t="n">
         <v>1.08</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="BH20" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="BI20" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,139 +4544,139 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.79</v>
+        <v>4.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="S21" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="T21" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="U21" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="V21" t="n">
-        <v>1.6</v>
+        <v>1.37</v>
       </c>
       <c r="W21" t="n">
-        <v>2.28</v>
+        <v>2.97</v>
       </c>
       <c r="X21" t="n">
-        <v>3.7</v>
+        <v>2.69</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.800000000000001</v>
+        <v>6.25</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AB21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>1.08</v>
       </c>
-      <c r="AC21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AF21" t="n">
+      <c r="AK21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
         <v>1.38</v>
       </c>
-      <c r="AG21" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>11</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK21" t="n">
+      <c r="AQ21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC21" t="n">
         <v>2.2</v>
       </c>
-      <c r="AL21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>2.8</v>
-      </c>
       <c r="BD21" t="n">
-        <v>2.74</v>
+        <v>3.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.36</v>
+        <v>1.66</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BH21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,139 +4741,139 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>4.5</v>
+        <v>7.75</v>
       </c>
       <c r="Q22" t="n">
         <v>3.4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.78</v>
+        <v>1.49</v>
       </c>
       <c r="S22" t="n">
-        <v>5.8</v>
+        <v>8.9</v>
       </c>
       <c r="T22" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="U22" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="V22" t="n">
-        <v>1.37</v>
+        <v>1.65</v>
       </c>
       <c r="W22" t="n">
-        <v>2.97</v>
+        <v>2.1</v>
       </c>
       <c r="X22" t="n">
-        <v>2.69</v>
+        <v>3.7</v>
       </c>
       <c r="Y22" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BB22" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z22" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AJ22" t="n">
+      <c r="BC22" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BF22" t="n">
         <v>1.08</v>
       </c>
-      <c r="AK22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>1.15</v>
-      </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI22" s="3" t="n">
         <v>46127.60416666666</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2</v>
+      </c>
+      <c r="S24" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V24" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q24" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="R24" t="n">
-        <v>6.79</v>
-      </c>
-      <c r="S24" t="n">
+      <c r="W24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK24" t="n">
         <v>1.85</v>
       </c>
-      <c r="T24" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="U24" t="n">
-        <v>6</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W24" t="n">
+      <c r="AL24" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BD24" t="n">
         <v>3.42</v>
       </c>
-      <c r="X24" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BE24" t="n">
-        <v>1.94</v>
+        <v>1.55</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>3</v>
+        <v>4.85</v>
       </c>
       <c r="R25" t="n">
-        <v>2</v>
+        <v>6.79</v>
       </c>
       <c r="S25" t="n">
-        <v>4.29</v>
+        <v>1.85</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>2.51</v>
       </c>
       <c r="U25" t="n">
-        <v>2.75</v>
+        <v>6</v>
       </c>
       <c r="V25" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="W25" t="n">
-        <v>2.8</v>
+        <v>3.42</v>
       </c>
       <c r="X25" t="n">
-        <v>3.15</v>
+        <v>2.36</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.31</v>
+        <v>1.56</v>
       </c>
       <c r="Z25" t="n">
-        <v>8.4</v>
+        <v>5</v>
       </c>
       <c r="AA25" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AM25" t="n">
         <v>1.07</v>
       </c>
-      <c r="AB25" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AN25" t="n">
-        <v>1.29</v>
+        <v>2.98</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.44</v>
+        <v>1.17</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.56</v>
+        <v>1.3</v>
       </c>
       <c r="AR25" t="n">
-        <v>2.03</v>
+        <v>1.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.7</v>
+        <v>1.81</v>
       </c>
       <c r="AT25" t="n">
-        <v>3.9</v>
+        <v>2.23</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.2</v>
+        <v>4.25</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.93</v>
+        <v>3.1</v>
       </c>
       <c r="AW25" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AY25" t="n">
         <v>1.57</v>
       </c>
-      <c r="AX25" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AZ25" t="n">
-        <v>2.55</v>
+        <v>1.22</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.63</v>
+        <v>4.8</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.35</v>
+        <v>1.81</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.42</v>
+        <v>4.8</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.55</v>
+        <v>1.94</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q2" t="n">
         <v>3.25</v>
@@ -810,7 +810,7 @@
         <v>2.6</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T2" t="n">
         <v>2.02</v>
@@ -822,16 +822,16 @@
         <v>1.36</v>
       </c>
       <c r="W2" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="X2" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="Y2" t="n">
         <v>1.42</v>
       </c>
       <c r="Z2" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AA2" t="n">
         <v>1.08</v>
@@ -843,25 +843,25 @@
         <v>1.28</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AG2" t="n">
-        <v>3.3</v>
+        <v>3.13</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AI2" t="n">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AK2" t="n">
         <v>1.77</v>
@@ -915,19 +915,19 @@
         <v>2.08</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BC2" t="n">
         <v>2.1</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.75</v>
+        <v>3.96</v>
       </c>
       <c r="BE2" t="n">
         <v>1.63</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,139 +4347,139 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.79</v>
+        <v>7.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="R20" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S20" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W20" t="n">
         <v>2.1</v>
-      </c>
-      <c r="S20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="U20" t="n">
-        <v>3</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="W20" t="n">
-        <v>2.28</v>
       </c>
       <c r="X20" t="n">
         <v>3.7</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="AA20" t="n">
         <v>1.03</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AE20" t="n">
         <v>2.7</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AG20" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AI20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.27</v>
+        <v>1.02</v>
       </c>
       <c r="AO20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BB20" t="n">
         <v>1.4</v>
       </c>
-      <c r="AP20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.37</v>
-      </c>
       <c r="BC20" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BF20" t="n">
         <v>1.08</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH20" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="BI20" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,139 +4544,139 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>4.5</v>
+        <v>3.79</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="R21" t="n">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="S21" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="T21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD21" t="n">
         <v>2.25</v>
       </c>
-      <c r="U21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="V21" t="n">
+      <c r="AE21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BB21" t="n">
         <v>1.37</v>
       </c>
-      <c r="W21" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AJ21" t="n">
+      <c r="BC21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BF21" t="n">
         <v>1.08</v>
       </c>
-      <c r="AK21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>1.15</v>
-      </c>
       <c r="BG21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BH21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,139 +4741,139 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>7.75</v>
+        <v>4.5</v>
       </c>
       <c r="Q22" t="n">
         <v>3.4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.49</v>
+        <v>1.78</v>
       </c>
       <c r="S22" t="n">
-        <v>8.9</v>
+        <v>5.8</v>
       </c>
       <c r="T22" t="n">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="U22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC22" t="n">
         <v>2.2</v>
       </c>
-      <c r="V22" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="X22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>2.82</v>
-      </c>
       <c r="BD22" t="n">
-        <v>2.62</v>
+        <v>3.6</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.35</v>
+        <v>1.66</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
         <v>46127.60416666666</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.13</v>
+        <v>5.28</v>
       </c>
       <c r="R26" t="n">
-        <v>8.800000000000001</v>
+        <v>4.73</v>
       </c>
       <c r="S26" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="T26" t="n">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="U26" t="n">
-        <v>6.65</v>
+        <v>4.33</v>
       </c>
       <c r="V26" t="n">
-        <v>1.34</v>
+        <v>1.13</v>
       </c>
       <c r="W26" t="n">
-        <v>3.24</v>
+        <v>5.4</v>
       </c>
       <c r="X26" t="n">
-        <v>2.55</v>
+        <v>1.87</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.48</v>
+        <v>2.02</v>
       </c>
       <c r="Z26" t="n">
-        <v>6</v>
+        <v>3.36</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.23</v>
+        <v>1.03</v>
       </c>
       <c r="AD26" t="n">
-        <v>4.2</v>
+        <v>7.3</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.73</v>
+        <v>1.28</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.98</v>
+        <v>3.75</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.84</v>
+        <v>1.83</v>
       </c>
       <c r="AH26" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AJ26" t="n">
         <v>1.42</v>
       </c>
-      <c r="AI26" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AK26" t="n">
-        <v>2.02</v>
+        <v>1.35</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.78</v>
+        <v>3</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AN26" t="n">
-        <v>2.88</v>
+        <v>2.27</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AQ26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BF26" t="n">
         <v>1.45</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>1.2</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.28</v>
+        <v>5.13</v>
       </c>
       <c r="R27" t="n">
-        <v>4.73</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S27" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="T27" t="n">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="U27" t="n">
-        <v>4.33</v>
+        <v>6.65</v>
       </c>
       <c r="V27" t="n">
-        <v>1.13</v>
+        <v>1.34</v>
       </c>
       <c r="W27" t="n">
-        <v>5.4</v>
+        <v>3.24</v>
       </c>
       <c r="X27" t="n">
-        <v>1.87</v>
+        <v>2.55</v>
       </c>
       <c r="Y27" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK27" t="n">
         <v>2.02</v>
       </c>
-      <c r="Z27" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AK27" t="n">
+      <c r="AL27" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ27" t="n">
         <v>1.35</v>
       </c>
-      <c r="AL27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>1.4</v>
-      </c>
       <c r="BA27" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.47</v>
+        <v>1.91</v>
       </c>
       <c r="BD27" t="n">
-        <v>8.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE27" t="n">
-        <v>2.48</v>
+        <v>1.79</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.45</v>
+        <v>1.2</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G29" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -1592,37 +1592,37 @@
         <v>1.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="R6" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="S6" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="T6" t="n">
-        <v>2.21</v>
+        <v>2.46</v>
       </c>
       <c r="U6" t="n">
-        <v>4.41</v>
+        <v>3.65</v>
       </c>
       <c r="V6" t="n">
         <v>1.28</v>
       </c>
       <c r="W6" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="X6" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AB6" t="n">
         <v>1.03</v>
@@ -1634,22 +1634,22 @@
         <v>4.4</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AI6" t="n">
-        <v>4.45</v>
+        <v>4</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AK6" t="n">
         <v>1.54</v>
@@ -1658,10 +1658,10 @@
         <v>2.29</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,16 +1703,16 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="BF6" t="n">
         <v>1.25</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3762,46 +3762,46 @@
         <v>3.4</v>
       </c>
       <c r="R17" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="S17" t="n">
-        <v>2.28</v>
+        <v>2.47</v>
       </c>
       <c r="T17" t="n">
-        <v>2.3</v>
+        <v>2.01</v>
       </c>
       <c r="U17" t="n">
-        <v>3.85</v>
+        <v>4.96</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X17" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.9</v>
+        <v>3.84</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="AF17" t="n">
         <v>2.05</v>
@@ -3813,22 +3813,22 @@
         <v>1.38</v>
       </c>
       <c r="AI17" t="n">
-        <v>4.5</v>
+        <v>4.77</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AK17" t="n">
         <v>1.54</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.71</v>
+        <v>3.68</v>
       </c>
       <c r="R18" t="n">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -3977,10 +3977,10 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
@@ -3992,40 +3992,40 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4034,49 +4034,49 @@
         <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AU18" t="n">
         <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BB18" t="n">
         <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BD18" t="n">
         <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BF18" t="n">
         <v>0</v>
@@ -4162,10 +4162,10 @@
         <v>5.08</v>
       </c>
       <c r="T19" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="V19" t="n">
         <v>1.17</v>
@@ -4174,16 +4174,16 @@
         <v>4.25</v>
       </c>
       <c r="X19" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="Y19" t="n">
         <v>1.8</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AB19" t="n">
         <v>1.01</v>
@@ -4219,10 +4219,10 @@
         <v>2.5</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,13 +4264,13 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="BC19" t="n">
         <v>1.54</v>
       </c>
       <c r="BD19" t="n">
-        <v>6.4</v>
+        <v>5.75</v>
       </c>
       <c r="BE19" t="n">
         <v>2.32</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,139 +4544,139 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.79</v>
+        <v>6</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="R21" t="n">
-        <v>2.1</v>
+        <v>1.49</v>
       </c>
       <c r="S21" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="T21" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="U21" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="V21" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="W21" t="n">
-        <v>2.28</v>
+        <v>2.85</v>
       </c>
       <c r="X21" t="n">
-        <v>3.7</v>
+        <v>2.69</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.2</v>
+        <v>1.39</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.57</v>
+        <v>1.26</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.25</v>
+        <v>3.2</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.7</v>
+        <v>1.97</v>
       </c>
       <c r="AF21" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
         <v>1.38</v>
       </c>
-      <c r="AG21" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>11</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AM21" t="n">
+      <c r="AQ21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BA21" t="n">
         <v>1.33</v>
       </c>
-      <c r="AN21" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>1.81</v>
-      </c>
       <c r="BB21" t="n">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.8</v>
+        <v>2.14</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.74</v>
+        <v>3.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BH21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,139 +4741,139 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>4.5</v>
+        <v>3.79</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="R22" t="n">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="S22" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="T22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD22" t="n">
         <v>2.25</v>
       </c>
-      <c r="U22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="V22" t="n">
+      <c r="AE22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BB22" t="n">
         <v>1.37</v>
       </c>
-      <c r="W22" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AJ22" t="n">
+      <c r="BC22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BF22" t="n">
         <v>1.08</v>
       </c>
-      <c r="AK22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>1.15</v>
-      </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BH22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BI22" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Q23" t="n">
-        <v>10.9</v>
+        <v>11.7</v>
       </c>
       <c r="R23" t="n">
-        <v>14.8</v>
+        <v>16</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S24" t="n">
-        <v>4.29</v>
+        <v>1.85</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>2.52</v>
       </c>
       <c r="U24" t="n">
-        <v>2.75</v>
+        <v>5.5</v>
       </c>
       <c r="V24" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="W24" t="n">
-        <v>2.8</v>
+        <v>3.42</v>
       </c>
       <c r="X24" t="n">
-        <v>3.15</v>
+        <v>2.34</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.31</v>
+        <v>1.56</v>
       </c>
       <c r="Z24" t="n">
-        <v>8.4</v>
+        <v>5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.89</v>
+        <v>4.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.67</v>
+        <v>2.35</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.8</v>
+        <v>2.45</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.19</v>
+        <v>1.53</v>
       </c>
       <c r="AI24" t="n">
-        <v>8</v>
+        <v>4.33</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.29</v>
+        <v>2.98</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.44</v>
+        <v>1.17</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.56</v>
+        <v>1.3</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.03</v>
+        <v>1.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.7</v>
+        <v>1.81</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.9</v>
+        <v>2.23</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.2</v>
+        <v>4.25</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.93</v>
+        <v>3.1</v>
       </c>
       <c r="AW24" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AY24" t="n">
         <v>1.57</v>
       </c>
-      <c r="AX24" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AZ24" t="n">
-        <v>2.55</v>
+        <v>1.22</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.63</v>
+        <v>4.8</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.42</v>
+        <v>4.8</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.85</v>
+        <v>3.5</v>
       </c>
       <c r="R25" t="n">
-        <v>6.79</v>
+        <v>1.95</v>
       </c>
       <c r="S25" t="n">
-        <v>1.85</v>
+        <v>4.42</v>
       </c>
       <c r="T25" t="n">
-        <v>2.51</v>
+        <v>2.19</v>
       </c>
       <c r="U25" t="n">
-        <v>6</v>
+        <v>2.43</v>
       </c>
       <c r="V25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH25" t="n">
         <v>1.28</v>
       </c>
-      <c r="W25" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="Y25" t="n">
+      <c r="AI25" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ25" t="n">
         <v>1.56</v>
       </c>
-      <c r="Z25" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG25" t="n">
+      <c r="AR25" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AS25" t="n">
         <v>2.45</v>
       </c>
-      <c r="AH25" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
+      <c r="AT25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BF25" t="n">
         <v>1.17</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>1.25</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5529,22 +5529,22 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.28</v>
+        <v>4.5</v>
       </c>
       <c r="R26" t="n">
-        <v>4.73</v>
+        <v>4.45</v>
       </c>
       <c r="S26" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="T26" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="U26" t="n">
-        <v>4.33</v>
+        <v>3.78</v>
       </c>
       <c r="V26" t="n">
         <v>1.13</v>
@@ -5580,82 +5580,82 @@
         <v>3.75</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="AI26" t="n">
         <v>2.9</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AL26" t="n">
         <v>3</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AN26" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AU26" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AV26" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AW26" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="BD26" t="n">
         <v>8.1</v>
       </c>
       <c r="BE26" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5726,22 +5726,22 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.13</v>
+        <v>4.4</v>
       </c>
       <c r="R27" t="n">
-        <v>8.800000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="S27" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="T27" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="U27" t="n">
-        <v>6.65</v>
+        <v>6.6</v>
       </c>
       <c r="V27" t="n">
         <v>1.34</v>
@@ -5765,40 +5765,40 @@
         <v>1.04</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AD27" t="n">
         <v>4.2</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="AG27" t="n">
         <v>2.84</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AI27" t="n">
         <v>5.25</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AK27" t="n">
         <v>2.02</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AN27" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5840,10 +5840,10 @@
         <v>3.7</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="BD27" t="n">
         <v>4.2</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -915,7 +915,7 @@
         <v>2.08</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="BC2" t="n">
         <v>2.1</v>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="Q6" t="n">
         <v>3.5</v>
@@ -1601,10 +1601,10 @@
         <v>2.3</v>
       </c>
       <c r="T6" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="U6" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="V6" t="n">
         <v>1.28</v>
@@ -1613,10 +1613,10 @@
         <v>3.15</v>
       </c>
       <c r="X6" t="n">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Z6" t="n">
         <v>5</v>
@@ -1646,22 +1646,22 @@
         <v>1.45</v>
       </c>
       <c r="AI6" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AK6" t="n">
         <v>1.54</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1706,13 +1706,13 @@
         <v>1.18</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="BD6" t="n">
         <v>4.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="BF6" t="n">
         <v>1.25</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3786,40 +3786,40 @@
         <v>1.46</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.84</v>
+        <v>4.31</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG17" t="n">
         <v>2.55</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AI17" t="n">
         <v>4.77</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="AL17" t="n">
         <v>2.17</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="BC17" t="n">
         <v>1.82</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BE17" t="n">
         <v>1.83</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W18" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AH18" t="n">
         <v>1.93</v>
       </c>
-      <c r="Q18" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="R18" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="U18" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Y18" t="n">
+      <c r="AI18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BC18" t="n">
         <v>1.54</v>
       </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>1.82</v>
-      </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.86</v>
+        <v>2.32</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>4.98</v>
+        <v>1.93</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.84</v>
+        <v>3.68</v>
       </c>
       <c r="R19" t="n">
-        <v>1.55</v>
+        <v>3.78</v>
       </c>
       <c r="S19" t="n">
-        <v>5.08</v>
+        <v>2.2</v>
       </c>
       <c r="T19" t="n">
-        <v>2.68</v>
+        <v>2.43</v>
       </c>
       <c r="U19" t="n">
-        <v>1.85</v>
+        <v>4.25</v>
       </c>
       <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
         <v>1.17</v>
       </c>
-      <c r="W19" t="n">
+      <c r="AD19" t="n">
         <v>4.25</v>
       </c>
-      <c r="X19" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>6.85</v>
-      </c>
       <c r="AE19" t="n">
-        <v>1.35</v>
+        <v>1.58</v>
       </c>
       <c r="AF19" t="n">
-        <v>3.19</v>
+        <v>2.18</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.92</v>
+        <v>2.48</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.93</v>
+        <v>1.47</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.8</v>
+        <v>4.25</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.38</v>
+        <v>1.17</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.15</v>
+        <v>1.96</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4231,52 +4231,52 @@
         <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AU19" t="n">
         <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.54</v>
+        <v>1.82</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.32</v>
+        <v>1.86</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="R24" t="n">
-        <v>7</v>
+        <v>1.95</v>
       </c>
       <c r="S24" t="n">
-        <v>1.85</v>
+        <v>4.42</v>
       </c>
       <c r="T24" t="n">
-        <v>2.52</v>
+        <v>2.19</v>
       </c>
       <c r="U24" t="n">
-        <v>5.5</v>
+        <v>2.43</v>
       </c>
       <c r="V24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC24" t="n">
         <v>1.25</v>
       </c>
-      <c r="W24" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Y24" t="n">
+      <c r="AD24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ24" t="n">
         <v>1.56</v>
       </c>
-      <c r="Z24" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AG24" t="n">
+      <c r="AR24" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AS24" t="n">
         <v>2.45</v>
       </c>
-      <c r="AH24" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
+      <c r="AT24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BF24" t="n">
         <v>1.17</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>1.25</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="R25" t="n">
+        <v>7</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="U25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W25" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE25" t="n">
         <v>1.95</v>
       </c>
-      <c r="S25" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W25" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC25" t="n">
+      <c r="BF25" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>6.34</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>1.17</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W26" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AX26" t="n">
         <v>1.58</v>
       </c>
-      <c r="Q26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R26" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="S26" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U26" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W26" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AK26" t="n">
+      <c r="AY26" t="n">
         <v>1.36</v>
       </c>
-      <c r="AL26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>1.49</v>
-      </c>
       <c r="AZ26" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="BA26" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.51</v>
+        <v>2.06</v>
       </c>
       <c r="BD26" t="n">
-        <v>8.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE26" t="n">
-        <v>2.54</v>
+        <v>1.79</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.51</v>
+        <v>1.2</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="R27" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W27" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD27" t="n">
         <v>7.3</v>
       </c>
-      <c r="S27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="T27" t="n">
+      <c r="AE27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AT27" t="n">
         <v>2.4</v>
       </c>
-      <c r="U27" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W27" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="X27" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>2.85</v>
-      </c>
       <c r="AU27" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="AV27" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.93</v>
+        <v>2.23</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.06</v>
+        <v>1.51</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.2</v>
+        <v>8.1</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.79</v>
+        <v>2.54</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.2</v>
+        <v>1.51</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.7</v>
+        <v>1.36</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.95</v>
+        <v>7.5</v>
       </c>
       <c r="S24" t="n">
-        <v>4.42</v>
+        <v>1.8</v>
       </c>
       <c r="T24" t="n">
-        <v>2.19</v>
+        <v>2.55</v>
       </c>
       <c r="U24" t="n">
+        <v>6</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W24" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AG24" t="n">
         <v>2.43</v>
       </c>
-      <c r="V24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W24" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF24" t="n">
+      <c r="AH24" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AX24" t="n">
         <v>1.87</v>
       </c>
-      <c r="AG24" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>6.34</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL24" t="n">
+      <c r="AY24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="BE24" t="n">
         <v>1.96</v>
       </c>
-      <c r="AM24" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>1.67</v>
-      </c>
       <c r="BF24" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y25" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q25" t="n">
-        <v>5</v>
-      </c>
-      <c r="R25" t="n">
-        <v>7</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="U25" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W25" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Y25" t="n">
+      <c r="Z25" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ25" t="n">
         <v>1.56</v>
       </c>
-      <c r="Z25" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AG25" t="n">
+      <c r="AR25" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AS25" t="n">
         <v>2.45</v>
       </c>
-      <c r="AH25" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AM25" t="n">
+      <c r="AT25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BF25" t="n">
         <v>1.15</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>1.25</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -1598,13 +1598,13 @@
         <v>3.6</v>
       </c>
       <c r="S6" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="T6" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="U6" t="n">
-        <v>3.9</v>
+        <v>4.57</v>
       </c>
       <c r="V6" t="n">
         <v>1.28</v>
@@ -1613,16 +1613,16 @@
         <v>3.15</v>
       </c>
       <c r="X6" t="n">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="Y6" t="n">
         <v>1.53</v>
       </c>
       <c r="Z6" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AB6" t="n">
         <v>1.03</v>
@@ -1634,22 +1634,22 @@
         <v>4.4</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.21</v>
+        <v>2.26</v>
       </c>
       <c r="AG6" t="n">
         <v>2.45</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AI6" t="n">
         <v>4.3</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AK6" t="n">
         <v>1.54</v>
@@ -1661,7 +1661,7 @@
         <v>1.19</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3762,16 +3762,16 @@
         <v>3.4</v>
       </c>
       <c r="R17" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="S17" t="n">
-        <v>2.47</v>
+        <v>2.52</v>
       </c>
       <c r="T17" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="U17" t="n">
-        <v>4.96</v>
+        <v>4.86</v>
       </c>
       <c r="V17" t="n">
         <v>1.38</v>
@@ -3786,10 +3786,10 @@
         <v>1.46</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AB17" t="n">
         <v>1.04</v>
@@ -3798,37 +3798,37 @@
         <v>1.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>4.31</v>
+        <v>4.23</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AG17" t="n">
         <v>2.55</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AI17" t="n">
-        <v>4.77</v>
+        <v>4.5</v>
       </c>
       <c r="AJ17" t="n">
         <v>1.12</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="BD17" t="n">
         <v>4.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>4.98</v>
+        <v>1.93</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.84</v>
+        <v>3.68</v>
       </c>
       <c r="R18" t="n">
-        <v>1.55</v>
+        <v>3.78</v>
       </c>
       <c r="S18" t="n">
-        <v>5.08</v>
+        <v>2.2</v>
       </c>
       <c r="T18" t="n">
-        <v>2.68</v>
+        <v>2.43</v>
       </c>
       <c r="U18" t="n">
-        <v>1.85</v>
+        <v>4.25</v>
       </c>
       <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
         <v>1.17</v>
       </c>
-      <c r="W18" t="n">
+      <c r="AD18" t="n">
         <v>4.25</v>
       </c>
-      <c r="X18" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>6.85</v>
-      </c>
       <c r="AE18" t="n">
-        <v>1.35</v>
+        <v>1.58</v>
       </c>
       <c r="AF18" t="n">
-        <v>3.19</v>
+        <v>2.18</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.92</v>
+        <v>2.48</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.93</v>
+        <v>1.47</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.8</v>
+        <v>4.25</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.38</v>
+        <v>1.17</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.15</v>
+        <v>1.96</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4034,52 +4034,52 @@
         <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AU18" t="n">
         <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.54</v>
+        <v>1.82</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.32</v>
+        <v>1.86</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W19" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.93</v>
       </c>
-      <c r="Q19" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="R19" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="U19" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Y19" t="n">
+      <c r="AI19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BC19" t="n">
         <v>1.54</v>
       </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>1.82</v>
-      </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.86</v>
+        <v>2.32</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,139 +4544,139 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>6</v>
+        <v>3.79</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="R21" t="n">
-        <v>1.49</v>
+        <v>2.1</v>
       </c>
       <c r="S21" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="T21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD21" t="n">
         <v>2.25</v>
       </c>
-      <c r="U21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="V21" t="n">
+      <c r="AE21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BE21" t="n">
         <v>1.36</v>
       </c>
-      <c r="W21" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.65</v>
-      </c>
       <c r="BF21" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="BG21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BH21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,139 +4741,139 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.79</v>
+        <v>6</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="R22" t="n">
-        <v>2.1</v>
+        <v>1.49</v>
       </c>
       <c r="S22" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="T22" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="U22" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="V22" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="W22" t="n">
-        <v>2.28</v>
+        <v>2.85</v>
       </c>
       <c r="X22" t="n">
-        <v>3.7</v>
+        <v>2.69</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.2</v>
+        <v>1.39</v>
       </c>
       <c r="Z22" t="n">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.57</v>
+        <v>1.26</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.25</v>
+        <v>3.2</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.7</v>
+        <v>1.97</v>
       </c>
       <c r="AF22" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
         <v>1.38</v>
       </c>
-      <c r="AG22" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AM22" t="n">
+      <c r="AQ22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BA22" t="n">
         <v>1.33</v>
       </c>
-      <c r="AN22" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>1.81</v>
-      </c>
       <c r="BB22" t="n">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.8</v>
+        <v>2.14</v>
       </c>
       <c r="BD22" t="n">
-        <v>2.74</v>
+        <v>3.6</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="BG22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BH22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
         <v>46127.60416666666</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="R26" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W26" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD26" t="n">
         <v>7.3</v>
       </c>
-      <c r="S26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="T26" t="n">
+      <c r="AE26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AT26" t="n">
         <v>2.4</v>
       </c>
-      <c r="U26" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W26" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>2.85</v>
-      </c>
       <c r="AU26" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.93</v>
+        <v>2.23</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.06</v>
+        <v>1.51</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.2</v>
+        <v>8.1</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.79</v>
+        <v>2.54</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.2</v>
+        <v>1.51</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W27" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="X27" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AX27" t="n">
         <v>1.58</v>
       </c>
-      <c r="Q27" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R27" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="S27" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U27" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W27" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AK27" t="n">
+      <c r="AY27" t="n">
         <v>1.36</v>
       </c>
-      <c r="AL27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>1.49</v>
-      </c>
       <c r="AZ27" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="BA27" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.51</v>
+        <v>2.06</v>
       </c>
       <c r="BD27" t="n">
-        <v>8.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE27" t="n">
-        <v>2.54</v>
+        <v>1.79</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.51</v>
+        <v>1.2</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G30" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q2" t="n">
         <v>3.25</v>
@@ -813,61 +813,61 @@
         <v>3.2</v>
       </c>
       <c r="T2" t="n">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="U2" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="V2" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W2" t="n">
-        <v>2.85</v>
+        <v>2.73</v>
       </c>
       <c r="X2" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="Y2" t="n">
         <v>1.42</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.5</v>
+        <v>6.95</v>
       </c>
       <c r="AA2" t="n">
         <v>1.08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="AG2" t="n">
-        <v>3.13</v>
+        <v>3.4</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AI2" t="n">
-        <v>5.75</v>
+        <v>6.15</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AM2" t="n">
         <v>1.28</v>
@@ -915,19 +915,19 @@
         <v>2.08</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="BC2" t="n">
         <v>2.1</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.96</v>
+        <v>3.66</v>
       </c>
       <c r="BE2" t="n">
         <v>1.63</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -1589,22 +1589,22 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R6" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="S6" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="T6" t="n">
         <v>2.18</v>
       </c>
       <c r="U6" t="n">
-        <v>4.57</v>
+        <v>4.68</v>
       </c>
       <c r="V6" t="n">
         <v>1.28</v>
@@ -1616,7 +1616,7 @@
         <v>2.33</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="Z6" t="n">
         <v>5.2</v>
@@ -1634,16 +1634,16 @@
         <v>4.4</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AI6" t="n">
         <v>4.3</v>
@@ -1652,16 +1652,16 @@
         <v>1.19</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AL6" t="n">
         <v>2.28</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,13 +1703,13 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="BC6" t="n">
         <v>1.79</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BE6" t="n">
         <v>1.91</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2386,13 +2386,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -2401,10 +2401,10 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -2416,40 +2416,40 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2494,13 +2494,13 @@
         <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD10" t="n">
         <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BF10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.12</v>
+        <v>3.6</v>
       </c>
       <c r="R11" t="n">
-        <v>2.45</v>
+        <v>4.14</v>
       </c>
       <c r="S11" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="Q17" t="n">
         <v>3.4</v>
       </c>
       <c r="R17" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="S17" t="n">
         <v>2.52</v>
@@ -3792,25 +3792,25 @@
         <v>1.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AD17" t="n">
-        <v>4.23</v>
+        <v>3.78</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="AG17" t="n">
         <v>2.55</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AI17" t="n">
         <v>4.5</v>
@@ -3822,7 +3822,7 @@
         <v>1.59</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AM17" t="n">
         <v>1.28</v>
@@ -3870,13 +3870,13 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BE17" t="n">
         <v>1.87</v>
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>4.98</v>
+        <v>6.15</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.84</v>
+        <v>5.4</v>
       </c>
       <c r="R19" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="S19" t="n">
-        <v>5.08</v>
+        <v>5.55</v>
       </c>
       <c r="T19" t="n">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="U19" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="V19" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="W19" t="n">
-        <v>4.25</v>
+        <v>4.8</v>
       </c>
       <c r="X19" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.75</v>
+        <v>3.42</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AB19" t="n">
         <v>1.01</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AD19" t="n">
-        <v>6.85</v>
+        <v>7.7</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AF19" t="n">
-        <v>3.19</v>
+        <v>3.44</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.92</v>
+        <v>1.73</v>
       </c>
       <c r="AH19" t="n">
         <v>1.93</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AK19" t="n">
         <v>1.46</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4267,16 +4267,16 @@
         <v>1.11</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="BD19" t="n">
         <v>5.75</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.32</v>
+        <v>2.56</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,139 +4544,139 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.79</v>
+        <v>6</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="R21" t="n">
-        <v>2.1</v>
+        <v>1.49</v>
       </c>
       <c r="S21" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="T21" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="U21" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="V21" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="W21" t="n">
-        <v>2.28</v>
+        <v>2.85</v>
       </c>
       <c r="X21" t="n">
-        <v>3.7</v>
+        <v>2.69</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.2</v>
+        <v>1.39</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.57</v>
+        <v>1.26</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.25</v>
+        <v>3.2</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.7</v>
+        <v>1.97</v>
       </c>
       <c r="AF21" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
         <v>1.38</v>
       </c>
-      <c r="AG21" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>11</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AM21" t="n">
+      <c r="AQ21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BA21" t="n">
         <v>1.33</v>
       </c>
-      <c r="AN21" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>1.81</v>
-      </c>
       <c r="BB21" t="n">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.8</v>
+        <v>2.14</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.74</v>
+        <v>3.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BH21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,139 +4741,139 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>6</v>
+        <v>3.87</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="R22" t="n">
-        <v>1.49</v>
+        <v>2.05</v>
       </c>
       <c r="S22" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="T22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD22" t="n">
         <v>2.25</v>
       </c>
-      <c r="U22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="V22" t="n">
+      <c r="AE22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BE22" t="n">
         <v>1.36</v>
       </c>
-      <c r="W22" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>1.65</v>
-      </c>
       <c r="BF22" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BH22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BI22" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4941,130 +4941,130 @@
         <v>1.08</v>
       </c>
       <c r="Q23" t="n">
-        <v>11.7</v>
+        <v>9.5</v>
       </c>
       <c r="R23" t="n">
         <v>16</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>10.15</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -1592,16 +1592,16 @@
         <v>1.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="R6" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="S6" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="T6" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="U6" t="n">
         <v>4.68</v>
@@ -1616,7 +1616,7 @@
         <v>2.33</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="Z6" t="n">
         <v>5.2</v>
@@ -1631,7 +1631,7 @@
         <v>1.14</v>
       </c>
       <c r="AD6" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AE6" t="n">
         <v>1.59</v>
@@ -1640,28 +1640,28 @@
         <v>2.21</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AI6" t="n">
         <v>4.3</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1706,13 +1706,13 @@
         <v>1.14</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="BD6" t="n">
         <v>4.9</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="BF6" t="n">
         <v>1.25</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.7</v>
+        <v>1.89</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.12</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
-        <v>2.45</v>
+        <v>3.8</v>
       </c>
       <c r="S7" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF8" t="n">
         <v>1.89</v>
       </c>
-      <c r="Q8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2100,13 +2100,13 @@
         <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD8" t="n">
         <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BF8" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,22 +2377,22 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="S10" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -2401,10 +2401,10 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -2416,40 +2416,40 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2494,13 +2494,13 @@
         <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
         <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.75</v>
+        <v>2.6</v>
       </c>
       <c r="Q11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD11" t="n">
         <v>3.6</v>
       </c>
-      <c r="R11" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>6.13</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.74</v>
+        <v>1.41</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="R16" t="n">
-        <v>4.04</v>
+        <v>6.13</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q17" t="n">
         <v>3.4</v>
       </c>
       <c r="R17" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="S17" t="n">
         <v>2.52</v>
@@ -3780,10 +3780,10 @@
         <v>2.7</v>
       </c>
       <c r="X17" t="n">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="Z17" t="n">
         <v>5.4</v>
@@ -3801,7 +3801,7 @@
         <v>3.78</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AF17" t="n">
         <v>2.07</v>
@@ -3822,13 +3822,13 @@
         <v>1.59</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,7 +3870,7 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="BC17" t="n">
         <v>1.83</v>
@@ -3882,7 +3882,7 @@
         <v>1.87</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Y18" t="n">
         <v>1.93</v>
       </c>
-      <c r="Q18" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="R18" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="U18" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.54</v>
-      </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="AD18" t="n">
-        <v>4.25</v>
+        <v>7.7</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.58</v>
+        <v>1.27</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.18</v>
+        <v>3.44</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.48</v>
+        <v>1.73</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.47</v>
+        <v>1.93</v>
       </c>
       <c r="AI18" t="n">
-        <v>4.25</v>
+        <v>2.6</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.17</v>
+        <v>1.48</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.23</v>
+        <v>2.7</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.96</v>
+        <v>1.12</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4034,52 +4034,52 @@
         <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
         <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.82</v>
+        <v>1.45</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.86</v>
+        <v>2.56</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>6.15</v>
+        <v>1.93</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.4</v>
+        <v>3.68</v>
       </c>
       <c r="R19" t="n">
-        <v>1.41</v>
+        <v>3.78</v>
       </c>
       <c r="S19" t="n">
-        <v>5.55</v>
+        <v>2.2</v>
       </c>
       <c r="T19" t="n">
-        <v>2.88</v>
+        <v>2.43</v>
       </c>
       <c r="U19" t="n">
-        <v>1.78</v>
+        <v>4.25</v>
       </c>
       <c r="V19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
         <v>1.82</v>
       </c>
-      <c r="Y19" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>1.45</v>
-      </c>
       <c r="BD19" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.56</v>
+        <v>1.86</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,139 +4347,139 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>7.75</v>
+        <v>3.87</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="R20" t="n">
-        <v>1.49</v>
+        <v>2.05</v>
       </c>
       <c r="S20" t="n">
-        <v>8.9</v>
+        <v>5.03</v>
       </c>
       <c r="T20" t="n">
-        <v>1.98</v>
+        <v>1.81</v>
       </c>
       <c r="U20" t="n">
-        <v>2.2</v>
+        <v>2.83</v>
       </c>
       <c r="V20" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="X20" t="n">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z20" t="n">
-        <v>8.9</v>
+        <v>8.1</v>
       </c>
       <c r="AA20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ20" t="n">
         <v>1.03</v>
       </c>
-      <c r="AB20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AE20" t="n">
+      <c r="AK20" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BC20" t="n">
         <v>2.7</v>
       </c>
-      <c r="AF20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BC20" t="n">
+      <c r="BD20" t="n">
         <v>2.82</v>
       </c>
-      <c r="BD20" t="n">
-        <v>2.62</v>
-      </c>
       <c r="BE20" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="BH20" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="BI20" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4547,16 +4547,16 @@
         <v>6</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.9</v>
+        <v>3.98</v>
       </c>
       <c r="R21" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S21" t="n">
-        <v>5.8</v>
+        <v>6.3</v>
       </c>
       <c r="T21" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="U21" t="n">
         <v>1.95</v>
@@ -4565,55 +4565,55 @@
         <v>1.36</v>
       </c>
       <c r="W21" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="X21" t="n">
-        <v>2.69</v>
+        <v>2.6</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="Z21" t="n">
         <v>7</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="AE21" t="n">
         <v>1.97</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AI21" t="n">
-        <v>5.8</v>
+        <v>6.25</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AM21" t="n">
-        <v>2.41</v>
+        <v>2.17</v>
       </c>
       <c r="AN21" t="n">
         <v>1.1</v>
@@ -4658,19 +4658,19 @@
         <v>1.33</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.6</v>
+        <v>3.78</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,139 +4741,139 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.87</v>
+        <v>7.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="R22" t="n">
-        <v>2.05</v>
+        <v>1.49</v>
       </c>
       <c r="S22" t="n">
-        <v>4.2</v>
+        <v>8.9</v>
       </c>
       <c r="T22" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="U22" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="V22" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="W22" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="X22" t="n">
         <v>3.7</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z22" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="AA22" t="n">
         <v>1.03</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AE22" t="n">
         <v>2.7</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AG22" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AI22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.27</v>
+        <v>1.02</v>
       </c>
       <c r="AO22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BB22" t="n">
         <v>1.4</v>
       </c>
-      <c r="AP22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.37</v>
-      </c>
       <c r="BC22" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BD22" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BF22" t="n">
         <v>1.08</v>
       </c>
       <c r="BG22" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH22" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="BI22" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4938,37 +4938,37 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q23" t="n">
-        <v>9.5</v>
+        <v>11.1</v>
       </c>
       <c r="R23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S23" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T23" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="U23" t="n">
-        <v>10.15</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>1.06</v>
       </c>
       <c r="W23" t="n">
-        <v>6.25</v>
+        <v>6.15</v>
       </c>
       <c r="X23" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AA23" t="n">
         <v>1.3</v>
@@ -4980,37 +4980,37 @@
         <v>1.02</v>
       </c>
       <c r="AD23" t="n">
-        <v>8.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AF23" t="n">
-        <v>4.1</v>
+        <v>3.98</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AM23" t="n">
         <v>1.01</v>
       </c>
       <c r="AN23" t="n">
-        <v>6.6</v>
+        <v>6.25</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5055,7 +5055,7 @@
         <v>1.04</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="BD23" t="n">
         <v>8.4</v>
@@ -5064,7 +5064,7 @@
         <v>2.7</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="S24" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="V24" t="n">
         <v>1.36</v>
       </c>
-      <c r="Q24" t="n">
-        <v>5</v>
-      </c>
-      <c r="R24" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U24" t="n">
-        <v>6</v>
-      </c>
-      <c r="V24" t="n">
+      <c r="W24" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC24" t="n">
         <v>1.25</v>
       </c>
-      <c r="W24" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AD24" t="n">
-        <v>4.6</v>
+        <v>3.24</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.51</v>
+        <v>1.93</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.27</v>
+        <v>1.86</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.43</v>
+        <v>3.31</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="AI24" t="n">
-        <v>4.05</v>
+        <v>5.8</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.06</v>
+        <v>1.26</v>
       </c>
       <c r="AN24" t="n">
-        <v>2.8</v>
+        <v>1.15</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.3</v>
+        <v>1.56</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.5</v>
+        <v>1.92</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.81</v>
+        <v>2.45</v>
       </c>
       <c r="AT24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AV24" t="n">
         <v>2.23</v>
       </c>
-      <c r="AU24" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AW24" t="n">
-        <v>2.35</v>
+        <v>1.76</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.87</v>
+        <v>1.47</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="AZ24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BB24" t="n">
         <v>1.22</v>
       </c>
-      <c r="BA24" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.13</v>
-      </c>
       <c r="BC24" t="n">
-        <v>1.79</v>
+        <v>2.13</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.85</v>
+        <v>3.66</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.96</v>
+        <v>1.67</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.74</v>
+        <v>1.31</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.65</v>
+        <v>5.07</v>
       </c>
       <c r="R25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="U25" t="n">
+        <v>6</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W25" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AX25" t="n">
         <v>1.87</v>
       </c>
-      <c r="S25" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W25" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC25" t="n">
+      <c r="AY25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BF25" t="n">
         <v>1.26</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>1.15</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5532,31 +5532,31 @@
         <v>1.58</v>
       </c>
       <c r="Q26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R26" t="n">
         <v>4.5</v>
       </c>
-      <c r="R26" t="n">
-        <v>4.45</v>
-      </c>
       <c r="S26" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="T26" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U26" t="n">
-        <v>3.78</v>
+        <v>4.5</v>
       </c>
       <c r="V26" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="W26" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="X26" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="Z26" t="n">
         <v>3.36</v>
@@ -5565,13 +5565,13 @@
         <v>1.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC26" t="n">
         <v>1.03</v>
       </c>
       <c r="AD26" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="AE26" t="n">
         <v>1.28</v>
@@ -5583,10 +5583,10 @@
         <v>1.78</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="AI26" t="n">
-        <v>2.9</v>
+        <v>2.46</v>
       </c>
       <c r="AJ26" t="n">
         <v>1.48</v>
@@ -5595,13 +5595,13 @@
         <v>1.36</v>
       </c>
       <c r="AL26" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AN26" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>1.18</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AS26" t="n">
         <v>1.9</v>
@@ -5625,10 +5625,10 @@
         <v>4.1</v>
       </c>
       <c r="AV26" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AW26" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AX26" t="n">
         <v>1.78</v>
@@ -5646,16 +5646,16 @@
         <v>1.07</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="BD26" t="n">
         <v>8.1</v>
       </c>
       <c r="BE26" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5726,34 +5726,34 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="R27" t="n">
-        <v>7.3</v>
+        <v>7.25</v>
       </c>
       <c r="S27" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="T27" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="U27" t="n">
-        <v>6.6</v>
+        <v>5.32</v>
       </c>
       <c r="V27" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W27" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="X27" t="n">
-        <v>2.55</v>
+        <v>2.64</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="Z27" t="n">
         <v>6</v>
@@ -5762,25 +5762,25 @@
         <v>1.09</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AC27" t="n">
         <v>1.22</v>
       </c>
       <c r="AD27" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AG27" t="n">
         <v>2.84</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AI27" t="n">
         <v>5.25</v>
@@ -5792,10 +5792,10 @@
         <v>2.02</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AN27" t="n">
         <v>2.85</v>
@@ -5804,52 +5804,52 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AS27" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AT27" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="AU27" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AV27" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="BA27" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="BF27" t="n">
         <v>1.2</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G31" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R7" t="n">
-        <v>3.8</v>
+        <v>4.14</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1992,13 +1992,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -2022,40 +2022,40 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2100,13 +2100,13 @@
         <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
         <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.75</v>
       </c>
-      <c r="Q10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R10" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2494,13 +2494,13 @@
         <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD10" t="n">
         <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BF10" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>6.13</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>6.15</v>
+        <v>1.93</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.4</v>
+        <v>3.68</v>
       </c>
       <c r="R18" t="n">
-        <v>1.41</v>
+        <v>3.78</v>
       </c>
       <c r="S18" t="n">
-        <v>5.55</v>
+        <v>2.2</v>
       </c>
       <c r="T18" t="n">
-        <v>2.88</v>
+        <v>2.43</v>
       </c>
       <c r="U18" t="n">
-        <v>1.78</v>
+        <v>4.25</v>
       </c>
       <c r="V18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
         <v>1.82</v>
       </c>
-      <c r="Y18" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>1.45</v>
-      </c>
       <c r="BD18" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.56</v>
+        <v>1.86</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Y19" t="n">
         <v>1.93</v>
       </c>
-      <c r="Q19" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="R19" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="U19" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.54</v>
-      </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="AD19" t="n">
-        <v>4.25</v>
+        <v>7.7</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.58</v>
+        <v>1.27</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.18</v>
+        <v>3.44</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.48</v>
+        <v>1.73</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.47</v>
+        <v>1.93</v>
       </c>
       <c r="AI19" t="n">
-        <v>4.25</v>
+        <v>2.6</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.17</v>
+        <v>1.48</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.23</v>
+        <v>2.7</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.96</v>
+        <v>1.12</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4231,52 +4231,52 @@
         <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
         <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.82</v>
+        <v>1.45</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.86</v>
+        <v>2.56</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -813,16 +813,16 @@
         <v>3.2</v>
       </c>
       <c r="T2" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="U2" t="n">
         <v>3.2</v>
       </c>
       <c r="V2" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W2" t="n">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="X2" t="n">
         <v>2.7</v>
@@ -831,7 +831,7 @@
         <v>1.42</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.95</v>
+        <v>7</v>
       </c>
       <c r="AA2" t="n">
         <v>1.08</v>
@@ -852,19 +852,19 @@
         <v>1.82</v>
       </c>
       <c r="AG2" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AI2" t="n">
-        <v>6.15</v>
+        <v>6.2</v>
       </c>
       <c r="AJ2" t="n">
         <v>1.11</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AL2" t="n">
         <v>2</v>
@@ -915,19 +915,19 @@
         <v>2.08</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1.75</v>
       </c>
-      <c r="Q7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R7" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1903,13 +1903,13 @@
         <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD7" t="n">
         <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BF7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2386,13 +2386,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -2401,10 +2401,10 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -2416,40 +2416,40 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2494,13 +2494,13 @@
         <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
         <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>6.13</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,139 +4347,139 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.87</v>
+        <v>7.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="R20" t="n">
-        <v>2.05</v>
+        <v>1.49</v>
       </c>
       <c r="S20" t="n">
-        <v>5.03</v>
+        <v>8.9</v>
       </c>
       <c r="T20" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AV20" t="n">
         <v>1.81</v>
       </c>
-      <c r="U20" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W20" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="X20" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>5.37</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AO20" t="n">
+      <c r="AW20" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BB20" t="n">
         <v>1.4</v>
       </c>
-      <c r="AP20" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>3</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BB20" t="n">
+      <c r="BC20" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BE20" t="n">
         <v>1.35</v>
       </c>
-      <c r="BC20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>1.38</v>
-      </c>
       <c r="BF20" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH20" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="BI20" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,139 +4544,139 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>6</v>
+        <v>3.87</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.98</v>
+        <v>2.8</v>
       </c>
       <c r="R21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="X21" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AP21" t="n">
         <v>1.48</v>
       </c>
-      <c r="S21" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W21" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK21" t="n">
+      <c r="AQ21" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BH21" t="n">
         <v>1.9</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,139 +4741,139 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>7.75</v>
+        <v>6</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.4</v>
+        <v>3.98</v>
       </c>
       <c r="R22" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S22" t="n">
-        <v>8.9</v>
+        <v>6.3</v>
       </c>
       <c r="T22" t="n">
-        <v>1.98</v>
+        <v>2.37</v>
       </c>
       <c r="U22" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="V22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ22" t="n">
         <v>1.65</v>
       </c>
-      <c r="W22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="X22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AR22" t="n">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="AS22" t="n">
-        <v>3.15</v>
+        <v>2.63</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AU22" t="n">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.81</v>
+        <v>2.08</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ22" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.82</v>
+        <v>2.08</v>
       </c>
       <c r="BD22" t="n">
-        <v>2.62</v>
+        <v>3.78</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.35</v>
+        <v>1.69</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
         <v>46127.60416666666</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="R26" t="n">
-        <v>4.5</v>
+        <v>7.25</v>
       </c>
       <c r="S26" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W26" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK26" t="n">
         <v>2.02</v>
       </c>
-      <c r="T26" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AE26" t="n">
+      <c r="AL26" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
         <v>1.28</v>
       </c>
-      <c r="AF26" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AG26" t="n">
+      <c r="AQ26" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR26" t="n">
         <v>1.78</v>
       </c>
-      <c r="AH26" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AM26" t="n">
+      <c r="AS26" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BB26" t="n">
         <v>1.19</v>
       </c>
-      <c r="AN26" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AU26" t="n">
+      <c r="BC26" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BD26" t="n">
         <v>4.1</v>
       </c>
-      <c r="AV26" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>8.1</v>
-      </c>
       <c r="BE26" t="n">
-        <v>2.57</v>
+        <v>1.72</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.52</v>
+        <v>1.2</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="R27" t="n">
-        <v>7.25</v>
+        <v>4.5</v>
       </c>
       <c r="S27" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="T27" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="U27" t="n">
-        <v>5.32</v>
+        <v>4.5</v>
       </c>
       <c r="V27" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="W27" t="n">
-        <v>3.18</v>
+        <v>5.5</v>
       </c>
       <c r="X27" t="n">
-        <v>2.64</v>
+        <v>1.83</v>
       </c>
       <c r="Y27" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AY27" t="n">
         <v>1.49</v>
       </c>
-      <c r="Z27" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AZ27" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.98</v>
+        <v>1.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.1</v>
+        <v>8.1</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.72</v>
+        <v>2.57</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.2</v>
+        <v>1.52</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -810,7 +810,7 @@
         <v>2.6</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T2" t="n">
         <v>2.23</v>
@@ -828,10 +828,10 @@
         <v>2.7</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="Z2" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="AA2" t="n">
         <v>1.08</v>
@@ -843,28 +843,28 @@
         <v>1.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AG2" t="n">
         <v>3.24</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AI2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AL2" t="n">
         <v>2</v>
@@ -915,19 +915,19 @@
         <v>2.08</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.6</v>
+        <v>3.66</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1795,13 +1795,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1810,10 +1810,10 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -1825,40 +1825,40 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1903,13 +1903,13 @@
         <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
         <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
         <v>0</v>
@@ -1992,13 +1992,13 @@
         <v>4.14</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -2022,40 +2022,40 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2100,13 +2100,13 @@
         <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BD8" t="n">
         <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BF8" t="n">
         <v>0</v>
@@ -2189,19 +2189,19 @@
         <v>3.8</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -2219,40 +2219,40 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2297,13 +2297,13 @@
         <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BD9" t="n">
         <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BF9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2386,13 +2386,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -2401,10 +2401,10 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -2416,40 +2416,40 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2494,13 +2494,13 @@
         <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD10" t="n">
         <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BF10" t="n">
         <v>0</v>
@@ -2977,13 +2977,13 @@
         <v>4.04</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -2992,10 +2992,10 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -3007,40 +3007,40 @@
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3085,13 +3085,13 @@
         <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD13" t="n">
         <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF13" t="n">
         <v>0</v>
@@ -3174,13 +3174,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -3189,10 +3189,10 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -3204,40 +3204,40 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3282,13 +3282,13 @@
         <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BD14" t="n">
         <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BF14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>6.13</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3598,40 +3598,40 @@
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W18" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AH18" t="n">
         <v>1.93</v>
       </c>
-      <c r="Q18" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="R18" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="U18" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AI18" t="n">
-        <v>4.25</v>
+        <v>2.45</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.17</v>
+        <v>1.44</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.96</v>
+        <v>1.1</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4034,52 +4034,52 @@
         <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
         <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.82</v>
+        <v>1.44</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.86</v>
+        <v>2.59</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>6.15</v>
+        <v>1.83</v>
       </c>
       <c r="Q19" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="R19" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W19" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z19" t="n">
         <v>5.4</v>
       </c>
-      <c r="R19" t="n">
+      <c r="AA19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.41</v>
       </c>
-      <c r="S19" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V19" t="n">
+      <c r="AI19" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AJ19" t="n">
         <v>1.13</v>
       </c>
-      <c r="W19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AK19" t="n">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.7</v>
+        <v>2.19</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.12</v>
+        <v>1.96</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4231,52 +4231,52 @@
         <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AU19" t="n">
         <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.45</v>
+        <v>1.88</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.75</v>
+        <v>4.33</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.56</v>
+        <v>1.86</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.51</v>
+        <v>1.23</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,139 +4544,139 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.87</v>
+        <v>6</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.8</v>
+        <v>3.98</v>
       </c>
       <c r="R21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S21" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AR21" t="n">
         <v>2.05</v>
       </c>
-      <c r="S21" t="n">
-        <v>5.03</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W21" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="X21" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>5.37</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>11</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AM21" t="n">
+      <c r="AS21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BA21" t="n">
         <v>1.33</v>
       </c>
-      <c r="AN21" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>3</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>1.66</v>
-      </c>
       <c r="BB21" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.7</v>
+        <v>2.08</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.82</v>
+        <v>3.78</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.38</v>
+        <v>1.69</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BH21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,139 +4741,139 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>6</v>
+        <v>3.87</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.98</v>
+        <v>2.8</v>
       </c>
       <c r="R22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AP22" t="n">
         <v>1.48</v>
       </c>
-      <c r="S22" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W22" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK22" t="n">
+      <c r="AQ22" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BH22" t="n">
         <v>1.9</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH22" t="n">
-        <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
         <v>46127.60416666666</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.7</v>
+        <v>1.33</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.87</v>
+        <v>7.5</v>
       </c>
       <c r="S24" t="n">
-        <v>4.42</v>
+        <v>1.84</v>
       </c>
       <c r="T24" t="n">
-        <v>2.19</v>
+        <v>2.45</v>
       </c>
       <c r="U24" t="n">
-        <v>2.43</v>
+        <v>6</v>
       </c>
       <c r="V24" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="W24" t="n">
-        <v>2.99</v>
+        <v>3.42</v>
       </c>
       <c r="X24" t="n">
-        <v>2.85</v>
+        <v>2.2</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="Z24" t="n">
-        <v>6.1</v>
+        <v>5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.24</v>
+        <v>4.1</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.93</v>
+        <v>1.57</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.86</v>
+        <v>2.35</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.31</v>
+        <v>2.46</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AI24" t="n">
-        <v>5.8</v>
+        <v>4.1</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AM24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BF24" t="n">
         <v>1.26</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>1.15</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.31</v>
+        <v>3.69</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.07</v>
+        <v>3.68</v>
       </c>
       <c r="R25" t="n">
-        <v>7.8</v>
+        <v>1.87</v>
       </c>
       <c r="S25" t="n">
-        <v>1.8</v>
+        <v>4.37</v>
       </c>
       <c r="T25" t="n">
-        <v>2.54</v>
+        <v>2.2</v>
       </c>
       <c r="U25" t="n">
-        <v>6</v>
+        <v>2.49</v>
       </c>
       <c r="V25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN25" t="n">
         <v>1.25</v>
       </c>
-      <c r="W25" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AJ25" t="n">
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BB25" t="n">
         <v>1.21</v>
       </c>
-      <c r="AK25" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.13</v>
-      </c>
       <c r="BC25" t="n">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.85</v>
+        <v>3.75</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.96</v>
+        <v>1.69</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="R26" t="n">
-        <v>7.25</v>
+        <v>4.5</v>
       </c>
       <c r="S26" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="T26" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="U26" t="n">
-        <v>5.32</v>
+        <v>4.5</v>
       </c>
       <c r="V26" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="W26" t="n">
-        <v>3.18</v>
+        <v>5.5</v>
       </c>
       <c r="X26" t="n">
-        <v>2.64</v>
+        <v>1.83</v>
       </c>
       <c r="Y26" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AY26" t="n">
         <v>1.49</v>
       </c>
-      <c r="Z26" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AZ26" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.98</v>
+        <v>1.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.1</v>
+        <v>8.1</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.72</v>
+        <v>2.57</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.2</v>
+        <v>1.52</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="R27" t="n">
-        <v>4.5</v>
+        <v>7.25</v>
       </c>
       <c r="S27" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W27" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="X27" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK27" t="n">
         <v>2.02</v>
       </c>
-      <c r="T27" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U27" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W27" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AE27" t="n">
+      <c r="AL27" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
         <v>1.28</v>
       </c>
-      <c r="AF27" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AG27" t="n">
+      <c r="AQ27" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR27" t="n">
         <v>1.78</v>
       </c>
-      <c r="AH27" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AM27" t="n">
+      <c r="AS27" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BB27" t="n">
         <v>1.19</v>
       </c>
-      <c r="AN27" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AU27" t="n">
+      <c r="BC27" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BD27" t="n">
         <v>4.1</v>
       </c>
-      <c r="AV27" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>8.1</v>
-      </c>
       <c r="BE27" t="n">
-        <v>2.57</v>
+        <v>1.72</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.52</v>
+        <v>1.2</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -1589,22 +1589,22 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="R6" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="S6" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="T6" t="n">
-        <v>2.19</v>
+        <v>2.46</v>
       </c>
       <c r="U6" t="n">
-        <v>4.68</v>
+        <v>3.9</v>
       </c>
       <c r="V6" t="n">
         <v>1.28</v>
@@ -1628,22 +1628,22 @@
         <v>1.03</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>4.45</v>
+        <v>4.52</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="AI6" t="n">
         <v>4.3</v>
@@ -1652,13 +1652,13 @@
         <v>1.15</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AN6" t="n">
         <v>1.89</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1795,13 +1795,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1810,10 +1810,10 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -1825,40 +1825,40 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1903,13 +1903,13 @@
         <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD7" t="n">
         <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BF7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,34 +1983,34 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>4.14</v>
+        <v>3.8</v>
       </c>
       <c r="S8" t="n">
-        <v>2.43</v>
+        <v>2.85</v>
       </c>
       <c r="T8" t="n">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="U8" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="X8" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -2022,40 +2022,40 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AI8" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2100,13 +2100,13 @@
         <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="BD8" t="n">
         <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="BF8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,28 +2180,28 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -2219,40 +2219,40 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2297,13 +2297,13 @@
         <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
         <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,22 +2377,22 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="S10" t="n">
-        <v>4.25</v>
+        <v>2.43</v>
       </c>
       <c r="T10" t="n">
         <v>2.28</v>
       </c>
       <c r="U10" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -2401,10 +2401,10 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -2416,41 +2416,41 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AI10" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AJ10" t="n">
         <v>1.11</v>
       </c>
       <c r="AK10" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN10" t="n">
         <v>1.68</v>
       </c>
-      <c r="AL10" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
@@ -2494,13 +2494,13 @@
         <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="BD10" t="n">
         <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="BF10" t="n">
         <v>0</v>
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R11" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S11" t="n">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
       <c r="T11" t="n">
-        <v>2.23</v>
+        <v>2.06</v>
       </c>
       <c r="U11" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="V11" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W11" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="X11" t="n">
-        <v>2.66</v>
+        <v>2.95</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Z11" t="n">
         <v>7</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AB11" t="n">
         <v>1.02</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AI11" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AJ11" t="n">
         <v>1.08</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>2.12</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.28</v>
+        <v>2.11</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2780,13 +2780,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -2795,10 +2795,10 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
@@ -2810,40 +2810,40 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2888,13 +2888,13 @@
         <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BD12" t="n">
         <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BF12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,22 +2968,22 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.74</v>
+        <v>1.41</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="R13" t="n">
-        <v>4.04</v>
+        <v>6.13</v>
       </c>
       <c r="S13" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -2992,10 +2992,10 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -3007,40 +3007,40 @@
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AD13" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.48</v>
+        <v>1.76</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.38</v>
+        <v>1.88</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.18</v>
+        <v>2.88</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="AI13" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.38</v>
+        <v>1.81</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3085,13 +3085,13 @@
         <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
         <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3174,13 +3174,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -3189,10 +3189,10 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -3204,40 +3204,40 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3282,13 +3282,13 @@
         <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
         <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,22 +3559,22 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.41</v>
+        <v>1.74</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="R16" t="n">
-        <v>6.13</v>
+        <v>4.04</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -3583,10 +3583,10 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -3598,40 +3598,40 @@
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.76</v>
+        <v>1.48</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.88</v>
+        <v>2.38</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.88</v>
+        <v>2.18</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="AI16" t="n">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.87</v>
+        <v>1.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.81</v>
+        <v>2.38</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3676,13 +3676,13 @@
         <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD16" t="n">
         <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF16" t="n">
         <v>0</v>
@@ -3756,22 +3756,22 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="Q17" t="n">
         <v>3.4</v>
       </c>
       <c r="R17" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="S17" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="T17" t="n">
         <v>1.99</v>
       </c>
       <c r="U17" t="n">
-        <v>4.86</v>
+        <v>3.95</v>
       </c>
       <c r="V17" t="n">
         <v>1.38</v>
@@ -3780,16 +3780,16 @@
         <v>2.7</v>
       </c>
       <c r="X17" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AB17" t="n">
         <v>1.01</v>
@@ -3801,34 +3801,34 @@
         <v>3.78</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AH17" t="n">
         <v>1.42</v>
       </c>
       <c r="AI17" t="n">
-        <v>4.5</v>
+        <v>4.88</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AK17" t="n">
         <v>1.59</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3882,7 +3882,7 @@
         <v>1.87</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,139 +4347,139 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>7.75</v>
+        <v>6</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="R20" t="n">
         <v>1.49</v>
       </c>
       <c r="S20" t="n">
-        <v>8.9</v>
+        <v>5.96</v>
       </c>
       <c r="T20" t="n">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="U20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BC20" t="n">
         <v>2.2</v>
       </c>
-      <c r="V20" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="X20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>2.82</v>
-      </c>
       <c r="BD20" t="n">
-        <v>2.62</v>
+        <v>3.68</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.35</v>
+        <v>1.68</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,139 +4544,139 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>6</v>
+        <v>3.87</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.98</v>
+        <v>2.8</v>
       </c>
       <c r="R21" t="n">
-        <v>1.48</v>
+        <v>2</v>
       </c>
       <c r="S21" t="n">
-        <v>6.3</v>
+        <v>4.2</v>
       </c>
       <c r="T21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W21" t="n">
         <v>2.37</v>
       </c>
-      <c r="U21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="V21" t="n">
+      <c r="X21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BE21" t="n">
         <v>1.36</v>
       </c>
-      <c r="W21" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ21" t="n">
+      <c r="BF21" t="n">
         <v>1.08</v>
       </c>
-      <c r="AK21" t="n">
+      <c r="BG21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BH21" t="n">
         <v>1.9</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,139 +4741,139 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.87</v>
+        <v>7.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="R22" t="n">
-        <v>2.05</v>
+        <v>1.49</v>
       </c>
       <c r="S22" t="n">
-        <v>5.03</v>
+        <v>8.9</v>
       </c>
       <c r="T22" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AV22" t="n">
         <v>1.81</v>
       </c>
-      <c r="U22" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W22" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="X22" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>5.37</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AO22" t="n">
+      <c r="AW22" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BB22" t="n">
         <v>1.4</v>
       </c>
-      <c r="AP22" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>3</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BB22" t="n">
+      <c r="BC22" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BE22" t="n">
         <v>1.35</v>
       </c>
-      <c r="BC22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>1.38</v>
-      </c>
       <c r="BF22" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="BG22" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH22" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="BI22" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4947,13 +4947,13 @@
         <v>15</v>
       </c>
       <c r="S23" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="T23" t="n">
-        <v>3.9</v>
+        <v>3.64</v>
       </c>
       <c r="U23" t="n">
-        <v>8.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="V23" t="n">
         <v>1.06</v>
@@ -4962,19 +4962,19 @@
         <v>6.15</v>
       </c>
       <c r="X23" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="Y23" t="n">
         <v>2.08</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AB23" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC23" t="n">
         <v>1.02</v>
@@ -4983,19 +4983,19 @@
         <v>9.300000000000001</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AF23" t="n">
-        <v>3.98</v>
+        <v>3.96</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="AJ23" t="n">
         <v>1.53</v>
@@ -5004,13 +5004,13 @@
         <v>1.67</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AM23" t="n">
         <v>1.01</v>
       </c>
       <c r="AN23" t="n">
-        <v>6.25</v>
+        <v>6.2</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5052,7 +5052,7 @@
         <v>8</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="BC23" t="n">
         <v>1.42</v>
@@ -5061,7 +5061,7 @@
         <v>8.4</v>
       </c>
       <c r="BE23" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="BF23" t="n">
         <v>1.5</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="R26" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="S26" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="T26" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="U26" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="V26" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="W26" t="n">
-        <v>5.5</v>
+        <v>3.18</v>
       </c>
       <c r="X26" t="n">
-        <v>1.83</v>
+        <v>2.45</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.03</v>
+        <v>1.48</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.36</v>
+        <v>6</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="AB26" t="n">
         <v>1</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="AD26" t="n">
-        <v>7.5</v>
+        <v>3.74</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.28</v>
+        <v>1.86</v>
       </c>
       <c r="AF26" t="n">
-        <v>3.75</v>
+        <v>2.06</v>
       </c>
       <c r="AG26" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE26" t="n">
         <v>1.78</v>
       </c>
-      <c r="AH26" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>2.57</v>
-      </c>
       <c r="BF26" t="n">
-        <v>1.52</v>
+        <v>1.2</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="R27" t="n">
-        <v>7.25</v>
+        <v>4.7</v>
       </c>
       <c r="S27" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="T27" t="n">
-        <v>2.3</v>
+        <v>2.85</v>
       </c>
       <c r="U27" t="n">
-        <v>5.32</v>
+        <v>3.78</v>
       </c>
       <c r="V27" t="n">
-        <v>1.35</v>
+        <v>1.13</v>
       </c>
       <c r="W27" t="n">
-        <v>3.18</v>
+        <v>5.5</v>
       </c>
       <c r="X27" t="n">
-        <v>2.64</v>
+        <v>1.83</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.49</v>
+        <v>2.04</v>
       </c>
       <c r="Z27" t="n">
-        <v>6</v>
+        <v>3.36</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.85</v>
+        <v>8</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.76</v>
+        <v>1.28</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.05</v>
+        <v>3.75</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.84</v>
+        <v>1.72</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.36</v>
+        <v>2.1</v>
       </c>
       <c r="AI27" t="n">
-        <v>5.25</v>
+        <v>2.6</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.09</v>
+        <v>1.47</v>
       </c>
       <c r="AK27" t="n">
-        <v>2.02</v>
+        <v>1.34</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.77</v>
+        <v>3.2</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AN27" t="n">
-        <v>2.85</v>
+        <v>2.48</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AS27" t="n">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="AT27" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="AU27" t="n">
-        <v>3.3</v>
+        <v>3.72</v>
       </c>
       <c r="AV27" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AY27" t="n">
         <v>1.33</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.38</v>
+        <v>1.69</v>
       </c>
       <c r="BA27" t="n">
-        <v>3.45</v>
+        <v>2.62</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.98</v>
+        <v>1.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.1</v>
+        <v>6.5</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.72</v>
+        <v>2.55</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -813,7 +813,7 @@
         <v>3.25</v>
       </c>
       <c r="T2" t="n">
-        <v>2.23</v>
+        <v>2.03</v>
       </c>
       <c r="U2" t="n">
         <v>3.2</v>
@@ -822,7 +822,7 @@
         <v>1.41</v>
       </c>
       <c r="W2" t="n">
-        <v>2.9</v>
+        <v>2.69</v>
       </c>
       <c r="X2" t="n">
         <v>2.7</v>
@@ -831,7 +831,7 @@
         <v>1.38</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="AA2" t="n">
         <v>1.08</v>
@@ -849,7 +849,7 @@
         <v>1.95</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AG2" t="n">
         <v>3.24</v>
@@ -1628,7 +1628,7 @@
         <v>1.03</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AD6" t="n">
         <v>4.52</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1795,13 +1795,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1810,10 +1810,10 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -1825,40 +1825,40 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1903,13 +1903,13 @@
         <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
         <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
         <v>2.02</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AN8" t="n">
         <v>1.46</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2189,13 +2189,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -2204,10 +2204,10 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
@@ -2219,40 +2219,40 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2297,13 +2297,13 @@
         <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD9" t="n">
         <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BF9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="Q10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BD10" t="n">
         <v>3.6</v>
       </c>
-      <c r="R10" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>0</v>
-      </c>
       <c r="BE10" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="R11" t="n">
-        <v>2.4</v>
+        <v>4.14</v>
       </c>
       <c r="S11" t="n">
-        <v>3.38</v>
+        <v>2.43</v>
       </c>
       <c r="T11" t="n">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="U11" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="V11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.95</v>
+        <v>2.43</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Z11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AD11" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AG11" t="n">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AI11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.47</v>
+        <v>1.2</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.11</v>
+        <v>1.93</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,22 +2771,22 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S12" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="T12" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="U12" t="n">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -2795,10 +2795,10 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.48</v>
+        <v>2.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
@@ -2810,40 +2810,40 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.77</v>
+        <v>1.48</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.88</v>
+        <v>2.38</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.9</v>
+        <v>2.18</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.32</v>
+        <v>1.56</v>
       </c>
       <c r="AI12" t="n">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.84</v>
+        <v>1.5</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="AM12" t="n">
         <v>1.18</v>
       </c>
       <c r="AN12" t="n">
-        <v>2.12</v>
+        <v>1.91</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2888,13 +2888,13 @@
         <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="BD12" t="n">
         <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="BF12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,34 +2968,34 @@
         </is>
       </c>
       <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Y13" t="n">
         <v>1.41</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R13" t="n">
-        <v>6.13</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -3013,16 +3013,16 @@
         <v>3.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AF13" t="n">
         <v>1.88</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AI13" t="n">
         <v>5.1</v>
@@ -3031,16 +3031,16 @@
         <v>1.11</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AN13" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3085,13 +3085,13 @@
         <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BD13" t="n">
         <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BF13" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3401,40 +3401,40 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,22 +3559,22 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -3583,10 +3583,10 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -3598,40 +3598,40 @@
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3676,13 +3676,13 @@
         <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
         <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
         <v>0</v>
@@ -3756,16 +3756,16 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R17" t="n">
         <v>3.5</v>
       </c>
       <c r="S17" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T17" t="n">
         <v>1.99</v>
@@ -3798,7 +3798,7 @@
         <v>1.19</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.78</v>
+        <v>4.22</v>
       </c>
       <c r="AE17" t="n">
         <v>1.7</v>
@@ -3819,7 +3819,7 @@
         <v>1.14</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AL17" t="n">
         <v>2.25</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,139 +4544,139 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.87</v>
+        <v>7.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>2</v>
+        <v>1.49</v>
       </c>
       <c r="S21" t="n">
-        <v>4.2</v>
+        <v>8.9</v>
       </c>
       <c r="T21" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="U21" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="V21" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="W21" t="n">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="X21" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.1</v>
+        <v>8.9</v>
       </c>
       <c r="AA21" t="n">
         <v>1.03</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AE21" t="n">
         <v>2.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG21" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AI21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.84</v>
+        <v>2.38</v>
       </c>
       <c r="AS21" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AT21" t="n">
-        <v>4.64</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>2.47</v>
+        <v>2.33</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2.43</v>
+        <v>3.7</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.81</v>
+        <v>1.3</v>
       </c>
       <c r="BB21" t="n">
         <v>1.4</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BF21" t="n">
         <v>1.08</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH21" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,139 +4741,139 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>7.75</v>
+        <v>3.87</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="R22" t="n">
-        <v>1.49</v>
+        <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>8.9</v>
+        <v>4.2</v>
       </c>
       <c r="T22" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="U22" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="V22" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="W22" t="n">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="X22" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z22" t="n">
-        <v>8.9</v>
+        <v>8.1</v>
       </c>
       <c r="AA22" t="n">
         <v>1.03</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AE22" t="n">
         <v>2.7</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG22" t="n">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AI22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="AL22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM22" t="n">
         <v>1.35</v>
       </c>
-      <c r="AM22" t="n">
+      <c r="AN22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AX22" t="n">
         <v>1.27</v>
       </c>
-      <c r="AN22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AV22" t="n">
+      <c r="AY22" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BA22" t="n">
         <v>1.81</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>1.3</v>
       </c>
       <c r="BB22" t="n">
         <v>1.4</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BD22" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="BF22" t="n">
         <v>1.08</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="BH22" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="BI22" s="3" t="n">
         <v>46127.60416666666</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,28 +1786,28 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1825,40 +1825,40 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1903,13 +1903,13 @@
         <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BD7" t="n">
         <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BF7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,67 +1983,67 @@
         </is>
       </c>
       <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF8" t="n">
         <v>1.89</v>
       </c>
-      <c r="Q8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V8" t="n">
+      <c r="AG8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH8" t="n">
         <v>1.33</v>
       </c>
-      <c r="W8" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AI8" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AK8" t="n">
         <v>1.68</v>
@@ -2052,10 +2052,10 @@
         <v>2.02</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.46</v>
+        <v>1.16</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2100,13 +2100,13 @@
         <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="BD8" t="n">
         <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="BF8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2189,13 +2189,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -2204,10 +2204,10 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
@@ -2219,40 +2219,40 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2297,13 +2297,13 @@
         <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
         <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="R10" t="n">
-        <v>2.4</v>
+        <v>4.14</v>
       </c>
       <c r="S10" t="n">
-        <v>3.38</v>
+        <v>2.43</v>
       </c>
       <c r="T10" t="n">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="U10" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="V10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.95</v>
+        <v>2.43</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Z10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AD10" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AI10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.47</v>
+        <v>1.2</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.11</v>
+        <v>1.93</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BD11" t="n">
         <v>3.6</v>
       </c>
-      <c r="R11" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>0</v>
-      </c>
       <c r="BE11" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,80 +2771,80 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AN12" t="n">
         <v>2.12</v>
       </c>
-      <c r="T12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
@@ -2888,13 +2888,13 @@
         <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.68</v>
+        <v>1.96</v>
       </c>
       <c r="BD12" t="n">
         <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.95</v>
+        <v>1.66</v>
       </c>
       <c r="BF12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2977,13 +2977,13 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -2992,10 +2992,10 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -3007,40 +3007,40 @@
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3085,13 +3085,13 @@
         <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
         <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3204,40 +3204,40 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,22 +3362,22 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.41</v>
+        <v>1.74</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="R15" t="n">
-        <v>6.13</v>
+        <v>4.04</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -3386,10 +3386,10 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -3401,40 +3401,40 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.76</v>
+        <v>1.48</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.88</v>
+        <v>2.38</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.88</v>
+        <v>2.18</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="AI15" t="n">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.87</v>
+        <v>1.5</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.81</v>
+        <v>2.38</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3479,13 +3479,13 @@
         <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD15" t="n">
         <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -801,28 +801,28 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="R2" t="n">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="S2" t="n">
         <v>3.25</v>
       </c>
       <c r="T2" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
         <v>3.2</v>
       </c>
       <c r="V2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W2" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="X2" t="n">
         <v>2.7</v>
@@ -849,7 +849,7 @@
         <v>1.95</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AG2" t="n">
         <v>3.24</v>
@@ -1589,28 +1589,28 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="R6" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="S6" t="n">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="T6" t="n">
-        <v>2.46</v>
+        <v>2.22</v>
       </c>
       <c r="U6" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="V6" t="n">
         <v>1.28</v>
       </c>
       <c r="W6" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="X6" t="n">
         <v>2.33</v>
@@ -1619,19 +1619,19 @@
         <v>1.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AB6" t="n">
         <v>1.03</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AD6" t="n">
-        <v>4.52</v>
+        <v>4.56</v>
       </c>
       <c r="AE6" t="n">
         <v>1.6</v>
@@ -1640,22 +1640,22 @@
         <v>2.3</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AI6" t="n">
         <v>4.3</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="AM6" t="n">
         <v>1.16</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,34 +1786,34 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R7" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U7" t="n">
         <v>3.8</v>
       </c>
-      <c r="S7" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3.3</v>
-      </c>
       <c r="V7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -1825,41 +1825,41 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AI7" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AK7" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN7" t="n">
         <v>1.68</v>
       </c>
-      <c r="AL7" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
@@ -1903,13 +1903,13 @@
         <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="BD7" t="n">
         <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="BF7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1992,13 +1992,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -2022,40 +2022,40 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2100,13 +2100,13 @@
         <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
         <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,28 +2180,28 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -2219,40 +2219,40 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2297,13 +2297,13 @@
         <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BD9" t="n">
         <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BF9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,22 +2377,22 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.43</v>
+        <v>4.25</v>
       </c>
       <c r="T10" t="n">
         <v>2.28</v>
       </c>
       <c r="U10" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -2401,10 +2401,10 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -2416,40 +2416,40 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AI10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AJ10" t="n">
         <v>1.11</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.68</v>
+        <v>1.16</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2494,13 +2494,13 @@
         <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="BD10" t="n">
         <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="BF10" t="n">
         <v>0</v>
@@ -2577,73 +2577,73 @@
         <v>2.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R11" t="n">
         <v>2.4</v>
       </c>
       <c r="S11" t="n">
-        <v>3.38</v>
+        <v>3.42</v>
       </c>
       <c r="T11" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="U11" t="n">
-        <v>3</v>
+        <v>3.23</v>
       </c>
       <c r="V11" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="W11" t="n">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="X11" t="n">
         <v>2.95</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z11" t="n">
         <v>7</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AD11" t="n">
-        <v>3</v>
+        <v>3.19</v>
       </c>
       <c r="AE11" t="n">
         <v>1.95</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="AG11" t="n">
-        <v>3.08</v>
+        <v>3.28</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AI11" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AK11" t="n">
         <v>1.7</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AN11" t="n">
         <v>1.44</v>
@@ -2688,19 +2688,19 @@
         <v>2.12</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,22 +2771,22 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="S12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -2795,10 +2795,10 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
@@ -2816,16 +2816,16 @@
         <v>3.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AF12" t="n">
         <v>1.88</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AI12" t="n">
         <v>5.1</v>
@@ -2834,16 +2834,16 @@
         <v>1.11</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AN12" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2888,13 +2888,13 @@
         <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
         <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,22 +2968,22 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -2992,10 +2992,10 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -3007,40 +3007,40 @@
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3085,13 +3085,13 @@
         <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD13" t="n">
         <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,34 +3165,34 @@
         </is>
       </c>
       <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Y14" t="n">
         <v>1.41</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R14" t="n">
-        <v>6.13</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -3210,16 +3210,16 @@
         <v>3.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AF14" t="n">
         <v>1.88</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AI14" t="n">
         <v>5.1</v>
@@ -3228,16 +3228,16 @@
         <v>1.11</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AN14" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3282,13 +3282,13 @@
         <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BD14" t="n">
         <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BF14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,22 +3362,22 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -3386,10 +3386,10 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -3401,40 +3401,40 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3479,13 +3479,13 @@
         <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
         <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BF15" t="n">
         <v>0</v>
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="Q17" t="n">
         <v>3.5</v>
       </c>
       <c r="R17" t="n">
-        <v>3.5</v>
+        <v>4.61</v>
       </c>
       <c r="S17" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="T17" t="n">
         <v>1.99</v>
       </c>
       <c r="U17" t="n">
-        <v>3.95</v>
+        <v>5.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W17" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="X17" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="Z17" t="n">
         <v>5.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC17" t="n">
         <v>1.19</v>
       </c>
       <c r="AD17" t="n">
-        <v>4.22</v>
+        <v>4.24</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AG17" t="n">
         <v>2.6</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AI17" t="n">
-        <v>4.88</v>
+        <v>4.85</v>
       </c>
       <c r="AJ17" t="n">
         <v>1.14</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AL17" t="n">
         <v>2.25</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3873,7 +3873,7 @@
         <v>1.15</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="BD17" t="n">
         <v>4.7</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>6.65</v>
+        <v>1.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.7</v>
+        <v>3.88</v>
       </c>
       <c r="R18" t="n">
-        <v>1.37</v>
+        <v>4.13</v>
       </c>
       <c r="S18" t="n">
-        <v>5.45</v>
+        <v>2.24</v>
       </c>
       <c r="T18" t="n">
-        <v>3.11</v>
+        <v>2.27</v>
       </c>
       <c r="U18" t="n">
-        <v>1.73</v>
+        <v>4.6</v>
       </c>
       <c r="V18" t="n">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="W18" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI18" t="n">
         <v>4.85</v>
       </c>
-      <c r="X18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AA18" t="n">
+      <c r="AJ18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AM18" t="n">
         <v>1.25</v>
       </c>
-      <c r="AB18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AI18" t="n">
+      <c r="AN18" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AT18" t="n">
         <v>2.45</v>
       </c>
-      <c r="AJ18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
       <c r="AU18" t="n">
         <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.44</v>
+        <v>1.88</v>
       </c>
       <c r="BD18" t="n">
-        <v>7.8</v>
+        <v>4.33</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.59</v>
+        <v>1.86</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.52</v>
+        <v>1.22</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.83</v>
+        <v>6</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.84</v>
+        <v>4.9</v>
       </c>
       <c r="R19" t="n">
-        <v>4.02</v>
+        <v>1.5</v>
       </c>
       <c r="S19" t="n">
-        <v>2.3</v>
+        <v>5.45</v>
       </c>
       <c r="T19" t="n">
-        <v>2.26</v>
+        <v>2.88</v>
       </c>
       <c r="U19" t="n">
-        <v>4.4</v>
+        <v>1.74</v>
       </c>
       <c r="V19" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="W19" t="n">
-        <v>3.15</v>
+        <v>4.75</v>
       </c>
       <c r="X19" t="n">
-        <v>2.44</v>
+        <v>1.84</v>
       </c>
       <c r="Y19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BF19" t="n">
         <v>1.49</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>1.23</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,139 +4347,139 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>6</v>
+        <v>7.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="R20" t="n">
         <v>1.49</v>
       </c>
       <c r="S20" t="n">
-        <v>5.96</v>
+        <v>8.9</v>
       </c>
       <c r="T20" t="n">
-        <v>2.17</v>
+        <v>1.98</v>
       </c>
       <c r="U20" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="V20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AF20" t="n">
         <v>1.36</v>
       </c>
-      <c r="W20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC20" t="n">
+      <c r="AG20" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM20" t="n">
         <v>1.27</v>
       </c>
-      <c r="AD20" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AJ20" t="n">
+      <c r="AN20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BF20" t="n">
         <v>1.08</v>
       </c>
-      <c r="AK20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>1.16</v>
-      </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI20" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,61 +4544,61 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>7.75</v>
+        <v>3.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="R21" t="n">
-        <v>1.49</v>
+        <v>2.05</v>
       </c>
       <c r="S21" t="n">
-        <v>8.9</v>
+        <v>4.33</v>
       </c>
       <c r="T21" t="n">
-        <v>1.98</v>
+        <v>1.81</v>
       </c>
       <c r="U21" t="n">
-        <v>2.2</v>
+        <v>2.85</v>
       </c>
       <c r="V21" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="W21" t="n">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="X21" t="n">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.9</v>
+        <v>8.1</v>
       </c>
       <c r="AA21" t="n">
         <v>1.03</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.23</v>
+        <v>2.39</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AG21" t="n">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AI21" t="n">
         <v>10</v>
@@ -4607,76 +4607,76 @@
         <v>1.02</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="AL21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BB21" t="n">
         <v>1.35</v>
       </c>
-      <c r="AM21" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.4</v>
-      </c>
       <c r="BC21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BD21" t="n">
         <v>2.82</v>
       </c>
-      <c r="BD21" t="n">
-        <v>2.62</v>
-      </c>
       <c r="BE21" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="BH21" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,139 +4741,139 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.87</v>
+        <v>5</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="R22" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="S22" t="n">
-        <v>4.2</v>
+        <v>5.99</v>
       </c>
       <c r="T22" t="n">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="U22" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="V22" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="W22" t="n">
-        <v>2.37</v>
+        <v>2.59</v>
       </c>
       <c r="X22" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="Z22" t="n">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
       <c r="AA22" t="n">
         <v>1.03</v>
       </c>
       <c r="AB22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AN22" t="n">
         <v>1.13</v>
       </c>
-      <c r="AC22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK22" t="n">
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BC22" t="n">
         <v>2.2</v>
       </c>
-      <c r="AL22" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>2.8</v>
-      </c>
       <c r="BD22" t="n">
-        <v>2.75</v>
+        <v>3.35</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="BG22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BH22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
         <v>46127.60416666666</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="S24" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
         <v>1.33</v>
       </c>
-      <c r="Q24" t="n">
-        <v>5</v>
-      </c>
-      <c r="R24" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="T24" t="n">
+      <c r="AQ24" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AS24" t="n">
         <v>2.45</v>
       </c>
-      <c r="U24" t="n">
-        <v>6</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W24" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AR24" t="n">
+      <c r="AT24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BE24" t="n">
         <v>1.69</v>
       </c>
-      <c r="AS24" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>6.26</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>1.95</v>
-      </c>
       <c r="BF24" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.69</v>
+        <v>1.33</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.68</v>
+        <v>5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.87</v>
+        <v>7.5</v>
       </c>
       <c r="S25" t="n">
-        <v>4.37</v>
+        <v>1.84</v>
       </c>
       <c r="T25" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U25" t="n">
+        <v>6</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W25" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="X25" t="n">
         <v>2.2</v>
       </c>
-      <c r="U25" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W25" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.69</v>
-      </c>
       <c r="Y25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ25" t="n">
         <v>1.41</v>
       </c>
-      <c r="Z25" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>6.13</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AR25" t="n">
-        <v>1.92</v>
+        <v>1.69</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="AT25" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="AU25" t="n">
-        <v>2.95</v>
+        <v>3.66</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.24</v>
+        <v>2.68</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.78</v>
+        <v>2.38</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.47</v>
+        <v>1.66</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="AZ25" t="n">
-        <v>2.4</v>
+        <v>1.19</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.63</v>
+        <v>6.26</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.75</v>
+        <v>4.8</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.69</v>
+        <v>1.95</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="R26" t="n">
-        <v>6.5</v>
+        <v>4.7</v>
       </c>
       <c r="S26" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="T26" t="n">
-        <v>2.3</v>
+        <v>2.85</v>
       </c>
       <c r="U26" t="n">
-        <v>6.5</v>
+        <v>3.78</v>
       </c>
       <c r="V26" t="n">
-        <v>1.35</v>
+        <v>1.13</v>
       </c>
       <c r="W26" t="n">
-        <v>3.18</v>
+        <v>5.5</v>
       </c>
       <c r="X26" t="n">
-        <v>2.45</v>
+        <v>1.83</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.48</v>
+        <v>2.04</v>
       </c>
       <c r="Z26" t="n">
-        <v>6</v>
+        <v>3.36</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="AB26" t="n">
         <v>1</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.74</v>
+        <v>8</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.86</v>
+        <v>1.28</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.06</v>
+        <v>3.75</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.88</v>
+        <v>1.72</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.35</v>
+        <v>2.1</v>
       </c>
       <c r="AI26" t="n">
-        <v>5.5</v>
+        <v>2.6</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.11</v>
+        <v>1.47</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.95</v>
+        <v>1.34</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.79</v>
+        <v>3.2</v>
       </c>
       <c r="AM26" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
         <v>1.2</v>
       </c>
-      <c r="AN26" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AQ26" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="AU26" t="n">
-        <v>3.28</v>
+        <v>3.72</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.39</v>
+        <v>1.69</v>
       </c>
       <c r="BA26" t="n">
-        <v>3.78</v>
+        <v>2.62</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.07</v>
+        <v>1.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.2</v>
+        <v>6.5</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.78</v>
+        <v>2.55</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="R27" t="n">
-        <v>4.7</v>
+        <v>6.5</v>
       </c>
       <c r="S27" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="T27" t="n">
-        <v>2.85</v>
+        <v>2.3</v>
       </c>
       <c r="U27" t="n">
-        <v>3.78</v>
+        <v>6.5</v>
       </c>
       <c r="V27" t="n">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="W27" t="n">
-        <v>5.5</v>
+        <v>3.18</v>
       </c>
       <c r="X27" t="n">
-        <v>1.83</v>
+        <v>2.45</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.04</v>
+        <v>1.48</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.36</v>
+        <v>6</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="AB27" t="n">
         <v>1</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.07</v>
+        <v>1.26</v>
       </c>
       <c r="AD27" t="n">
-        <v>8</v>
+        <v>3.74</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.28</v>
+        <v>1.86</v>
       </c>
       <c r="AF27" t="n">
-        <v>3.75</v>
+        <v>2.06</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.72</v>
+        <v>2.88</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.1</v>
+        <v>1.35</v>
       </c>
       <c r="AI27" t="n">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.47</v>
+        <v>1.11</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.34</v>
+        <v>1.95</v>
       </c>
       <c r="AL27" t="n">
-        <v>3.2</v>
+        <v>1.79</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AN27" t="n">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BF27" t="n">
         <v>1.2</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>1.5</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -1640,16 +1640,16 @@
         <v>2.3</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AI6" t="n">
         <v>4.3</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AK6" t="n">
         <v>1.55</v>
@@ -1658,10 +1658,10 @@
         <v>2.27</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1804,10 +1804,10 @@
         <v>3.8</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="X7" t="n">
         <v>2.43</v>
@@ -1816,13 +1816,13 @@
         <v>1.43</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC7" t="n">
         <v>1.22</v>
@@ -1855,7 +1855,7 @@
         <v>2.1</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AN7" t="n">
         <v>1.68</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC7" t="n">
         <v>1.93</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE7" t="n">
         <v>1.68</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2204,19 +2204,19 @@
         <v>2.75</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC9" t="n">
         <v>1.26</v>
@@ -2249,7 +2249,7 @@
         <v>2.02</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AN9" t="n">
         <v>1.46</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC9" t="n">
         <v>2.02</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE9" t="n">
         <v>1.61</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S10" t="n">
         <v>4.25</v>
@@ -2395,10 +2395,10 @@
         <v>2.3</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="X10" t="n">
         <v>2.45</v>
@@ -2407,13 +2407,13 @@
         <v>1.42</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC10" t="n">
         <v>1.23</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC10" t="n">
         <v>1.95</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BE10" t="n">
         <v>1.66</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2574,34 +2574,34 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R11" t="n">
         <v>2.4</v>
       </c>
       <c r="S11" t="n">
-        <v>3.42</v>
+        <v>3.02</v>
       </c>
       <c r="T11" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="U11" t="n">
-        <v>3.23</v>
+        <v>2.88</v>
       </c>
       <c r="V11" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W11" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="X11" t="n">
         <v>2.95</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z11" t="n">
         <v>7</v>
@@ -2613,40 +2613,40 @@
         <v>1.03</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.19</v>
+        <v>2.97</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AG11" t="n">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AI11" t="n">
-        <v>6.25</v>
+        <v>6.4</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,16 +2688,16 @@
         <v>2.12</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.44</v>
+        <v>3.36</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="BF11" t="n">
         <v>1.13</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>6.13</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2810,40 +2810,40 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2986,10 +2986,10 @@
         <v>4.1</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="X13" t="n">
         <v>2.06</v>
@@ -2998,13 +2998,13 @@
         <v>1.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC13" t="n">
         <v>1.13</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BC13" t="n">
         <v>1.68</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="BE13" t="n">
         <v>1.95</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3174,13 +3174,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -3189,10 +3189,10 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -3204,40 +3204,40 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3282,13 +3282,13 @@
         <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
         <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,79 +3362,79 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3568,70 +3568,70 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3765,25 +3765,25 @@
         <v>4.61</v>
       </c>
       <c r="S17" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="T17" t="n">
         <v>1.99</v>
       </c>
       <c r="U17" t="n">
-        <v>5.01</v>
+        <v>4.86</v>
       </c>
       <c r="V17" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W17" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="X17" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Z17" t="n">
         <v>5.8</v>
@@ -3792,7 +3792,7 @@
         <v>1.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC17" t="n">
         <v>1.19</v>
@@ -3801,16 +3801,16 @@
         <v>4.24</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AI17" t="n">
         <v>4.85</v>
@@ -3822,13 +3822,13 @@
         <v>1.59</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3873,10 +3873,10 @@
         <v>1.15</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BE17" t="n">
         <v>1.87</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,61 +4347,61 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>7.75</v>
+        <v>3.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="R20" t="n">
-        <v>1.49</v>
+        <v>2.05</v>
       </c>
       <c r="S20" t="n">
-        <v>8.9</v>
+        <v>4.33</v>
       </c>
       <c r="T20" t="n">
-        <v>1.98</v>
+        <v>1.81</v>
       </c>
       <c r="U20" t="n">
-        <v>2.2</v>
+        <v>2.85</v>
       </c>
       <c r="V20" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="X20" t="n">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z20" t="n">
-        <v>8.9</v>
+        <v>8.1</v>
       </c>
       <c r="AA20" t="n">
         <v>1.03</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.23</v>
+        <v>2.39</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AG20" t="n">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AI20" t="n">
         <v>10</v>
@@ -4410,76 +4410,76 @@
         <v>1.02</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="AL20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BB20" t="n">
         <v>1.35</v>
       </c>
-      <c r="AM20" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.4</v>
-      </c>
       <c r="BC20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BD20" t="n">
         <v>2.82</v>
       </c>
-      <c r="BD20" t="n">
-        <v>2.62</v>
-      </c>
       <c r="BE20" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="BH20" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="BI20" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,139 +4544,139 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="R21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U21" t="n">
         <v>2.05</v>
       </c>
-      <c r="S21" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2.85</v>
-      </c>
       <c r="V21" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="W21" t="n">
-        <v>2.37</v>
+        <v>2.59</v>
       </c>
       <c r="X21" t="n">
-        <v>3.58</v>
+        <v>3.25</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
       <c r="AA21" t="n">
         <v>1.03</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.39</v>
+        <v>2.91</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.72</v>
+        <v>1.97</v>
       </c>
       <c r="AF21" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AX21" t="n">
         <v>1.41</v>
       </c>
-      <c r="AG21" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AM21" t="n">
+      <c r="AY21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA21" t="n">
         <v>1.32</v>
       </c>
-      <c r="AN21" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>3</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>1.81</v>
-      </c>
       <c r="BB21" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.7</v>
+        <v>2.17</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.82</v>
+        <v>3.28</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BH21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,139 +4741,139 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>5</v>
+        <v>7.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="S22" t="n">
-        <v>5.99</v>
+        <v>8.9</v>
       </c>
       <c r="T22" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="U22" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="V22" t="n">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="W22" t="n">
-        <v>2.59</v>
+        <v>2.1</v>
       </c>
       <c r="X22" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="Z22" t="n">
-        <v>7.2</v>
+        <v>8.9</v>
       </c>
       <c r="AA22" t="n">
         <v>1.03</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.38</v>
+        <v>1.59</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.91</v>
+        <v>2.23</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.97</v>
+        <v>2.7</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.66</v>
+        <v>1.36</v>
       </c>
       <c r="AG22" t="n">
-        <v>3.58</v>
+        <v>5.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="AI22" t="n">
-        <v>6.95</v>
+        <v>10</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.03</v>
+        <v>2.88</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="AM22" t="n">
-        <v>2.21</v>
+        <v>1.27</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.63</v>
+        <v>3.15</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>2.75</v>
+        <v>2.33</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.08</v>
+        <v>1.81</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.2</v>
+        <v>2.82</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.35</v>
+        <v>2.62</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI22" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4938,10 +4938,10 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>11.1</v>
+        <v>7.9</v>
       </c>
       <c r="R23" t="n">
         <v>15</v>
@@ -4950,67 +4950,67 @@
         <v>1.44</v>
       </c>
       <c r="T23" t="n">
-        <v>3.64</v>
+        <v>3.62</v>
       </c>
       <c r="U23" t="n">
         <v>10</v>
       </c>
       <c r="V23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC23" t="n">
         <v>1.06</v>
       </c>
-      <c r="W23" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AD23" t="n">
-        <v>9.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AE23" t="n">
         <v>1.23</v>
       </c>
       <c r="AF23" t="n">
-        <v>3.96</v>
+        <v>3.9</v>
       </c>
       <c r="AG23" t="n">
         <v>1.62</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AK23" t="n">
         <v>1.67</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AN23" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5055,10 +5055,10 @@
         <v>1.08</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="BD23" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE23" t="n">
         <v>2.56</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R7" t="n">
-        <v>4.14</v>
+        <v>2.5</v>
       </c>
       <c r="S7" t="n">
-        <v>2.43</v>
+        <v>3.05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="U7" t="n">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="V7" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W7" t="n">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="X7" t="n">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.15</v>
+        <v>6.55</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AB7" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AI7" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="BD7" t="n">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R8" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S8" t="n">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="T8" t="n">
-        <v>2.18</v>
+        <v>1.97</v>
       </c>
       <c r="U8" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="V8" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="W8" t="n">
-        <v>2.83</v>
+        <v>2.56</v>
       </c>
       <c r="X8" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AS8" t="n">
         <v>2.55</v>
       </c>
-      <c r="Y8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="BC8" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.82</v>
+        <v>3.36</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,67 +2180,67 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.89</v>
+        <v>3.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R9" t="n">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="S9" t="n">
-        <v>2.85</v>
+        <v>4.25</v>
       </c>
       <c r="T9" t="n">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="U9" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="V9" t="n">
         <v>1.33</v>
       </c>
       <c r="W9" t="n">
-        <v>2.75</v>
+        <v>2.86</v>
       </c>
       <c r="X9" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.85</v>
+        <v>6.35</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AB9" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="AG9" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AI9" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AK9" t="n">
         <v>1.68</v>
@@ -2249,10 +2249,10 @@
         <v>2.02</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.46</v>
+        <v>1.16</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,67 +2377,67 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3.6</v>
+        <v>1.89</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="S10" t="n">
-        <v>4.25</v>
+        <v>2.85</v>
       </c>
       <c r="T10" t="n">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="U10" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="V10" t="n">
         <v>1.33</v>
       </c>
       <c r="W10" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="X10" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.35</v>
+        <v>6.85</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AI10" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AK10" t="n">
         <v>1.68</v>
@@ -2446,10 +2446,10 @@
         <v>2.02</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.16</v>
+        <v>1.46</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.6</v>
+        <v>1.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="R11" t="n">
-        <v>2.4</v>
+        <v>4.14</v>
       </c>
       <c r="S11" t="n">
-        <v>3.02</v>
+        <v>2.43</v>
       </c>
       <c r="T11" t="n">
-        <v>1.97</v>
+        <v>2.28</v>
       </c>
       <c r="U11" t="n">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="V11" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="W11" t="n">
-        <v>2.56</v>
+        <v>2.92</v>
       </c>
       <c r="X11" t="n">
-        <v>2.95</v>
+        <v>2.43</v>
       </c>
       <c r="Y11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.35</v>
       </c>
-      <c r="Z11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AI11" t="n">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.41</v>
+        <v>1.68</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.28</v>
+        <v>1.93</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.36</v>
+        <v>4</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,79 +2771,79 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,79 +2968,79 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3174,70 +3174,70 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,79 +3362,79 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.41</v>
+        <v>1.74</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="R15" t="n">
-        <v>6.13</v>
+        <v>4.04</v>
       </c>
       <c r="S15" t="n">
-        <v>1.99</v>
+        <v>2.12</v>
       </c>
       <c r="T15" t="n">
-        <v>2.19</v>
+        <v>2.5</v>
       </c>
       <c r="U15" t="n">
-        <v>6.6</v>
+        <v>4.1</v>
       </c>
       <c r="V15" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="W15" t="n">
-        <v>2.88</v>
+        <v>3.48</v>
       </c>
       <c r="X15" t="n">
-        <v>2.63</v>
+        <v>2.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="Z15" t="n">
-        <v>6.7</v>
+        <v>4.9</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AB15" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.76</v>
+        <v>1.48</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.88</v>
+        <v>2.38</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.88</v>
+        <v>2.18</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="AI15" t="n">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.87</v>
+        <v>1.5</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.81</v>
+        <v>2.38</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.99</v>
+        <v>1.68</v>
       </c>
       <c r="BD15" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3568,70 +3568,70 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,139 +4544,139 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>4.8</v>
+        <v>7.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="S21" t="n">
-        <v>5.93</v>
+        <v>8.9</v>
       </c>
       <c r="T21" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="U21" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="V21" t="n">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="W21" t="n">
-        <v>2.59</v>
+        <v>2.1</v>
       </c>
       <c r="X21" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.2</v>
+        <v>8.9</v>
       </c>
       <c r="AA21" t="n">
         <v>1.03</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.38</v>
+        <v>1.59</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.91</v>
+        <v>2.23</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.97</v>
+        <v>2.7</v>
       </c>
       <c r="AF21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AQ21" t="n">
         <v>1.87</v>
       </c>
-      <c r="AG21" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AR21" t="n">
-        <v>2.07</v>
+        <v>2.38</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.65</v>
+        <v>3.15</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>2.7</v>
+        <v>2.33</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.66</v>
+        <v>1.49</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.17</v>
+        <v>2.82</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.28</v>
+        <v>2.62</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="BG21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,139 +4741,139 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>7.75</v>
+        <v>4.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="S22" t="n">
-        <v>8.9</v>
+        <v>5.93</v>
       </c>
       <c r="T22" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="U22" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="V22" t="n">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="W22" t="n">
-        <v>2.1</v>
+        <v>2.59</v>
       </c>
       <c r="X22" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="Z22" t="n">
-        <v>8.9</v>
+        <v>7.2</v>
       </c>
       <c r="AA22" t="n">
         <v>1.03</v>
       </c>
       <c r="AB22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BF22" t="n">
         <v>1.1</v>
       </c>
-      <c r="AC22" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>1.08</v>
-      </c>
       <c r="BG22" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
         <v>46127.60416666666</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.69</v>
+        <v>1.27</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.68</v>
+        <v>4.65</v>
       </c>
       <c r="R24" t="n">
-        <v>1.87</v>
+        <v>7.5</v>
       </c>
       <c r="S24" t="n">
-        <v>4.37</v>
+        <v>1.84</v>
       </c>
       <c r="T24" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="U24" t="n">
-        <v>2.49</v>
+        <v>6.5</v>
       </c>
       <c r="V24" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W24" t="n">
-        <v>2.65</v>
+        <v>3.5</v>
       </c>
       <c r="X24" t="n">
-        <v>2.69</v>
+        <v>2.33</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="Z24" t="n">
-        <v>6.25</v>
+        <v>5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.23</v>
+        <v>2.52</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.29</v>
+        <v>1.52</v>
       </c>
       <c r="AI24" t="n">
-        <v>6.13</v>
+        <v>4.51</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
       <c r="AL24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AS24" t="n">
         <v>1.98</v>
       </c>
-      <c r="AM24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN24" t="n">
+      <c r="AT24" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BF24" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>1.16</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
         <v>1.33</v>
       </c>
-      <c r="Q25" t="n">
-        <v>5</v>
-      </c>
-      <c r="R25" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="T25" t="n">
+      <c r="AQ25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AS25" t="n">
         <v>2.45</v>
       </c>
-      <c r="U25" t="n">
-        <v>6</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W25" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>2.09</v>
-      </c>
       <c r="AT25" t="n">
-        <v>2.7</v>
+        <v>3.72</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.66</v>
+        <v>2.88</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.68</v>
+        <v>2.11</v>
       </c>
       <c r="AW25" t="n">
-        <v>2.38</v>
+        <v>1.68</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.66</v>
+        <v>1.47</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.19</v>
+        <v>2.4</v>
       </c>
       <c r="BA25" t="n">
-        <v>6.26</v>
+        <v>1.7</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.8</v>
+        <v>2.11</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.8</v>
+        <v>3.75</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="R26" t="n">
-        <v>4.7</v>
+        <v>7.25</v>
       </c>
       <c r="S26" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="T26" t="n">
-        <v>2.85</v>
+        <v>2.3</v>
       </c>
       <c r="U26" t="n">
-        <v>3.78</v>
+        <v>6.6</v>
       </c>
       <c r="V26" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="W26" t="n">
-        <v>5.5</v>
+        <v>3.29</v>
       </c>
       <c r="X26" t="n">
-        <v>1.83</v>
+        <v>2.63</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.04</v>
+        <v>1.47</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.36</v>
+        <v>6</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.3</v>
+        <v>1.06</v>
       </c>
       <c r="AB26" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.07</v>
+        <v>1.26</v>
       </c>
       <c r="AD26" t="n">
-        <v>8</v>
+        <v>3.94</v>
       </c>
       <c r="AE26" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
         <v>1.28</v>
       </c>
-      <c r="AF26" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
+      <c r="AQ26" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BF26" t="n">
         <v>1.2</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>1.5</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="R27" t="n">
-        <v>6.5</v>
+        <v>4.8</v>
       </c>
       <c r="S27" t="n">
-        <v>1.96</v>
+        <v>1.82</v>
       </c>
       <c r="T27" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="U27" t="n">
-        <v>6.5</v>
+        <v>4.65</v>
       </c>
       <c r="V27" t="n">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="W27" t="n">
-        <v>3.18</v>
+        <v>4.7</v>
       </c>
       <c r="X27" t="n">
-        <v>2.45</v>
+        <v>1.83</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.48</v>
+        <v>1.98</v>
       </c>
       <c r="Z27" t="n">
-        <v>6</v>
+        <v>3.24</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="AB27" t="n">
         <v>1</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.74</v>
+        <v>8</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.86</v>
+        <v>1.28</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.06</v>
+        <v>3.75</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.88</v>
+        <v>1.72</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.35</v>
+        <v>2.1</v>
       </c>
       <c r="AI27" t="n">
-        <v>5.5</v>
+        <v>2.6</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.11</v>
+        <v>1.47</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.95</v>
+        <v>1.31</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.79</v>
+        <v>3.15</v>
       </c>
       <c r="AM27" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
         <v>1.2</v>
       </c>
-      <c r="AN27" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AQ27" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AS27" t="n">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="AT27" t="n">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="AU27" t="n">
-        <v>3.28</v>
+        <v>3.9</v>
       </c>
       <c r="AV27" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.39</v>
+        <v>1.8</v>
       </c>
       <c r="BA27" t="n">
-        <v>3.78</v>
+        <v>2.2</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.07</v>
+        <v>1.51</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.78</v>
+        <v>2.65</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G31" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="R2" t="n">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="S2" t="n">
         <v>3.25</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="U2" t="n">
         <v>3.2</v>
@@ -837,7 +837,7 @@
         <v>1.08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AC2" t="n">
         <v>1.3</v>
@@ -855,16 +855,16 @@
         <v>3.24</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AI2" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AJ2" t="n">
         <v>1.09</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AL2" t="n">
         <v>2</v>
@@ -921,7 +921,7 @@
         <v>2.1</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="BE2" t="n">
         <v>1.63</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.5</v>
+        <v>1.89</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="S7" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="T7" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="U7" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W7" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="X7" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.55</v>
+        <v>6.85</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM7" t="n">
         <v>1.24</v>
       </c>
-      <c r="AD7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AN7" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.82</v>
+        <v>3.7</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R8" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S8" t="n">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="T8" t="n">
-        <v>1.97</v>
+        <v>2.18</v>
       </c>
       <c r="U8" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="V8" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="W8" t="n">
-        <v>2.56</v>
+        <v>2.83</v>
       </c>
       <c r="X8" t="n">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="Z8" t="n">
-        <v>7</v>
+        <v>6.55</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH8" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD8" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AI8" t="n">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.36</v>
+        <v>3.82</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,80 +2377,80 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R10" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U10" t="n">
         <v>3.8</v>
       </c>
-      <c r="S10" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="U10" t="n">
-        <v>3.3</v>
-      </c>
       <c r="V10" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W10" t="n">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="X10" t="n">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.85</v>
+        <v>6.15</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AB10" t="n">
         <v>1</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AI10" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AK10" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN10" t="n">
         <v>1.68</v>
       </c>
-      <c r="AL10" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK11" t="n">
         <v>1.75</v>
       </c>
-      <c r="Q11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R11" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="T11" t="n">
+      <c r="AL11" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC11" t="n">
         <v>2.28</v>
       </c>
-      <c r="U11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W11" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>1.93</v>
-      </c>
       <c r="BD11" t="n">
-        <v>4</v>
+        <v>3.36</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,22 +2771,22 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>6.13</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="T12" t="n">
-        <v>2.19</v>
+        <v>2.33</v>
       </c>
       <c r="U12" t="n">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="V12" t="n">
         <v>1.33</v>
@@ -2795,16 +2795,16 @@
         <v>2.88</v>
       </c>
       <c r="X12" t="n">
-        <v>2.63</v>
+        <v>2.48</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.7</v>
+        <v>6.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AB12" t="n">
         <v>1</v>
@@ -2816,16 +2816,16 @@
         <v>3.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AF12" t="n">
         <v>1.88</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AI12" t="n">
         <v>5.1</v>
@@ -2834,16 +2834,16 @@
         <v>1.11</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AN12" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="BD12" t="n">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,79 +2968,79 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3174,70 +3174,70 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,79 +3362,79 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,79 +3559,79 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,61 +4347,61 @@
         </is>
       </c>
       <c r="P20" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S20" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X20" t="n">
         <v>3.7</v>
       </c>
-      <c r="Q20" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R20" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="S20" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W20" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="X20" t="n">
-        <v>3.58</v>
-      </c>
       <c r="Y20" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z20" t="n">
-        <v>8.1</v>
+        <v>8.9</v>
       </c>
       <c r="AA20" t="n">
         <v>1.03</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.39</v>
+        <v>2.23</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AG20" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AI20" t="n">
         <v>10</v>
@@ -4410,76 +4410,76 @@
         <v>1.02</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="AO20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BB20" t="n">
         <v>1.4</v>
       </c>
-      <c r="AP20" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>3</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BB20" t="n">
+      <c r="BC20" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BE20" t="n">
         <v>1.35</v>
       </c>
-      <c r="BC20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>1.38</v>
-      </c>
       <c r="BF20" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH20" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="BI20" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,61 +4544,61 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>7.75</v>
+        <v>3.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="R21" t="n">
-        <v>1.49</v>
+        <v>2.05</v>
       </c>
       <c r="S21" t="n">
-        <v>8.9</v>
+        <v>4.33</v>
       </c>
       <c r="T21" t="n">
-        <v>1.98</v>
+        <v>1.81</v>
       </c>
       <c r="U21" t="n">
-        <v>2.2</v>
+        <v>2.85</v>
       </c>
       <c r="V21" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="W21" t="n">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="X21" t="n">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.9</v>
+        <v>8.1</v>
       </c>
       <c r="AA21" t="n">
         <v>1.03</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.23</v>
+        <v>2.39</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AG21" t="n">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AI21" t="n">
         <v>10</v>
@@ -4607,76 +4607,76 @@
         <v>1.02</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="AL21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BB21" t="n">
         <v>1.35</v>
       </c>
-      <c r="AM21" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.4</v>
-      </c>
       <c r="BC21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BD21" t="n">
         <v>2.82</v>
       </c>
-      <c r="BD21" t="n">
-        <v>2.62</v>
-      </c>
       <c r="BE21" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="BH21" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.27</v>
+        <v>3.56</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.65</v>
+        <v>3.58</v>
       </c>
       <c r="R24" t="n">
-        <v>7.5</v>
+        <v>1.91</v>
       </c>
       <c r="S24" t="n">
-        <v>1.84</v>
+        <v>4.26</v>
       </c>
       <c r="T24" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AS24" t="n">
         <v>2.45</v>
       </c>
-      <c r="U24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="AJ24" t="n">
+      <c r="AT24" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BF24" t="n">
         <v>1.16</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>1.25</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.56</v>
+        <v>1.27</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.58</v>
+        <v>4.65</v>
       </c>
       <c r="R25" t="n">
-        <v>1.91</v>
+        <v>7.5</v>
       </c>
       <c r="S25" t="n">
-        <v>4.26</v>
+        <v>1.84</v>
       </c>
       <c r="T25" t="n">
-        <v>2.19</v>
+        <v>2.45</v>
       </c>
       <c r="U25" t="n">
-        <v>2.55</v>
+        <v>6.5</v>
       </c>
       <c r="V25" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W25" t="n">
-        <v>2.94</v>
+        <v>3.5</v>
       </c>
       <c r="X25" t="n">
-        <v>2.73</v>
+        <v>2.33</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="Z25" t="n">
-        <v>6.35</v>
+        <v>5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AB25" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AC25" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BF25" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>6.19</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>1.16</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="R26" t="n">
-        <v>7.25</v>
+        <v>4.8</v>
       </c>
       <c r="S26" t="n">
-        <v>1.96</v>
+        <v>1.82</v>
       </c>
       <c r="T26" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="U26" t="n">
-        <v>6.6</v>
+        <v>4.65</v>
       </c>
       <c r="V26" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="W26" t="n">
-        <v>3.29</v>
+        <v>4.7</v>
       </c>
       <c r="X26" t="n">
-        <v>2.63</v>
+        <v>1.83</v>
       </c>
       <c r="Y26" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AJ26" t="n">
         <v>1.47</v>
       </c>
-      <c r="Z26" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA26" t="n">
+      <c r="AK26" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BB26" t="n">
         <v>1.06</v>
       </c>
-      <c r="AB26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>1.21</v>
-      </c>
       <c r="BC26" t="n">
-        <v>2.07</v>
+        <v>1.51</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.78</v>
+        <v>2.65</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="R27" t="n">
-        <v>4.8</v>
+        <v>7.25</v>
       </c>
       <c r="S27" t="n">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="T27" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="U27" t="n">
-        <v>4.65</v>
+        <v>6.6</v>
       </c>
       <c r="V27" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="W27" t="n">
-        <v>4.7</v>
+        <v>3.29</v>
       </c>
       <c r="X27" t="n">
-        <v>1.83</v>
+        <v>2.63</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.98</v>
+        <v>1.47</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.24</v>
+        <v>6</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.23</v>
+        <v>1.06</v>
       </c>
       <c r="AB27" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.07</v>
+        <v>1.26</v>
       </c>
       <c r="AD27" t="n">
-        <v>8</v>
+        <v>3.94</v>
       </c>
       <c r="AE27" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
         <v>1.28</v>
       </c>
-      <c r="AF27" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
+      <c r="AQ27" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BF27" t="n">
         <v>1.2</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>1.5</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,130 +1786,130 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.89</v>
+        <v>2.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="R7" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="S7" t="n">
-        <v>2.85</v>
+        <v>3.02</v>
       </c>
       <c r="T7" t="n">
-        <v>2.17</v>
+        <v>1.97</v>
       </c>
       <c r="U7" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="V7" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="W7" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="X7" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.85</v>
+        <v>7</v>
       </c>
       <c r="AA7" t="n">
         <v>1.04</v>
       </c>
       <c r="AB7" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.25</v>
+        <v>2.97</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AI7" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.7</v>
+        <v>3.36</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="BF7" t="n">
         <v>1.13</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R8" t="n">
-        <v>2.5</v>
+        <v>4.14</v>
       </c>
       <c r="S8" t="n">
-        <v>3.05</v>
+        <v>2.43</v>
       </c>
       <c r="T8" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="U8" t="n">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="V8" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W8" t="n">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="X8" t="n">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.55</v>
+        <v>6.15</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AG8" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AI8" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="BC8" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.82</v>
+        <v>4</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,67 +2180,67 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.6</v>
+        <v>1.89</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="S9" t="n">
-        <v>4.25</v>
+        <v>2.85</v>
       </c>
       <c r="T9" t="n">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="U9" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="V9" t="n">
         <v>1.33</v>
       </c>
       <c r="W9" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="X9" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.35</v>
+        <v>6.85</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AI9" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AK9" t="n">
         <v>1.68</v>
@@ -2249,10 +2249,10 @@
         <v>2.02</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.16</v>
+        <v>1.46</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R10" t="n">
-        <v>4.14</v>
+        <v>2.5</v>
       </c>
       <c r="S10" t="n">
-        <v>2.43</v>
+        <v>3.05</v>
       </c>
       <c r="T10" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="U10" t="n">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="V10" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W10" t="n">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="X10" t="n">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.15</v>
+        <v>6.55</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AB10" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AI10" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="BD10" t="n">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R11" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="S11" t="n">
-        <v>3.02</v>
+        <v>4.25</v>
       </c>
       <c r="T11" t="n">
-        <v>1.97</v>
+        <v>2.28</v>
       </c>
       <c r="U11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AG11" t="n">
         <v>2.88</v>
       </c>
-      <c r="V11" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W11" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>3.34</v>
-      </c>
       <c r="AH11" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AI11" t="n">
-        <v>6.4</v>
+        <v>5.1</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.41</v>
+        <v>1.16</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.28</v>
+        <v>1.95</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.36</v>
+        <v>3.95</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,79 +2771,79 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S12" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="T12" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="U12" t="n">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="V12" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="W12" t="n">
-        <v>2.88</v>
+        <v>3.48</v>
       </c>
       <c r="X12" t="n">
-        <v>2.48</v>
+        <v>2.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.1</v>
+        <v>4.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AB12" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.77</v>
+        <v>1.48</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.88</v>
+        <v>2.38</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.9</v>
+        <v>2.18</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.32</v>
+        <v>1.56</v>
       </c>
       <c r="AI12" t="n">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.84</v>
+        <v>1.5</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="AM12" t="n">
         <v>1.18</v>
       </c>
       <c r="AN12" t="n">
-        <v>2.12</v>
+        <v>1.91</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.82</v>
+        <v>5.25</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,79 +2968,79 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,79 +3165,79 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3371,70 +3371,70 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,79 +3559,79 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>6.13</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,139 +4347,139 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>7.75</v>
+        <v>4.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="S20" t="n">
-        <v>8.9</v>
+        <v>5.93</v>
       </c>
       <c r="T20" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="U20" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="V20" t="n">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1</v>
+        <v>2.59</v>
       </c>
       <c r="X20" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>8.9</v>
+        <v>7.2</v>
       </c>
       <c r="AA20" t="n">
         <v>1.03</v>
       </c>
       <c r="AB20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BF20" t="n">
         <v>1.1</v>
       </c>
-      <c r="AC20" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>1.08</v>
-      </c>
       <c r="BG20" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,61 +4544,61 @@
         </is>
       </c>
       <c r="P21" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S21" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X21" t="n">
         <v>3.7</v>
       </c>
-      <c r="Q21" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="S21" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W21" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="X21" t="n">
-        <v>3.58</v>
-      </c>
       <c r="Y21" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.1</v>
+        <v>8.9</v>
       </c>
       <c r="AA21" t="n">
         <v>1.03</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.39</v>
+        <v>2.23</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AG21" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AI21" t="n">
         <v>10</v>
@@ -4607,76 +4607,76 @@
         <v>1.02</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="AO21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BB21" t="n">
         <v>1.4</v>
       </c>
-      <c r="AP21" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>3</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BB21" t="n">
+      <c r="BC21" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BE21" t="n">
         <v>1.35</v>
       </c>
-      <c r="BC21" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.38</v>
-      </c>
       <c r="BF21" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH21" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,139 +4741,139 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6</v>
+        <v>2.05</v>
       </c>
       <c r="S22" t="n">
-        <v>5.93</v>
+        <v>4.33</v>
       </c>
       <c r="T22" t="n">
-        <v>2.08</v>
+        <v>1.81</v>
       </c>
       <c r="U22" t="n">
-        <v>2.05</v>
+        <v>2.85</v>
       </c>
       <c r="V22" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="W22" t="n">
-        <v>2.59</v>
+        <v>2.37</v>
       </c>
       <c r="X22" t="n">
-        <v>3.25</v>
+        <v>3.58</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="Z22" t="n">
-        <v>7.2</v>
+        <v>8.1</v>
       </c>
       <c r="AA22" t="n">
         <v>1.03</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AC22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BE22" t="n">
         <v>1.38</v>
       </c>
-      <c r="AD22" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ22" t="n">
+      <c r="BF22" t="n">
         <v>1.04</v>
       </c>
-      <c r="AK22" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>1.1</v>
-      </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BH22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BI22" s="3" t="n">
         <v>46127.60416666666</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="R2" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="S2" t="n">
         <v>3.25</v>
       </c>
       <c r="T2" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="U2" t="n">
         <v>3.2</v>
@@ -831,7 +831,7 @@
         <v>1.38</v>
       </c>
       <c r="Z2" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="AA2" t="n">
         <v>1.08</v>
@@ -843,7 +843,7 @@
         <v>1.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.35</v>
+        <v>3.47</v>
       </c>
       <c r="AE2" t="n">
         <v>1.95</v>
@@ -861,10 +861,10 @@
         <v>6.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AL2" t="n">
         <v>2</v>
@@ -921,7 +921,7 @@
         <v>2.1</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.6</v>
+        <v>3.66</v>
       </c>
       <c r="BE2" t="n">
         <v>1.63</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AG7" t="n">
         <v>3.1</v>
       </c>
-      <c r="R7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U7" t="n">
+      <c r="AH7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="AV7" t="n">
         <v>2.88</v>
       </c>
-      <c r="V7" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W7" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AE7" t="n">
+      <c r="AW7" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BC7" t="n">
         <v>2.05</v>
       </c>
-      <c r="AF7" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>2.28</v>
-      </c>
       <c r="BD7" t="n">
-        <v>3.36</v>
+        <v>3.78</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.75</v>
+        <v>3.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R8" t="n">
-        <v>4.14</v>
+        <v>1.85</v>
       </c>
       <c r="S8" t="n">
-        <v>2.43</v>
+        <v>4.2</v>
       </c>
       <c r="T8" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="U8" t="n">
-        <v>3.8</v>
+        <v>2.46</v>
       </c>
       <c r="V8" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W8" t="n">
-        <v>2.92</v>
+        <v>2.79</v>
       </c>
       <c r="X8" t="n">
-        <v>2.43</v>
+        <v>2.67</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.15</v>
+        <v>6.55</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AB8" t="n">
         <v>1</v>
       </c>
       <c r="AC8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
         <v>1.22</v>
       </c>
-      <c r="AD8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF8" t="n">
+      <c r="AQ8" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW8" t="n">
         <v>1.92</v>
       </c>
-      <c r="AG8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="BE8" t="n">
         <v>1.68</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R9" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="S9" t="n">
-        <v>2.85</v>
+        <v>2.41</v>
       </c>
       <c r="T9" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="U9" t="n">
-        <v>3.3</v>
+        <v>4.32</v>
       </c>
       <c r="V9" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W9" t="n">
-        <v>2.75</v>
+        <v>2.97</v>
       </c>
       <c r="X9" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.85</v>
+        <v>6</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AB9" t="n">
         <v>1</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.25</v>
+        <v>3.72</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="AG9" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="AV9" t="n">
         <v>3.1</v>
       </c>
-      <c r="AH9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0</v>
-      </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q10" t="n">
         <v>3.4</v>
       </c>
       <c r="R10" t="n">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="S10" t="n">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="T10" t="n">
-        <v>2.18</v>
+        <v>2.01</v>
       </c>
       <c r="U10" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="V10" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W10" t="n">
-        <v>2.83</v>
+        <v>2.67</v>
       </c>
       <c r="X10" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.55</v>
+        <v>7</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AB10" t="n">
         <v>1.01</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AI10" t="n">
-        <v>5.3</v>
+        <v>6.15</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="BC10" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.82</v>
+        <v>3.68</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="S11" t="n">
-        <v>4.25</v>
+        <v>3.02</v>
       </c>
       <c r="T11" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC11" t="n">
         <v>2.28</v>
       </c>
-      <c r="U11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W11" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>1.95</v>
-      </c>
       <c r="BD11" t="n">
-        <v>3.95</v>
+        <v>3.36</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,80 +2771,80 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="Q12" t="n">
         <v>3.7</v>
       </c>
       <c r="R12" t="n">
-        <v>4.04</v>
+        <v>4.8</v>
       </c>
       <c r="S12" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="U12" t="n">
+        <v>5</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN12" t="n">
         <v>2.12</v>
       </c>
-      <c r="T12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W12" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.68</v>
+        <v>1.96</v>
       </c>
       <c r="BD12" t="n">
-        <v>5.25</v>
+        <v>3.58</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.95</v>
+        <v>1.64</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,79 +2968,79 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,79 +3165,79 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>6.13</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,79 +3362,79 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="S15" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="T15" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="U15" t="n">
-        <v>5.2</v>
+        <v>7.01</v>
       </c>
       <c r="V15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W15" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AH15" t="n">
         <v>1.33</v>
       </c>
-      <c r="W15" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AI15" t="n">
-        <v>5.1</v>
+        <v>4.45</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.12</v>
+        <v>2.78</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.82</v>
+        <v>4.65</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.66</v>
+        <v>1.87</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3568,70 +3568,70 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.75</v>
+        <v>5.66</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.88</v>
+        <v>5.6</v>
       </c>
       <c r="R18" t="n">
-        <v>4.13</v>
+        <v>1.38</v>
       </c>
       <c r="S18" t="n">
-        <v>2.24</v>
+        <v>5.45</v>
       </c>
       <c r="T18" t="n">
-        <v>2.27</v>
+        <v>2.88</v>
       </c>
       <c r="U18" t="n">
-        <v>4.6</v>
+        <v>1.74</v>
       </c>
       <c r="V18" t="n">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="W18" t="n">
-        <v>3.15</v>
+        <v>4.75</v>
       </c>
       <c r="X18" t="n">
-        <v>2.52</v>
+        <v>1.77</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.51</v>
+        <v>1.91</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="AD18" t="n">
-        <v>4.31</v>
+        <v>8</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.58</v>
+        <v>1.24</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.14</v>
+        <v>3.6</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.68</v>
+        <v>1.76</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.46</v>
+        <v>1.93</v>
       </c>
       <c r="AI18" t="n">
-        <v>4.85</v>
+        <v>2.72</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.17</v>
+        <v>1.42</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.63</v>
+        <v>1.43</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.11</v>
+        <v>2.6</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.25</v>
+        <v>2.88</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.04</v>
+        <v>1.11</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4034,52 +4034,52 @@
         <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
         <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.88</v>
+        <v>1.57</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.33</v>
+        <v>5.75</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.86</v>
+        <v>2.3</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>6</v>
+        <v>1.83</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.9</v>
+        <v>3.6</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="S19" t="n">
-        <v>5.45</v>
+        <v>2.24</v>
       </c>
       <c r="T19" t="n">
-        <v>2.88</v>
+        <v>2.27</v>
       </c>
       <c r="U19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W19" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AX19" t="n">
         <v>1.74</v>
       </c>
-      <c r="V19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W19" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AG19" t="n">
+      <c r="AY19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AZ19" t="n">
         <v>1.76</v>
       </c>
-      <c r="AH19" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.46</v>
+        <v>1.88</v>
       </c>
       <c r="BD19" t="n">
-        <v>7.8</v>
+        <v>4.33</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.53</v>
+        <v>1.86</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.49</v>
+        <v>1.22</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,139 +4347,139 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>4.8</v>
+        <v>3.74</v>
       </c>
       <c r="Q20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="X20" t="n">
         <v>3.5</v>
       </c>
-      <c r="R20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S20" t="n">
-        <v>5.93</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W20" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="X20" t="n">
-        <v>3.25</v>
-      </c>
       <c r="Y20" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="Z20" t="n">
-        <v>7.2</v>
+        <v>8.1</v>
       </c>
       <c r="AA20" t="n">
         <v>1.03</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.91</v>
+        <v>2.4</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.97</v>
+        <v>2.68</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.87</v>
+        <v>1.48</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.58</v>
+        <v>5.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AI20" t="n">
-        <v>7</v>
+        <v>8.9</v>
       </c>
       <c r="AJ20" t="n">
         <v>1.04</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AM20" t="n">
-        <v>2.17</v>
+        <v>1.4</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.07</v>
+        <v>2.84</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="AT20" t="n">
-        <v>3.5</v>
+        <v>4.64</v>
       </c>
       <c r="AU20" t="n">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AZ20" t="n">
-        <v>4</v>
+        <v>2.43</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.32</v>
+        <v>1.81</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.17</v>
+        <v>2.8</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.28</v>
+        <v>2.75</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BH20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BI20" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,139 +4741,139 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="R22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U22" t="n">
         <v>2.05</v>
       </c>
-      <c r="S22" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2.85</v>
-      </c>
       <c r="V22" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="W22" t="n">
-        <v>2.37</v>
+        <v>2.59</v>
       </c>
       <c r="X22" t="n">
-        <v>3.58</v>
+        <v>3.25</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="Z22" t="n">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
       <c r="AA22" t="n">
         <v>1.03</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.39</v>
+        <v>2.91</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.72</v>
+        <v>1.97</v>
       </c>
       <c r="AF22" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AX22" t="n">
         <v>1.41</v>
       </c>
-      <c r="AG22" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AM22" t="n">
+      <c r="AY22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA22" t="n">
         <v>1.32</v>
       </c>
-      <c r="AN22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>3</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>1.81</v>
-      </c>
       <c r="BB22" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.7</v>
+        <v>2.17</v>
       </c>
       <c r="BD22" t="n">
-        <v>2.82</v>
+        <v>3.28</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="BG22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BH22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4938,55 +4938,55 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Q23" t="n">
-        <v>7.9</v>
+        <v>9.76</v>
       </c>
       <c r="R23" t="n">
-        <v>15</v>
+        <v>11.7</v>
       </c>
       <c r="S23" t="n">
         <v>1.44</v>
       </c>
       <c r="T23" t="n">
-        <v>3.62</v>
+        <v>3.8</v>
       </c>
       <c r="U23" t="n">
-        <v>10</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="W23" t="n">
-        <v>4.8</v>
+        <v>5.95</v>
       </c>
       <c r="X23" t="n">
         <v>1.68</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AB23" t="n">
         <v>1</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AD23" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AF23" t="n">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="AG23" t="n">
         <v>1.62</v>
@@ -4995,55 +4995,55 @@
         <v>2.28</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AK23" t="n">
         <v>1.67</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AM23" t="n">
         <v>1.02</v>
       </c>
       <c r="AN23" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.79</v>
+        <v>2.02</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.2</v>
+        <v>3.14</v>
       </c>
       <c r="AU23" t="n">
-        <v>4.2</v>
+        <v>3.28</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.05</v>
+        <v>2.35</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.33</v>
+        <v>1.85</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.86</v>
+        <v>1.65</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.55</v>
+        <v>1.27</v>
       </c>
       <c r="AZ23" t="n">
         <v>1.09</v>
@@ -5052,10 +5052,10 @@
         <v>8</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="BD23" t="n">
         <v>7.8</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.56</v>
+        <v>1.27</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.58</v>
+        <v>4.65</v>
       </c>
       <c r="R24" t="n">
-        <v>1.91</v>
+        <v>7.5</v>
       </c>
       <c r="S24" t="n">
-        <v>4.26</v>
+        <v>1.84</v>
       </c>
       <c r="T24" t="n">
-        <v>2.19</v>
+        <v>2.45</v>
       </c>
       <c r="U24" t="n">
-        <v>2.55</v>
+        <v>6.5</v>
       </c>
       <c r="V24" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W24" t="n">
-        <v>2.94</v>
+        <v>3.5</v>
       </c>
       <c r="X24" t="n">
-        <v>2.73</v>
+        <v>2.33</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="Z24" t="n">
-        <v>6.35</v>
+        <v>5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AB24" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AC24" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BF24" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>6.19</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>1.16</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.27</v>
+        <v>3.56</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.65</v>
+        <v>3.58</v>
       </c>
       <c r="R25" t="n">
-        <v>7.5</v>
+        <v>1.91</v>
       </c>
       <c r="S25" t="n">
-        <v>1.84</v>
+        <v>4.26</v>
       </c>
       <c r="T25" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AS25" t="n">
         <v>2.45</v>
       </c>
-      <c r="U25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="AJ25" t="n">
+      <c r="AT25" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BF25" t="n">
         <v>1.16</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>1.25</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R6" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="S6" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="T6" t="n">
         <v>2.22</v>
       </c>
       <c r="U6" t="n">
-        <v>4.4</v>
+        <v>4.78</v>
       </c>
       <c r="V6" t="n">
         <v>1.28</v>
       </c>
       <c r="W6" t="n">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="X6" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AA6" t="n">
         <v>1.12</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AD6" t="n">
-        <v>4.56</v>
+        <v>4.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AF6" t="n">
         <v>2.3</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="AH6" t="n">
         <v>1.46</v>
       </c>
       <c r="AI6" t="n">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AL6" t="n">
         <v>2.27</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="R7" t="n">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="S7" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="T7" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="U7" t="n">
-        <v>4</v>
+        <v>4.32</v>
       </c>
       <c r="V7" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W7" t="n">
-        <v>2.79</v>
+        <v>2.92</v>
       </c>
       <c r="X7" t="n">
-        <v>2.71</v>
+        <v>2.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.34</v>
+        <v>3.7</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.91</v>
+        <v>1.74</v>
       </c>
       <c r="AF7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AS7" t="n">
         <v>1.89</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AT7" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="AV7" t="n">
         <v>3.1</v>
       </c>
-      <c r="AH7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>2.88</v>
-      </c>
       <c r="AW7" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="AX7" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="BE7" t="n">
         <v>1.73</v>
       </c>
-      <c r="AY7" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.66</v>
-      </c>
       <c r="BF7" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="U8" t="n">
         <v>3.4</v>
       </c>
-      <c r="Q8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.46</v>
-      </c>
       <c r="V8" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W8" t="n">
-        <v>2.79</v>
+        <v>2.67</v>
       </c>
       <c r="X8" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.55</v>
+        <v>6.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AB8" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AE8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF8" t="n">
         <v>1.83</v>
       </c>
-      <c r="AF8" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AG8" t="n">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AI8" t="n">
-        <v>5.75</v>
+        <v>6.15</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.19</v>
+        <v>1.45</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.02</v>
+        <v>1.77</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.99</v>
+        <v>2.53</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.51</v>
+        <v>4.28</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.48</v>
+        <v>2.89</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.92</v>
+        <v>2.16</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.56</v>
+        <v>1.74</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3.55</v>
+        <v>2.12</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.5</v>
+        <v>2.12</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.82</v>
+        <v>3.7</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="R9" t="n">
-        <v>3.6</v>
+        <v>3.63</v>
       </c>
       <c r="S9" t="n">
-        <v>2.41</v>
+        <v>2.48</v>
       </c>
       <c r="T9" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW9" t="n">
         <v>2.16</v>
       </c>
-      <c r="U9" t="n">
-        <v>4.32</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>2.28</v>
-      </c>
       <c r="AX9" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="BA9" t="n">
-        <v>3.62</v>
+        <v>4.36</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.1</v>
+        <v>3.78</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,130 +2377,130 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q10" t="n">
         <v>3.4</v>
       </c>
       <c r="R10" t="n">
-        <v>2.77</v>
+        <v>1.85</v>
       </c>
       <c r="S10" t="n">
-        <v>3.02</v>
+        <v>3.9</v>
       </c>
       <c r="T10" t="n">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="U10" t="n">
-        <v>3.4</v>
+        <v>2.49</v>
       </c>
       <c r="V10" t="n">
         <v>1.36</v>
       </c>
       <c r="W10" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="X10" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="Z10" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AI10" t="n">
-        <v>6.15</v>
+        <v>5.1</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AL10" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AN10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ10" t="n">
         <v>1.45</v>
       </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AR10" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.53</v>
+        <v>2.99</v>
       </c>
       <c r="AU10" t="n">
-        <v>4.28</v>
+        <v>3.51</v>
       </c>
       <c r="AV10" t="n">
-        <v>2.89</v>
+        <v>2.51</v>
       </c>
       <c r="AW10" t="n">
-        <v>2.16</v>
+        <v>1.92</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.74</v>
+        <v>1.56</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AZ10" t="n">
-        <v>2.12</v>
+        <v>3.55</v>
       </c>
       <c r="BA10" t="n">
-        <v>2.12</v>
+        <v>1.5</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.68</v>
+        <v>3.78</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="BF10" t="n">
         <v>1.14</v>
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="Q11" t="n">
         <v>3.1</v>
       </c>
       <c r="R11" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="S11" t="n">
-        <v>3.02</v>
+        <v>3.48</v>
       </c>
       <c r="T11" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="U11" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="V11" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="W11" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="X11" t="n">
-        <v>2.95</v>
+        <v>3.19</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA11" t="n">
         <v>1.04</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AG11" t="n">
-        <v>3.34</v>
+        <v>3.45</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AI11" t="n">
-        <v>6.4</v>
+        <v>6.14</v>
       </c>
       <c r="AJ11" t="n">
         <v>1.05</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>2.12</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="BC11" t="n">
         <v>2.28</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2771,19 +2771,19 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="R12" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="S12" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="T12" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="U12" t="n">
         <v>5</v>
@@ -2792,7 +2792,7 @@
         <v>1.37</v>
       </c>
       <c r="W12" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="X12" t="n">
         <v>2.75</v>
@@ -2810,28 +2810,28 @@
         <v>1.01</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AD12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG12" t="n">
         <v>3.2</v>
       </c>
-      <c r="AE12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>3</v>
-      </c>
       <c r="AH12" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AI12" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AK12" t="n">
         <v>1.8</v>
@@ -2849,40 +2849,40 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="BB12" t="n">
         <v>1.21</v>
@@ -2894,7 +2894,7 @@
         <v>3.58</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="BF12" t="n">
         <v>1.14</v>
@@ -2968,22 +2968,22 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="R13" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="S13" t="n">
         <v>2.25</v>
       </c>
       <c r="T13" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="U13" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="V13" t="n">
         <v>1.28</v>
@@ -2992,10 +2992,10 @@
         <v>3.14</v>
       </c>
       <c r="X13" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Z13" t="n">
         <v>5.7</v>
@@ -3004,19 +3004,19 @@
         <v>1.08</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC13" t="n">
         <v>1.15</v>
       </c>
       <c r="AD13" t="n">
-        <v>4.7</v>
+        <v>4.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AG13" t="n">
         <v>2.3</v>
@@ -3028,13 +3028,13 @@
         <v>3.85</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="AM13" t="n">
         <v>1.21</v>
@@ -3046,55 +3046,55 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="BD13" t="n">
         <v>4.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3362,22 +3362,22 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="R15" t="n">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="S15" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="T15" t="n">
         <v>2.5</v>
       </c>
       <c r="U15" t="n">
-        <v>7.01</v>
+        <v>7.13</v>
       </c>
       <c r="V15" t="n">
         <v>1.28</v>
@@ -3398,7 +3398,7 @@
         <v>1.08</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC15" t="n">
         <v>1.15</v>
@@ -3407,10 +3407,10 @@
         <v>4.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.25</v>
+        <v>1.88</v>
       </c>
       <c r="AG15" t="n">
         <v>2.46</v>
@@ -3419,61 +3419,61 @@
         <v>1.33</v>
       </c>
       <c r="AI15" t="n">
-        <v>4.45</v>
+        <v>5.1</v>
       </c>
       <c r="AJ15" t="n">
         <v>1.14</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AM15" t="n">
         <v>1.17</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>6.71</v>
       </c>
       <c r="BB15" t="n">
         <v>1.12</v>
@@ -3604,13 +3604,13 @@
         <v>3.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="AH16" t="n">
         <v>1.29</v>
@@ -3628,7 +3628,7 @@
         <v>2</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AN16" t="n">
         <v>1.7</v>
@@ -3759,19 +3759,19 @@
         <v>1.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>4.61</v>
+        <v>4.16</v>
       </c>
       <c r="S17" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="T17" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>4.86</v>
+        <v>4.7</v>
       </c>
       <c r="V17" t="n">
         <v>1.38</v>
@@ -3780,55 +3780,55 @@
         <v>2.7</v>
       </c>
       <c r="X17" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>4.24</v>
+        <v>3.9</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AG17" t="n">
         <v>2.49</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AI17" t="n">
-        <v>4.85</v>
+        <v>4.4</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AL17" t="n">
         <v>2.15</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BC17" t="n">
         <v>1.83</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BE17" t="n">
         <v>1.87</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,139 +4347,139 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.74</v>
+        <v>4.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.9</v>
+        <v>3.75</v>
       </c>
       <c r="R20" t="n">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="S20" t="n">
-        <v>4.33</v>
+        <v>5.9</v>
       </c>
       <c r="T20" t="n">
-        <v>1.81</v>
+        <v>2.16</v>
       </c>
       <c r="U20" t="n">
-        <v>2.79</v>
+        <v>2.21</v>
       </c>
       <c r="V20" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="W20" t="n">
-        <v>2.22</v>
+        <v>2.59</v>
       </c>
       <c r="X20" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
       <c r="AA20" t="n">
         <v>1.03</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.4</v>
+        <v>2.83</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.68</v>
+        <v>2.12</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="AG20" t="n">
-        <v>5.25</v>
+        <v>3.58</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AI20" t="n">
-        <v>8.9</v>
+        <v>6.35</v>
       </c>
       <c r="AJ20" t="n">
         <v>1.04</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AN20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AY20" t="n">
         <v>1.25</v>
       </c>
-      <c r="AO20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>3</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AX20" t="n">
+      <c r="AZ20" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA20" t="n">
         <v>1.32</v>
       </c>
-      <c r="AY20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>1.81</v>
-      </c>
       <c r="BB20" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.75</v>
+        <v>3.28</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BH20" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,139 +4544,139 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>7.75</v>
+        <v>3.74</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="R21" t="n">
-        <v>1.49</v>
+        <v>2.05</v>
       </c>
       <c r="S21" t="n">
-        <v>8.9</v>
+        <v>4.33</v>
       </c>
       <c r="T21" t="n">
-        <v>1.98</v>
+        <v>1.81</v>
       </c>
       <c r="U21" t="n">
-        <v>2.2</v>
+        <v>2.79</v>
       </c>
       <c r="V21" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="W21" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="X21" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.9</v>
+        <v>8.1</v>
       </c>
       <c r="AA21" t="n">
         <v>1.03</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AG21" t="n">
         <v>5.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AI21" t="n">
-        <v>10</v>
+        <v>8.9</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.38</v>
+        <v>2.84</v>
       </c>
       <c r="AS21" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="AU21" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AV21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BA21" t="n">
         <v>1.81</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>1.3</v>
       </c>
       <c r="BB21" t="n">
         <v>1.4</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="BF21" t="n">
         <v>1.08</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="BH21" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,139 +4741,139 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>4.8</v>
+        <v>7.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="S22" t="n">
-        <v>5.93</v>
+        <v>8.9</v>
       </c>
       <c r="T22" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="U22" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="V22" t="n">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="W22" t="n">
-        <v>2.59</v>
+        <v>2.1</v>
       </c>
       <c r="X22" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="Z22" t="n">
-        <v>7.2</v>
+        <v>8.9</v>
       </c>
       <c r="AA22" t="n">
         <v>1.03</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.38</v>
+        <v>1.59</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.91</v>
+        <v>2.23</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.97</v>
+        <v>2.7</v>
       </c>
       <c r="AF22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AQ22" t="n">
         <v>1.87</v>
       </c>
-      <c r="AG22" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AR22" t="n">
-        <v>2.07</v>
+        <v>2.38</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.65</v>
+        <v>3.15</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>2.7</v>
+        <v>2.33</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.66</v>
+        <v>1.49</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.17</v>
+        <v>2.82</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.28</v>
+        <v>2.62</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI22" s="3" t="n">
         <v>46127.60416666666</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.27</v>
+        <v>3.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.65</v>
+        <v>3.64</v>
       </c>
       <c r="R24" t="n">
-        <v>7.5</v>
+        <v>1.94</v>
       </c>
       <c r="S24" t="n">
-        <v>1.84</v>
+        <v>4</v>
       </c>
       <c r="T24" t="n">
-        <v>2.45</v>
+        <v>2.19</v>
       </c>
       <c r="U24" t="n">
-        <v>6.5</v>
+        <v>2.55</v>
       </c>
       <c r="V24" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W24" t="n">
-        <v>3.5</v>
+        <v>2.94</v>
       </c>
       <c r="X24" t="n">
-        <v>2.33</v>
+        <v>2.82</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>5</v>
+        <v>6.35</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AD24" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.61</v>
+        <v>1.89</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.52</v>
+        <v>3.24</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.52</v>
+        <v>1.32</v>
       </c>
       <c r="AI24" t="n">
-        <v>4.51</v>
+        <v>5.6</v>
       </c>
       <c r="AJ24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BF24" t="n">
         <v>1.16</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>1.25</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.56</v>
+        <v>1.33</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.58</v>
+        <v>5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.91</v>
+        <v>7.81</v>
       </c>
       <c r="S25" t="n">
-        <v>4.26</v>
+        <v>1.76</v>
       </c>
       <c r="T25" t="n">
-        <v>2.19</v>
+        <v>2.5</v>
       </c>
       <c r="U25" t="n">
-        <v>2.55</v>
+        <v>5.51</v>
       </c>
       <c r="V25" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="W25" t="n">
-        <v>2.94</v>
+        <v>3.4</v>
       </c>
       <c r="X25" t="n">
-        <v>2.73</v>
+        <v>2.28</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="Z25" t="n">
-        <v>6.35</v>
+        <v>5.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AC25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BF25" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>6.19</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>1.16</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="R26" t="n">
-        <v>4.8</v>
+        <v>6.25</v>
       </c>
       <c r="S26" t="n">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="T26" t="n">
-        <v>3.1</v>
+        <v>2.35</v>
       </c>
       <c r="U26" t="n">
-        <v>4.65</v>
+        <v>7</v>
       </c>
       <c r="V26" t="n">
-        <v>1.14</v>
+        <v>1.34</v>
       </c>
       <c r="W26" t="n">
-        <v>4.7</v>
+        <v>2.9</v>
       </c>
       <c r="X26" t="n">
-        <v>1.83</v>
+        <v>2.63</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.98</v>
+        <v>1.48</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.24</v>
+        <v>6.75</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="AB26" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AD26" t="n">
-        <v>8</v>
+        <v>3.72</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.28</v>
+        <v>1.8</v>
       </c>
       <c r="AF26" t="n">
-        <v>3.75</v>
+        <v>2.07</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.72</v>
+        <v>2.99</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.1</v>
+        <v>1.33</v>
       </c>
       <c r="AI26" t="n">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="AJ26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AX26" t="n">
         <v>1.47</v>
       </c>
-      <c r="AK26" t="n">
+      <c r="AY26" t="n">
         <v>1.31</v>
       </c>
-      <c r="AL26" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
+      <c r="AZ26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BF26" t="n">
         <v>1.2</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>1.5</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="R27" t="n">
-        <v>7.25</v>
+        <v>4.64</v>
       </c>
       <c r="S27" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="T27" t="n">
-        <v>2.3</v>
+        <v>3.08</v>
       </c>
       <c r="U27" t="n">
-        <v>6.6</v>
+        <v>4.95</v>
       </c>
       <c r="V27" t="n">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="W27" t="n">
-        <v>3.29</v>
+        <v>6</v>
       </c>
       <c r="X27" t="n">
-        <v>2.63</v>
+        <v>1.81</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.47</v>
+        <v>2.07</v>
       </c>
       <c r="Z27" t="n">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.06</v>
+        <v>1.23</v>
       </c>
       <c r="AB27" t="n">
         <v>1.01</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.26</v>
+        <v>1.03</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.94</v>
+        <v>8.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.86</v>
+        <v>1.28</v>
       </c>
       <c r="AF27" t="n">
-        <v>2</v>
+        <v>3.75</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.88</v>
+        <v>1.77</v>
       </c>
       <c r="AH27" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AK27" t="n">
         <v>1.35</v>
       </c>
-      <c r="AI27" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AL27" t="n">
-        <v>1.79</v>
+        <v>3</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AN27" t="n">
-        <v>2.77</v>
+        <v>2.68</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AQ27" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR27" t="n">
         <v>1.52</v>
       </c>
-      <c r="AR27" t="n">
+      <c r="AS27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AZ27" t="n">
         <v>1.8</v>
       </c>
-      <c r="AS27" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>1.33</v>
-      </c>
       <c r="BA27" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.07</v>
+        <v>1.51</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.2</v>
+        <v>6.5</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.78</v>
+        <v>2.54</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.2</v>
+        <v>1.51</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G31" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI35"/>
+  <dimension ref="A1:BI36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.82</v>
+        <v>3.4</v>
       </c>
       <c r="Q7" t="n">
         <v>3.4</v>
       </c>
       <c r="R7" t="n">
-        <v>3.6</v>
+        <v>1.85</v>
       </c>
       <c r="S7" t="n">
-        <v>2.42</v>
+        <v>3.9</v>
       </c>
       <c r="T7" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="U7" t="n">
-        <v>4.32</v>
+        <v>2.49</v>
       </c>
       <c r="V7" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W7" t="n">
-        <v>2.92</v>
+        <v>2.75</v>
       </c>
       <c r="X7" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="Z7" t="n">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AB7" t="n">
         <v>1</v>
       </c>
       <c r="AC7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
         <v>1.22</v>
       </c>
-      <c r="AD7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AQ7" t="n">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.89</v>
+        <v>2.25</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.38</v>
+        <v>2.99</v>
       </c>
       <c r="AU7" t="n">
-        <v>4.66</v>
+        <v>3.51</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.1</v>
+        <v>2.51</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.28</v>
+        <v>1.92</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.81</v>
+        <v>1.56</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.51</v>
+        <v>1.3</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.47</v>
+        <v>3.55</v>
       </c>
       <c r="BA7" t="n">
-        <v>3.62</v>
+        <v>1.5</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.05</v>
+        <v>3.78</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.3</v>
+        <v>1.82</v>
       </c>
       <c r="Q8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="AV8" t="n">
         <v>3.1</v>
       </c>
-      <c r="R8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>2.89</v>
-      </c>
       <c r="AW8" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="AZ8" t="n">
-        <v>2.12</v>
+        <v>1.47</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.12</v>
+        <v>3.62</v>
       </c>
       <c r="BB8" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BF8" t="n">
         <v>1.2</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>1.14</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,130 +2377,130 @@
         </is>
       </c>
       <c r="P10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="U10" t="n">
         <v>3.4</v>
       </c>
-      <c r="Q10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.49</v>
-      </c>
       <c r="V10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.36</v>
       </c>
-      <c r="W10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.37</v>
-      </c>
       <c r="Z10" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AB10" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AF10" t="n">
         <v>1.83</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AH10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ10" t="n">
         <v>1.33</v>
       </c>
-      <c r="AI10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AR10" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AS10" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.99</v>
+        <v>2.53</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.51</v>
+        <v>4.28</v>
       </c>
       <c r="AV10" t="n">
-        <v>2.51</v>
+        <v>2.89</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.92</v>
+        <v>2.16</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.56</v>
+        <v>1.74</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AZ10" t="n">
-        <v>3.55</v>
+        <v>2.12</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.5</v>
+        <v>2.12</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="BF10" t="n">
         <v>1.14</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,130 +2771,130 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD12" t="n">
         <v>3.5</v>
       </c>
-      <c r="R12" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U12" t="n">
-        <v>5</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>3.35</v>
-      </c>
       <c r="AE12" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AI12" t="n">
-        <v>5.1</v>
+        <v>5.95</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AN12" t="n">
-        <v>2.12</v>
+        <v>1.7</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
         <v>1.17</v>
       </c>
-      <c r="AQ12" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AW12" t="n">
+      <c r="BC12" t="n">
         <v>2.03</v>
       </c>
-      <c r="AX12" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>1.96</v>
-      </c>
       <c r="BD12" t="n">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="BF12" t="n">
         <v>1.14</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,22 +2968,22 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="R13" t="n">
-        <v>3.7</v>
+        <v>6.5</v>
       </c>
       <c r="S13" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="T13" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="U13" t="n">
-        <v>4.3</v>
+        <v>7.13</v>
       </c>
       <c r="V13" t="n">
         <v>1.28</v>
@@ -2992,109 +2992,109 @@
         <v>3.14</v>
       </c>
       <c r="X13" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="AA13" t="n">
         <v>1.08</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC13" t="n">
         <v>1.15</v>
       </c>
       <c r="AD13" t="n">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.53</v>
+        <v>1.76</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.4</v>
+        <v>1.88</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AI13" t="n">
-        <v>3.85</v>
+        <v>5.1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.56</v>
+        <v>1.77</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.22</v>
+        <v>1.82</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.91</v>
+        <v>2.77</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.28</v>
+        <v>2.39</v>
       </c>
       <c r="AU13" t="n">
-        <v>4.96</v>
+        <v>4.62</v>
       </c>
       <c r="AV13" t="n">
-        <v>3.34</v>
+        <v>3.07</v>
       </c>
       <c r="AW13" t="n">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="AX13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="BE13" t="n">
         <v>1.87</v>
       </c>
-      <c r="AY13" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.85</v>
-      </c>
       <c r="BF13" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>7.13</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>6.71</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S16" t="n">
-        <v>2.53</v>
+        <v>2.25</v>
       </c>
       <c r="T16" t="n">
-        <v>2.09</v>
+        <v>2.35</v>
       </c>
       <c r="U16" t="n">
-        <v>4.23</v>
+        <v>4.3</v>
       </c>
       <c r="V16" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="W16" t="n">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="X16" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="Z16" t="n">
-        <v>6.85</v>
+        <v>5.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AB16" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="AG16" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AI16" t="n">
-        <v>5.95</v>
+        <v>3.85</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AK16" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC16" t="n">
         <v>1.68</v>
       </c>
-      <c r="AL16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>2.03</v>
-      </c>
       <c r="BD16" t="n">
-        <v>3.94</v>
+        <v>4.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,139 +4544,139 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.74</v>
+        <v>7.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>2.05</v>
+        <v>1.49</v>
       </c>
       <c r="S21" t="n">
-        <v>4.33</v>
+        <v>8.9</v>
       </c>
       <c r="T21" t="n">
-        <v>1.81</v>
+        <v>1.98</v>
       </c>
       <c r="U21" t="n">
-        <v>2.79</v>
+        <v>2.2</v>
       </c>
       <c r="V21" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="W21" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="X21" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.1</v>
+        <v>8.9</v>
       </c>
       <c r="AA21" t="n">
         <v>1.03</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AG21" t="n">
         <v>5.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AI21" t="n">
-        <v>8.9</v>
+        <v>10</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.84</v>
+        <v>2.38</v>
       </c>
       <c r="AS21" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="AT21" t="n">
-        <v>4.64</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2.43</v>
+        <v>3.7</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.81</v>
+        <v>1.3</v>
       </c>
       <c r="BB21" t="n">
         <v>1.4</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BF21" t="n">
         <v>1.08</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH21" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,139 +4741,139 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>7.75</v>
+        <v>3.74</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="R22" t="n">
-        <v>1.49</v>
+        <v>2.05</v>
       </c>
       <c r="S22" t="n">
-        <v>8.9</v>
+        <v>4.33</v>
       </c>
       <c r="T22" t="n">
-        <v>1.98</v>
+        <v>1.81</v>
       </c>
       <c r="U22" t="n">
-        <v>2.2</v>
+        <v>2.79</v>
       </c>
       <c r="V22" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="W22" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="X22" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z22" t="n">
-        <v>8.9</v>
+        <v>8.1</v>
       </c>
       <c r="AA22" t="n">
         <v>1.03</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AG22" t="n">
         <v>5.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AI22" t="n">
-        <v>10</v>
+        <v>8.9</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="AO22" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.38</v>
+        <v>2.84</v>
       </c>
       <c r="AS22" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="AU22" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AV22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BA22" t="n">
         <v>1.81</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>1.3</v>
       </c>
       <c r="BB22" t="n">
         <v>1.4</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BD22" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="BF22" t="n">
         <v>1.08</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="BH22" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="BI22" s="3" t="n">
         <v>46127.60416666666</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.9</v>
+        <v>1.74</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.64</v>
+        <v>3.35</v>
       </c>
       <c r="R24" t="n">
-        <v>1.94</v>
+        <v>3.75</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>2.34</v>
       </c>
       <c r="T24" t="n">
-        <v>2.19</v>
+        <v>2.32</v>
       </c>
       <c r="U24" t="n">
-        <v>2.55</v>
+        <v>4.89</v>
       </c>
       <c r="V24" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W24" t="n">
-        <v>2.94</v>
+        <v>2.77</v>
       </c>
       <c r="X24" t="n">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z24" t="n">
-        <v>6.35</v>
+        <v>5.9</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.3</v>
+        <v>3.49</v>
       </c>
       <c r="AE24" t="n">
         <v>1.89</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="AH24" t="n">
         <v>1.32</v>
       </c>
       <c r="AI24" t="n">
-        <v>5.6</v>
+        <v>6.37</v>
       </c>
       <c r="AJ24" t="n">
         <v>1.08</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AL24" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.32</v>
+        <v>1.52</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="AU24" t="n">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AY24" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BF24" t="n">
         <v>1.2</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>1.16</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.33</v>
+        <v>3.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>5</v>
+        <v>3.64</v>
       </c>
       <c r="R25" t="n">
-        <v>7.81</v>
+        <v>1.94</v>
       </c>
       <c r="S25" t="n">
-        <v>1.76</v>
+        <v>4</v>
       </c>
       <c r="T25" t="n">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="U25" t="n">
-        <v>5.51</v>
+        <v>2.55</v>
       </c>
       <c r="V25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC25" t="n">
         <v>1.25</v>
       </c>
-      <c r="W25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AD25" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.61</v>
+        <v>1.89</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.21</v>
+        <v>1.89</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.52</v>
+        <v>3.24</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.52</v>
+        <v>1.32</v>
       </c>
       <c r="AI25" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="AJ25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BF25" t="n">
         <v>1.16</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>1.25</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5476,12 +5476,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="Q26" t="n">
+        <v>5</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U26" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD26" t="n">
         <v>4.4</v>
       </c>
-      <c r="R26" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="S26" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U26" t="n">
-        <v>7</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W26" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>3.72</v>
-      </c>
       <c r="AE26" t="n">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.07</v>
+        <v>2.21</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.99</v>
+        <v>2.52</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="AI26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BA26" t="n">
         <v>5.5</v>
       </c>
-      <c r="AJ26" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>3.6</v>
-      </c>
       <c r="BB26" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.07</v>
+        <v>1.82</v>
       </c>
       <c r="BD26" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
         <v>0</v>
       </c>
       <c r="BI26" s="3" t="n">
-        <v>46127.66666666666</v>
+        <v>46127.65625</v>
       </c>
     </row>
     <row r="27">
@@ -5870,12 +5870,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6058,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="BI28" s="3" t="n">
-        <v>46127.72916666666</v>
+        <v>46127.66666666666</v>
       </c>
     </row>
     <row r="29">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6658,7 +6658,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6846,7 +6846,7 @@
         <v>0</v>
       </c>
       <c r="BI32" s="3" t="n">
-        <v>46127.875</v>
+        <v>46127.72916666666</v>
       </c>
     </row>
     <row r="33">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7249,27 +7249,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7437,6 +7437,203 @@
         <v>0</v>
       </c>
       <c r="BI35" s="3" t="n">
+        <v>46127.875</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>46127</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Los Angeles II</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Portland Timbers II</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI36" s="3" t="n">
         <v>46127.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="Q6" t="n">
         <v>3.7</v>
       </c>
       <c r="R6" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="S6" t="n">
         <v>2.23</v>
@@ -1619,7 +1619,7 @@
         <v>1.51</v>
       </c>
       <c r="Z6" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AA6" t="n">
         <v>1.12</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,40 +2180,40 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R9" t="n">
-        <v>3.63</v>
+        <v>2.7</v>
       </c>
       <c r="S9" t="n">
-        <v>2.48</v>
+        <v>3.02</v>
       </c>
       <c r="T9" t="n">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="U9" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="V9" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W9" t="n">
-        <v>2.79</v>
+        <v>2.67</v>
       </c>
       <c r="X9" t="n">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AB9" t="n">
         <v>1.01</v>
@@ -2222,37 +2222,37 @@
         <v>1.26</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AG9" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AI9" t="n">
-        <v>5.9</v>
+        <v>6.15</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.73</v>
+        <v>1.45</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2264,46 +2264,46 @@
         <v>1.33</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AU9" t="n">
-        <v>4.26</v>
+        <v>4.28</v>
       </c>
       <c r="AV9" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="AW9" t="n">
         <v>2.16</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.36</v>
+        <v>2.12</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.36</v>
+        <v>2.12</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="BF9" t="n">
         <v>1.14</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,40 +2377,40 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R10" t="n">
-        <v>2.7</v>
+        <v>3.63</v>
       </c>
       <c r="S10" t="n">
-        <v>3.02</v>
+        <v>2.48</v>
       </c>
       <c r="T10" t="n">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="U10" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="V10" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W10" t="n">
-        <v>2.67</v>
+        <v>2.79</v>
       </c>
       <c r="X10" t="n">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AB10" t="n">
         <v>1.01</v>
@@ -2419,37 +2419,37 @@
         <v>1.26</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AI10" t="n">
-        <v>6.15</v>
+        <v>5.9</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AL10" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.45</v>
+        <v>1.73</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2461,46 +2461,46 @@
         <v>1.33</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>4.28</v>
+        <v>4.26</v>
       </c>
       <c r="AV10" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="AW10" t="n">
         <v>2.16</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AZ10" t="n">
-        <v>2.12</v>
+        <v>1.36</v>
       </c>
       <c r="BA10" t="n">
-        <v>2.12</v>
+        <v>4.36</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.7</v>
+        <v>3.78</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="BF10" t="n">
         <v>1.14</v>
@@ -2574,73 +2574,73 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="S11" t="n">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="T11" t="n">
         <v>1.95</v>
       </c>
       <c r="U11" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="V11" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W11" t="n">
-        <v>2.53</v>
+        <v>2.73</v>
       </c>
       <c r="X11" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z11" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AB11" t="n">
         <v>1.04</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="AG11" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AI11" t="n">
         <v>6.14</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AL11" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AM11" t="n">
         <v>1.34</v>
@@ -2697,7 +2697,7 @@
         <v>3.3</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="BF11" t="n">
         <v>1.12</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,37 +2968,37 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="R13" t="n">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="S13" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="U13" t="n">
-        <v>7.13</v>
+        <v>5</v>
       </c>
       <c r="V13" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="W13" t="n">
-        <v>3.14</v>
+        <v>2.8</v>
       </c>
       <c r="X13" t="n">
-        <v>2.36</v>
+        <v>2.75</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA13" t="n">
         <v>1.08</v>
@@ -3007,94 +3007,94 @@
         <v>1.01</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AD13" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.46</v>
+        <v>3.2</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AI13" t="n">
         <v>5.1</v>
       </c>
       <c r="AJ13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BF13" t="n">
         <v>1.14</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>6.71</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>1.22</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>7.13</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>6.71</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3756,19 +3756,19 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="R17" t="n">
-        <v>4.16</v>
+        <v>3.5</v>
       </c>
       <c r="S17" t="n">
         <v>2.47</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="U17" t="n">
         <v>4.7</v>
@@ -3828,7 +3828,7 @@
         <v>1.25</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>5.66</v>
+        <v>1.83</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.6</v>
+        <v>3.6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.38</v>
+        <v>3.9</v>
       </c>
       <c r="S18" t="n">
-        <v>5.45</v>
+        <v>2.24</v>
       </c>
       <c r="T18" t="n">
-        <v>2.88</v>
+        <v>2.27</v>
       </c>
       <c r="U18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W18" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AX18" t="n">
         <v>1.74</v>
       </c>
-      <c r="V18" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W18" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AG18" t="n">
+      <c r="AY18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AZ18" t="n">
         <v>1.76</v>
       </c>
-      <c r="AH18" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.75</v>
+        <v>4.33</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.3</v>
+        <v>1.86</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.83</v>
+        <v>5.66</v>
       </c>
       <c r="Q19" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W19" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF19" t="n">
         <v>3.6</v>
       </c>
-      <c r="R19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="U19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W19" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AG19" t="n">
-        <v>2.7</v>
+        <v>1.76</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.45</v>
+        <v>1.93</v>
       </c>
       <c r="AI19" t="n">
-        <v>4.5</v>
+        <v>2.72</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.13</v>
+        <v>1.42</v>
       </c>
       <c r="AK19" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BC19" t="n">
         <v>1.57</v>
       </c>
-      <c r="AL19" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>1.88</v>
-      </c>
       <c r="BD19" t="n">
-        <v>4.33</v>
+        <v>5.75</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.86</v>
+        <v>2.3</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,139 +4347,139 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>4.8</v>
+        <v>7.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="S20" t="n">
-        <v>5.9</v>
+        <v>8.9</v>
       </c>
       <c r="T20" t="n">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="U20" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="V20" t="n">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="W20" t="n">
-        <v>2.59</v>
+        <v>2.1</v>
       </c>
       <c r="X20" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="Z20" t="n">
-        <v>7.2</v>
+        <v>8.9</v>
       </c>
       <c r="AA20" t="n">
         <v>1.03</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.38</v>
+        <v>1.59</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.83</v>
+        <v>2.23</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.12</v>
+        <v>2.7</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.58</v>
+        <v>5.25</v>
       </c>
       <c r="AH20" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AO20" t="n">
         <v>1.26</v>
       </c>
-      <c r="AI20" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
       <c r="AP20" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.07</v>
+        <v>2.38</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.65</v>
+        <v>3.15</v>
       </c>
       <c r="AT20" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>2.7</v>
+        <v>2.33</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.66</v>
+        <v>1.49</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.3</v>
+        <v>2.82</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.28</v>
+        <v>2.62</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI20" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,139 +4544,139 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>7.75</v>
+        <v>3.74</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="R21" t="n">
-        <v>1.49</v>
+        <v>2.05</v>
       </c>
       <c r="S21" t="n">
-        <v>8.9</v>
+        <v>4.33</v>
       </c>
       <c r="T21" t="n">
-        <v>1.98</v>
+        <v>1.81</v>
       </c>
       <c r="U21" t="n">
-        <v>2.2</v>
+        <v>2.79</v>
       </c>
       <c r="V21" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="W21" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="X21" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.9</v>
+        <v>8.1</v>
       </c>
       <c r="AA21" t="n">
         <v>1.03</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AG21" t="n">
         <v>5.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AI21" t="n">
-        <v>10</v>
+        <v>8.9</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.38</v>
+        <v>2.84</v>
       </c>
       <c r="AS21" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="AU21" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AV21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BA21" t="n">
         <v>1.81</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>1.3</v>
       </c>
       <c r="BB21" t="n">
         <v>1.4</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="BF21" t="n">
         <v>1.08</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="BH21" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,139 +4741,139 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.74</v>
+        <v>5.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="R22" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="S22" t="n">
-        <v>4.33</v>
+        <v>6.38</v>
       </c>
       <c r="T22" t="n">
-        <v>1.81</v>
+        <v>2.11</v>
       </c>
       <c r="U22" t="n">
-        <v>2.79</v>
+        <v>2.12</v>
       </c>
       <c r="V22" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="W22" t="n">
-        <v>2.22</v>
+        <v>2.62</v>
       </c>
       <c r="X22" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="Z22" t="n">
-        <v>8.1</v>
+        <v>7.1</v>
       </c>
       <c r="AA22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB22" t="n">
         <v>1.03</v>
       </c>
-      <c r="AB22" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AC22" t="n">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.4</v>
+        <v>3.01</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.68</v>
+        <v>2.09</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AG22" t="n">
-        <v>5.25</v>
+        <v>3.58</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AI22" t="n">
-        <v>8.9</v>
+        <v>6.85</v>
       </c>
       <c r="AJ22" t="n">
         <v>1.04</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AN22" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AY22" t="n">
         <v>1.25</v>
       </c>
-      <c r="AO22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>3</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AX22" t="n">
+      <c r="AZ22" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA22" t="n">
         <v>1.32</v>
       </c>
-      <c r="AY22" t="n">
+      <c r="BB22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BF22" t="n">
         <v>1.11</v>
       </c>
-      <c r="AZ22" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>1.08</v>
-      </c>
       <c r="BG22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BH22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
         <v>46127.60416666666</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.74</v>
+        <v>3.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.35</v>
+        <v>3.64</v>
       </c>
       <c r="R24" t="n">
-        <v>3.75</v>
+        <v>1.94</v>
       </c>
       <c r="S24" t="n">
-        <v>2.34</v>
+        <v>4</v>
       </c>
       <c r="T24" t="n">
-        <v>2.32</v>
+        <v>2.19</v>
       </c>
       <c r="U24" t="n">
-        <v>4.89</v>
+        <v>2.55</v>
       </c>
       <c r="V24" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W24" t="n">
-        <v>2.77</v>
+        <v>2.94</v>
       </c>
       <c r="X24" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>5.9</v>
+        <v>6.35</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.49</v>
+        <v>3.3</v>
       </c>
       <c r="AE24" t="n">
         <v>1.89</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="AH24" t="n">
         <v>1.32</v>
       </c>
       <c r="AI24" t="n">
-        <v>6.37</v>
+        <v>5.6</v>
       </c>
       <c r="AJ24" t="n">
         <v>1.08</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.52</v>
+        <v>1.32</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.71</v>
+        <v>3.72</v>
       </c>
       <c r="AU24" t="n">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.39</v>
+        <v>2.4</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.76</v>
+        <v>1.63</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.9</v>
+        <v>1.74</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.64</v>
+        <v>3.35</v>
       </c>
       <c r="R25" t="n">
-        <v>1.94</v>
+        <v>3.75</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>2.34</v>
       </c>
       <c r="T25" t="n">
-        <v>2.19</v>
+        <v>2.32</v>
       </c>
       <c r="U25" t="n">
-        <v>2.55</v>
+        <v>4.89</v>
       </c>
       <c r="V25" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W25" t="n">
-        <v>2.94</v>
+        <v>2.77</v>
       </c>
       <c r="X25" t="n">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z25" t="n">
-        <v>6.35</v>
+        <v>5.9</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.3</v>
+        <v>3.49</v>
       </c>
       <c r="AE25" t="n">
         <v>1.89</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="AH25" t="n">
         <v>1.32</v>
       </c>
       <c r="AI25" t="n">
-        <v>5.6</v>
+        <v>6.37</v>
       </c>
       <c r="AJ25" t="n">
         <v>1.08</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AL25" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.32</v>
+        <v>1.52</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR25" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="AT25" t="n">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="AU25" t="n">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AY25" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BF25" t="n">
         <v>1.2</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>1.16</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="R27" t="n">
-        <v>4.64</v>
+        <v>6.25</v>
       </c>
       <c r="S27" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="T27" t="n">
-        <v>3.08</v>
+        <v>2.35</v>
       </c>
       <c r="U27" t="n">
-        <v>4.95</v>
+        <v>7</v>
       </c>
       <c r="V27" t="n">
-        <v>1.11</v>
+        <v>1.34</v>
       </c>
       <c r="W27" t="n">
-        <v>6</v>
+        <v>2.9</v>
       </c>
       <c r="X27" t="n">
-        <v>1.81</v>
+        <v>2.63</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.07</v>
+        <v>1.48</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.65</v>
+        <v>6.75</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="AB27" t="n">
         <v>1.01</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="AD27" t="n">
-        <v>8.5</v>
+        <v>3.72</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.28</v>
+        <v>1.8</v>
       </c>
       <c r="AF27" t="n">
-        <v>3.75</v>
+        <v>2.07</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.77</v>
+        <v>2.99</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.15</v>
+        <v>1.33</v>
       </c>
       <c r="AI27" t="n">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="AJ27" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AX27" t="n">
         <v>1.47</v>
       </c>
-      <c r="AK27" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AQ27" t="n">
+      <c r="AY27" t="n">
         <v>1.31</v>
       </c>
-      <c r="AR27" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AZ27" t="n">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="BA27" t="n">
-        <v>2.63</v>
+        <v>3.6</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.51</v>
+        <v>2.07</v>
       </c>
       <c r="BD27" t="n">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="BE27" t="n">
-        <v>2.54</v>
+        <v>1.78</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.51</v>
+        <v>1.2</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="R28" t="n">
-        <v>6.25</v>
+        <v>4.64</v>
       </c>
       <c r="S28" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="T28" t="n">
-        <v>2.35</v>
+        <v>3.08</v>
       </c>
       <c r="U28" t="n">
-        <v>7</v>
+        <v>4.95</v>
       </c>
       <c r="V28" t="n">
-        <v>1.34</v>
+        <v>1.11</v>
       </c>
       <c r="W28" t="n">
-        <v>2.9</v>
+        <v>6</v>
       </c>
       <c r="X28" t="n">
-        <v>2.63</v>
+        <v>1.81</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.48</v>
+        <v>2.07</v>
       </c>
       <c r="Z28" t="n">
-        <v>6.75</v>
+        <v>3.65</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="AB28" t="n">
         <v>1.01</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.22</v>
+        <v>1.03</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.72</v>
+        <v>8.5</v>
       </c>
       <c r="AE28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AZ28" t="n">
         <v>1.8</v>
       </c>
-      <c r="AF28" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>1.33</v>
-      </c>
       <c r="BA28" t="n">
-        <v>3.6</v>
+        <v>2.63</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.07</v>
+        <v>1.51</v>
       </c>
       <c r="BD28" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.78</v>
+        <v>2.54</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.2</v>
+        <v>1.51</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G35" t="n">

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="R2" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="S2" t="n">
         <v>3.25</v>
@@ -837,16 +837,16 @@
         <v>1.08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.47</v>
+        <v>3.3</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AF2" t="n">
         <v>1.8</v>
@@ -855,16 +855,16 @@
         <v>3.24</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AI2" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AL2" t="n">
         <v>2</v>
@@ -885,7 +885,7 @@
         <v>1.77</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AS2" t="n">
         <v>2.95</v>
@@ -912,7 +912,7 @@
         <v>1.98</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.08</v>
+        <v>2.29</v>
       </c>
       <c r="BB2" t="n">
         <v>1.22</v>
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3.4</v>
+        <v>1.82</v>
       </c>
       <c r="Q7" t="n">
         <v>3.4</v>
       </c>
       <c r="R7" t="n">
-        <v>1.85</v>
+        <v>3.66</v>
       </c>
       <c r="S7" t="n">
-        <v>3.9</v>
+        <v>2.42</v>
       </c>
       <c r="T7" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="U7" t="n">
-        <v>2.49</v>
+        <v>4.32</v>
       </c>
       <c r="V7" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W7" t="n">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="X7" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AB7" t="n">
         <v>1</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.08</v>
+        <v>2.81</v>
       </c>
       <c r="AH7" t="n">
         <v>1.33</v>
       </c>
       <c r="AI7" t="n">
-        <v>5.1</v>
+        <v>5.25</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.21</v>
+        <v>1.77</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.79</v>
+        <v>1.51</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.99</v>
+        <v>2.39</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.51</v>
+        <v>4.88</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.51</v>
+        <v>3.2</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.92</v>
+        <v>2.34</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.56</v>
+        <v>1.83</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="AZ7" t="n">
-        <v>3.55</v>
+        <v>1.41</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.5</v>
+        <v>3.95</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.78</v>
+        <v>4.05</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,76 +1983,76 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="Q8" t="n">
         <v>3.4</v>
       </c>
       <c r="R8" t="n">
-        <v>3.6</v>
+        <v>3.63</v>
       </c>
       <c r="S8" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="T8" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="U8" t="n">
-        <v>4.32</v>
+        <v>4</v>
       </c>
       <c r="V8" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W8" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="X8" t="n">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="Z8" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AB8" t="n">
         <v>1</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.7</v>
+        <v>3.34</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AI8" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AN8" t="n">
         <v>1.77</v>
@@ -2064,52 +2064,52 @@
         <v>1.11</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>4.66</v>
+        <v>4.62</v>
       </c>
       <c r="AV8" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="BA8" t="n">
-        <v>3.62</v>
+        <v>4.34</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.05</v>
+        <v>3.82</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2186,7 +2186,7 @@
         <v>3.1</v>
       </c>
       <c r="R9" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="S9" t="n">
         <v>3.02</v>
@@ -2195,7 +2195,7 @@
         <v>2.01</v>
       </c>
       <c r="U9" t="n">
-        <v>3.4</v>
+        <v>3.56</v>
       </c>
       <c r="V9" t="n">
         <v>1.38</v>
@@ -2207,10 +2207,10 @@
         <v>2.8</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.9</v>
+        <v>6.95</v>
       </c>
       <c r="AA9" t="n">
         <v>1.04</v>
@@ -2228,7 +2228,7 @@
         <v>1.9</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG9" t="n">
         <v>3.14</v>
@@ -2252,55 +2252,55 @@
         <v>1.27</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.77</v>
+        <v>1.56</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.53</v>
+        <v>2.42</v>
       </c>
       <c r="AU9" t="n">
-        <v>4.28</v>
+        <v>4.54</v>
       </c>
       <c r="AV9" t="n">
-        <v>2.89</v>
+        <v>3.03</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AZ9" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BC9" t="n">
         <v>2.1</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="BE9" t="n">
         <v>1.64</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,22 +2377,22 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.91</v>
+        <v>3.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.2</v>
+        <v>3.54</v>
       </c>
       <c r="R10" t="n">
-        <v>3.63</v>
+        <v>1.83</v>
       </c>
       <c r="S10" t="n">
-        <v>2.48</v>
+        <v>3.95</v>
       </c>
       <c r="T10" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="U10" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="V10" t="n">
         <v>1.35</v>
@@ -2401,13 +2401,13 @@
         <v>2.79</v>
       </c>
       <c r="X10" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.7</v>
+        <v>6.55</v>
       </c>
       <c r="AA10" t="n">
         <v>1.05</v>
@@ -2416,94 +2416,94 @@
         <v>1.01</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AD10" t="n">
         <v>3.34</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AI10" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="AJ10" t="n">
         <v>1.07</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.73</v>
+        <v>1.17</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.61</v>
+        <v>1.97</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.5</v>
+        <v>2.92</v>
       </c>
       <c r="AU10" t="n">
-        <v>4.26</v>
+        <v>3.68</v>
       </c>
       <c r="AV10" t="n">
-        <v>2.88</v>
+        <v>2.51</v>
       </c>
       <c r="AW10" t="n">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.36</v>
+        <v>3.4</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.36</v>
+        <v>1.53</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BC10" t="n">
         <v>2.05</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.78</v>
+        <v>3.82</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2583,103 +2583,103 @@
         <v>2.5</v>
       </c>
       <c r="S11" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T11" t="n">
         <v>1.95</v>
       </c>
       <c r="U11" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="V11" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W11" t="n">
-        <v>2.73</v>
+        <v>2.39</v>
       </c>
       <c r="X11" t="n">
         <v>3.2</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AA11" t="n">
         <v>1.03</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.11</v>
+        <v>2.27</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG11" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AI11" t="n">
         <v>6.14</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AZ11" t="n">
         <v>1.92</v>
@@ -2688,19 +2688,19 @@
         <v>2.12</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.28</v>
+        <v>2.39</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="S12" t="n">
-        <v>2.53</v>
+        <v>1.8</v>
       </c>
       <c r="T12" t="n">
-        <v>2.09</v>
+        <v>2.5</v>
       </c>
       <c r="U12" t="n">
-        <v>4.23</v>
+        <v>7.18</v>
       </c>
       <c r="V12" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="W12" t="n">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="X12" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.85</v>
+        <v>5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AB12" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="AG12" t="n">
-        <v>3</v>
+        <v>2.46</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="AI12" t="n">
-        <v>5.95</v>
+        <v>5.1</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AL12" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AM12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BF12" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>1.14</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2971,37 +2971,37 @@
         <v>1.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R13" t="n">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="S13" t="n">
         <v>2.15</v>
       </c>
       <c r="T13" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="U13" t="n">
         <v>5</v>
       </c>
       <c r="V13" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W13" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="X13" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Z13" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AB13" t="n">
         <v>1.01</v>
@@ -3010,34 +3010,34 @@
         <v>1.28</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="AE13" t="n">
         <v>1.85</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AI13" t="n">
         <v>5.1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AK13" t="n">
         <v>1.8</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AN13" t="n">
         <v>2.12</v>
@@ -3046,55 +3046,55 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AQ13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AY13" t="n">
         <v>1.39</v>
       </c>
-      <c r="AR13" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AW13" t="n">
+      <c r="AZ13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BC13" t="n">
         <v>2.03</v>
       </c>
-      <c r="AX13" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>1.96</v>
-      </c>
       <c r="BD13" t="n">
-        <v>3.58</v>
+        <v>3.78</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.83</v>
+        <v>2.53</v>
       </c>
       <c r="T15" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U15" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="X15" t="n">
         <v>2.5</v>
       </c>
-      <c r="U15" t="n">
-        <v>7.13</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W15" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.36</v>
-      </c>
       <c r="Y15" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="Z15" t="n">
-        <v>5</v>
+        <v>6.85</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AD15" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.46</v>
+        <v>3</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AI15" t="n">
-        <v>5.1</v>
+        <v>5.95</v>
       </c>
       <c r="AJ15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BF15" t="n">
         <v>1.14</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>6.71</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>1.22</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q16" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R16" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W16" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AF16" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Q18" t="n">
         <v>3.6</v>
       </c>
       <c r="R18" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="S18" t="n">
         <v>2.24</v>
@@ -3983,10 +3983,10 @@
         <v>1.49</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AB18" t="n">
         <v>1.04</v>
@@ -3995,16 +3995,16 @@
         <v>1.18</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="AH18" t="n">
         <v>1.45</v>
@@ -4013,7 +4013,7 @@
         <v>4.5</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AK18" t="n">
         <v>1.57</v>
@@ -4025,7 +4025,7 @@
         <v>1.25</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4079,7 +4079,7 @@
         <v>1.86</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4150,40 +4150,40 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>5.66</v>
+        <v>6</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.6</v>
+        <v>5.25</v>
       </c>
       <c r="R19" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S19" t="n">
-        <v>5.45</v>
+        <v>5.35</v>
       </c>
       <c r="T19" t="n">
         <v>2.88</v>
       </c>
       <c r="U19" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V19" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W19" t="n">
         <v>4.75</v>
       </c>
       <c r="X19" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AB19" t="n">
         <v>1.01</v>
@@ -4192,13 +4192,13 @@
         <v>1.03</v>
       </c>
       <c r="AD19" t="n">
-        <v>8</v>
+        <v>6.85</v>
       </c>
       <c r="AE19" t="n">
         <v>1.24</v>
       </c>
       <c r="AF19" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AG19" t="n">
         <v>1.76</v>
@@ -4207,7 +4207,7 @@
         <v>1.93</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="AJ19" t="n">
         <v>1.42</v>
@@ -4219,10 +4219,10 @@
         <v>2.6</v>
       </c>
       <c r="AM19" t="n">
-        <v>2.88</v>
+        <v>1.14</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.75</v>
+        <v>7.8</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.3</v>
+        <v>2.53</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4750,64 +4750,64 @@
         <v>1.57</v>
       </c>
       <c r="S22" t="n">
-        <v>6.38</v>
+        <v>6.53</v>
       </c>
       <c r="T22" t="n">
-        <v>2.11</v>
+        <v>2.03</v>
       </c>
       <c r="U22" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="V22" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="W22" t="n">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="X22" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>7.1</v>
+        <v>7.8</v>
       </c>
       <c r="AA22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB22" t="n">
         <v>1.04</v>
       </c>
-      <c r="AB22" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AC22" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.01</v>
+        <v>2.73</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.09</v>
+        <v>2.27</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AG22" t="n">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AI22" t="n">
-        <v>6.85</v>
+        <v>7.8</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AM22" t="n">
         <v>1.25</v>
@@ -4819,34 +4819,34 @@
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.07</v>
+        <v>2.17</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AU22" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AZ22" t="n">
         <v>4</v>
@@ -4855,19 +4855,19 @@
         <v>1.32</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="R27" t="n">
-        <v>6.25</v>
+        <v>4.64</v>
       </c>
       <c r="S27" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="T27" t="n">
-        <v>2.35</v>
+        <v>3.08</v>
       </c>
       <c r="U27" t="n">
-        <v>7</v>
+        <v>4.95</v>
       </c>
       <c r="V27" t="n">
-        <v>1.34</v>
+        <v>1.11</v>
       </c>
       <c r="W27" t="n">
-        <v>2.9</v>
+        <v>6</v>
       </c>
       <c r="X27" t="n">
-        <v>2.63</v>
+        <v>1.81</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.48</v>
+        <v>2.07</v>
       </c>
       <c r="Z27" t="n">
-        <v>6.75</v>
+        <v>3.65</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="AB27" t="n">
         <v>1.01</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.22</v>
+        <v>1.03</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.72</v>
+        <v>8.5</v>
       </c>
       <c r="AE27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AZ27" t="n">
         <v>1.8</v>
       </c>
-      <c r="AF27" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>1.33</v>
-      </c>
       <c r="BA27" t="n">
-        <v>3.6</v>
+        <v>2.63</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.07</v>
+        <v>1.51</v>
       </c>
       <c r="BD27" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.78</v>
+        <v>2.54</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.2</v>
+        <v>1.51</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="R28" t="n">
-        <v>4.64</v>
+        <v>6.25</v>
       </c>
       <c r="S28" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="T28" t="n">
-        <v>3.08</v>
+        <v>2.35</v>
       </c>
       <c r="U28" t="n">
-        <v>4.95</v>
+        <v>7</v>
       </c>
       <c r="V28" t="n">
-        <v>1.11</v>
+        <v>1.34</v>
       </c>
       <c r="W28" t="n">
-        <v>6</v>
+        <v>2.9</v>
       </c>
       <c r="X28" t="n">
-        <v>1.81</v>
+        <v>2.63</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.07</v>
+        <v>1.48</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.65</v>
+        <v>6.75</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="AB28" t="n">
         <v>1.01</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="AD28" t="n">
-        <v>8.5</v>
+        <v>3.72</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.28</v>
+        <v>1.8</v>
       </c>
       <c r="AF28" t="n">
-        <v>3.75</v>
+        <v>2.07</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.77</v>
+        <v>2.99</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.15</v>
+        <v>1.33</v>
       </c>
       <c r="AI28" t="n">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="AJ28" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AX28" t="n">
         <v>1.47</v>
       </c>
-      <c r="AK28" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AQ28" t="n">
+      <c r="AY28" t="n">
         <v>1.31</v>
       </c>
-      <c r="AR28" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AZ28" t="n">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.63</v>
+        <v>3.6</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.51</v>
+        <v>2.07</v>
       </c>
       <c r="BD28" t="n">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="BE28" t="n">
-        <v>2.54</v>
+        <v>1.78</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.51</v>
+        <v>1.2</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,79 +7302,79 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
@@ -7416,19 +7416,19 @@
         <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7499,79 +7499,79 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB36" t="n">
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
@@ -7613,19 +7613,19 @@
         <v>0</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC36" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="BE36" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="R6" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="S6" t="n">
         <v>2.23</v>
@@ -1610,7 +1610,7 @@
         <v>1.28</v>
       </c>
       <c r="W6" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="X6" t="n">
         <v>2.31</v>
@@ -1643,7 +1643,7 @@
         <v>2.46</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AI6" t="n">
         <v>4.25</v>
@@ -1667,55 +1667,55 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="BD6" t="n">
         <v>4.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,76 +1786,76 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="Q7" t="n">
         <v>3.4</v>
       </c>
       <c r="R7" t="n">
-        <v>3.66</v>
+        <v>3.63</v>
       </c>
       <c r="S7" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="T7" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="U7" t="n">
-        <v>4.32</v>
+        <v>4</v>
       </c>
       <c r="V7" t="n">
         <v>1.33</v>
       </c>
       <c r="W7" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="X7" t="n">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="Z7" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AB7" t="n">
         <v>1</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.68</v>
+        <v>3.34</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.81</v>
+        <v>3.05</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AI7" t="n">
-        <v>5.25</v>
+        <v>5.8</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AN7" t="n">
         <v>1.77</v>
@@ -1864,55 +1864,55 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.51</v>
+        <v>1.75</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>4.88</v>
+        <v>4.62</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.2</v>
+        <v>3.07</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.34</v>
+        <v>2.21</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="BA7" t="n">
-        <v>3.95</v>
+        <v>4.34</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.05</v>
+        <v>3.82</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="X8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AT8" t="n">
         <v>3.4</v>
       </c>
-      <c r="R8" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="T8" t="n">
+      <c r="AU8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AV8" t="n">
         <v>2.1</v>
       </c>
-      <c r="U8" t="n">
-        <v>4</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>3.07</v>
-      </c>
       <c r="AW8" t="n">
-        <v>2.21</v>
+        <v>1.68</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.76</v>
+        <v>1.43</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.49</v>
+        <v>1.26</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.36</v>
+        <v>1.92</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.34</v>
+        <v>2.12</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.05</v>
+        <v>2.39</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.82</v>
+        <v>3.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.6</v>
+        <v>1.82</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="R11" t="n">
-        <v>2.5</v>
+        <v>3.66</v>
       </c>
       <c r="S11" t="n">
-        <v>3.25</v>
+        <v>2.42</v>
       </c>
       <c r="T11" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="U11" t="n">
-        <v>3.1</v>
+        <v>4.32</v>
       </c>
       <c r="V11" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="W11" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AT11" t="n">
         <v>2.39</v>
       </c>
-      <c r="X11" t="n">
+      <c r="AU11" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="AV11" t="n">
         <v>3.2</v>
       </c>
-      <c r="Y11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AH11" t="n">
+      <c r="AW11" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BF11" t="n">
         <v>1.2</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>6.14</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>1.09</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.8</v>
+        <v>2.53</v>
       </c>
       <c r="T12" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="X12" t="n">
         <v>2.5</v>
       </c>
-      <c r="U12" t="n">
-        <v>7.18</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W12" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.36</v>
-      </c>
       <c r="Y12" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="Z12" t="n">
-        <v>5</v>
+        <v>6.85</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AD12" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.46</v>
+        <v>3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="AI12" t="n">
-        <v>5.1</v>
+        <v>5.95</v>
       </c>
       <c r="AJ12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BF12" t="n">
         <v>1.14</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>1.22</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,67 +2968,67 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.6</v>
+        <v>1.37</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="R13" t="n">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="S13" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="U13" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z13" t="n">
         <v>5</v>
       </c>
-      <c r="V13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>6.5</v>
-      </c>
       <c r="AA13" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.34</v>
+        <v>4.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.97</v>
+        <v>2.46</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AI13" t="n">
         <v>5.1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AK13" t="n">
         <v>1.8</v>
@@ -3037,64 +3037,64 @@
         <v>1.85</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AN13" t="n">
-        <v>2.12</v>
+        <v>2.78</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.65</v>
+        <v>2.36</v>
       </c>
       <c r="AU13" t="n">
-        <v>4.03</v>
+        <v>4.73</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.76</v>
+        <v>3.13</v>
       </c>
       <c r="AW13" t="n">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.67</v>
+        <v>4.55</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.78</v>
+        <v>4.65</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.75</v>
+        <v>1.46</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
       <c r="R14" t="n">
-        <v>4</v>
+        <v>6.3</v>
       </c>
       <c r="S14" t="n">
-        <v>2.25</v>
+        <v>1.88</v>
       </c>
       <c r="T14" t="n">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="U14" t="n">
-        <v>4.37</v>
+        <v>7.24</v>
       </c>
       <c r="V14" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W14" t="n">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="X14" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="Z14" t="n">
         <v>5.7</v>
       </c>
       <c r="AA14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AM14" t="n">
         <v>1.08</v>
       </c>
-      <c r="AB14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="AJ14" t="n">
+      <c r="AN14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
         <v>1.13</v>
       </c>
-      <c r="AK14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL14" t="n">
+      <c r="AQ14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AW14" t="n">
         <v>2.2</v>
       </c>
-      <c r="AM14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>2.45</v>
-      </c>
       <c r="AX14" t="n">
-        <v>1.94</v>
+        <v>1.76</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BD14" t="n">
         <v>3.9</v>
       </c>
-      <c r="BB14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BE14" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.53</v>
+        <v>2.25</v>
       </c>
       <c r="T15" t="n">
-        <v>2.09</v>
+        <v>2.35</v>
       </c>
       <c r="U15" t="n">
-        <v>4.23</v>
+        <v>4.37</v>
       </c>
       <c r="V15" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="W15" t="n">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="X15" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AZ15" t="n">
         <v>1.42</v>
       </c>
-      <c r="Z15" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM15" t="n">
+      <c r="BA15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BF15" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>1.14</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.88</v>
+        <v>3.6</v>
       </c>
       <c r="R16" t="n">
-        <v>6.3</v>
+        <v>4.6</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AE16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK16" t="n">
         <v>1.8</v>
       </c>
-      <c r="AF16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>5.67</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3756,10 +3756,10 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R17" t="n">
         <v>3.5</v>
@@ -3786,7 +3786,7 @@
         <v>1.53</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AA17" t="n">
         <v>1.09</v>
@@ -3825,49 +3825,49 @@
         <v>2.15</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="BB17" t="n">
         <v>1.16</v>
@@ -3882,7 +3882,7 @@
         <v>1.87</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.82</v>
+        <v>6</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.6</v>
+        <v>5.25</v>
       </c>
       <c r="R18" t="n">
-        <v>3.8</v>
+        <v>1.41</v>
       </c>
       <c r="S18" t="n">
-        <v>2.24</v>
+        <v>5.35</v>
       </c>
       <c r="T18" t="n">
-        <v>2.27</v>
+        <v>2.88</v>
       </c>
       <c r="U18" t="n">
-        <v>4.6</v>
+        <v>1.75</v>
       </c>
       <c r="V18" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="W18" t="n">
-        <v>3.15</v>
+        <v>4.75</v>
       </c>
       <c r="X18" t="n">
-        <v>2.44</v>
+        <v>1.8</v>
       </c>
       <c r="Y18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BF18" t="n">
         <v>1.49</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>1.23</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>6</v>
+        <v>1.82</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.25</v>
+        <v>3.6</v>
       </c>
       <c r="R19" t="n">
-        <v>1.41</v>
+        <v>3.8</v>
       </c>
       <c r="S19" t="n">
-        <v>5.35</v>
+        <v>2.24</v>
       </c>
       <c r="T19" t="n">
-        <v>2.88</v>
+        <v>2.27</v>
       </c>
       <c r="U19" t="n">
-        <v>1.75</v>
+        <v>4.6</v>
       </c>
       <c r="V19" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="W19" t="n">
-        <v>4.75</v>
+        <v>3.15</v>
       </c>
       <c r="X19" t="n">
-        <v>1.8</v>
+        <v>2.44</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.9</v>
+        <v>1.49</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AD19" t="n">
-        <v>6.85</v>
+        <v>3.96</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.24</v>
+        <v>1.67</v>
       </c>
       <c r="AF19" t="n">
-        <v>3.65</v>
+        <v>2.18</v>
       </c>
       <c r="AG19" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AZ19" t="n">
         <v>1.76</v>
       </c>
-      <c r="AH19" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.46</v>
+        <v>1.88</v>
       </c>
       <c r="BD19" t="n">
-        <v>7.8</v>
+        <v>4.33</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.53</v>
+        <v>1.86</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.49</v>
+        <v>1.23</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,139 +4347,139 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>7.75</v>
+        <v>3.74</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="R20" t="n">
-        <v>1.49</v>
+        <v>2.05</v>
       </c>
       <c r="S20" t="n">
-        <v>8.9</v>
+        <v>4.33</v>
       </c>
       <c r="T20" t="n">
-        <v>1.98</v>
+        <v>1.81</v>
       </c>
       <c r="U20" t="n">
-        <v>2.2</v>
+        <v>2.79</v>
       </c>
       <c r="V20" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="X20" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z20" t="n">
-        <v>8.9</v>
+        <v>8.1</v>
       </c>
       <c r="AA20" t="n">
         <v>1.03</v>
       </c>
       <c r="AB20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.1</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AI20" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL20" t="n">
         <v>1.59</v>
       </c>
-      <c r="AD20" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AL20" t="n">
+      <c r="AM20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BB20" t="n">
         <v>1.35</v>
       </c>
-      <c r="AM20" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.4</v>
-      </c>
       <c r="BC20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BD20" t="n">
         <v>2.82</v>
       </c>
-      <c r="BD20" t="n">
-        <v>2.62</v>
-      </c>
       <c r="BE20" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="BF20" t="n">
         <v>1.08</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="BH20" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="BI20" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,139 +4544,139 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.74</v>
+        <v>7.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>2.05</v>
+        <v>1.49</v>
       </c>
       <c r="S21" t="n">
-        <v>4.33</v>
+        <v>8.9</v>
       </c>
       <c r="T21" t="n">
-        <v>1.81</v>
+        <v>1.98</v>
       </c>
       <c r="U21" t="n">
-        <v>2.79</v>
+        <v>2.2</v>
       </c>
       <c r="V21" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="W21" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="X21" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.1</v>
+        <v>8.9</v>
       </c>
       <c r="AA21" t="n">
         <v>1.03</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AG21" t="n">
         <v>5.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AI21" t="n">
-        <v>8.9</v>
+        <v>10</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.84</v>
+        <v>2.38</v>
       </c>
       <c r="AS21" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="AT21" t="n">
-        <v>4.64</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2.43</v>
+        <v>3.7</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.81</v>
+        <v>1.3</v>
       </c>
       <c r="BB21" t="n">
         <v>1.4</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BF21" t="n">
         <v>1.08</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH21" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46127.60416666666</v>
@@ -4938,7 +4938,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="Q23" t="n">
         <v>9.76</v>
@@ -4959,16 +4959,16 @@
         <v>1.07</v>
       </c>
       <c r="W23" t="n">
-        <v>5.95</v>
+        <v>4.8</v>
       </c>
       <c r="X23" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.92</v>
+        <v>2.03</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AA23" t="n">
         <v>1.28</v>
@@ -4977,28 +4977,28 @@
         <v>1</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AD23" t="n">
         <v>8.6</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AF23" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="AI23" t="n">
         <v>2.4</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AK23" t="n">
         <v>1.67</v>
@@ -5016,25 +5016,25 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AS23" t="n">
         <v>2.02</v>
       </c>
       <c r="AT23" t="n">
-        <v>3.14</v>
+        <v>3.07</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.28</v>
+        <v>3.55</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="AW23" t="n">
         <v>1.85</v>
@@ -5043,10 +5043,10 @@
         <v>1.65</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="BA23" t="n">
         <v>8</v>
@@ -5061,7 +5061,7 @@
         <v>7.8</v>
       </c>
       <c r="BE23" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="BF23" t="n">
         <v>1.5</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.9</v>
+        <v>1.33</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.64</v>
+        <v>5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.94</v>
+        <v>7.81</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>1.76</v>
       </c>
       <c r="T24" t="n">
-        <v>2.19</v>
+        <v>2.5</v>
       </c>
       <c r="U24" t="n">
-        <v>2.55</v>
+        <v>5.51</v>
       </c>
       <c r="V24" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="W24" t="n">
-        <v>2.94</v>
+        <v>3.4</v>
       </c>
       <c r="X24" t="n">
-        <v>2.82</v>
+        <v>2.28</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="Z24" t="n">
-        <v>6.35</v>
+        <v>5.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AC24" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BF24" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>1.16</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="R25" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="S25" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="T25" t="n">
-        <v>2.32</v>
+        <v>2.07</v>
       </c>
       <c r="U25" t="n">
-        <v>4.89</v>
+        <v>4.2</v>
       </c>
       <c r="V25" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W25" t="n">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="X25" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="AE25" t="n">
         <v>1.89</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AI25" t="n">
-        <v>6.37</v>
+        <v>6.04</v>
       </c>
       <c r="AJ25" t="n">
         <v>1.08</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5428,7 +5428,7 @@
         <v>2.1</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AW25" t="n">
         <v>1.69</v>
@@ -5446,19 +5446,19 @@
         <v>4.76</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="BE25" t="n">
         <v>1.62</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.33</v>
+        <v>3.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>5</v>
+        <v>3.64</v>
       </c>
       <c r="R26" t="n">
-        <v>7.81</v>
+        <v>1.94</v>
       </c>
       <c r="S26" t="n">
-        <v>1.76</v>
+        <v>4</v>
       </c>
       <c r="T26" t="n">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="U26" t="n">
-        <v>5.51</v>
+        <v>2.55</v>
       </c>
       <c r="V26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC26" t="n">
         <v>1.25</v>
       </c>
-      <c r="W26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AD26" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.61</v>
+        <v>1.89</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.21</v>
+        <v>1.89</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.52</v>
+        <v>3.24</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.52</v>
+        <v>1.32</v>
       </c>
       <c r="AI26" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="AJ26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BF26" t="n">
         <v>1.16</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>1.25</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6523,70 +6523,70 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
@@ -6628,19 +6628,19 @@
         <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,79 +7105,79 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7219,19 +7219,19 @@
         <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>

--- a/jogos_2026-04-15.xlsx
+++ b/jogos_2026-04-15.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI36"/>
+  <dimension ref="A1:BI38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,96 +772,96 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N2" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="R2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W2" t="n">
         <v>2.5</v>
       </c>
-      <c r="S2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2.65</v>
-      </c>
       <c r="X2" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="Y2" t="n">
         <v>1.38</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.1</v>
+        <v>6.25</v>
       </c>
       <c r="AA2" t="n">
         <v>1.08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AG2" t="n">
-        <v>3.24</v>
+        <v>3.75</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AI2" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AK2" t="n">
         <v>1.68</v>
@@ -879,13 +879,13 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.75</v>
+        <v>2.34</v>
       </c>
       <c r="AS2" t="n">
         <v>2.95</v>
@@ -897,7 +897,7 @@
         <v>2.48</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AW2" t="n">
         <v>1.56</v>
@@ -909,25 +909,25 @@
         <v>1.19</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.29</v>
+        <v>2.17</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="BC2" t="n">
         <v>2.1</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.66</v>
+        <v>3.34</v>
       </c>
       <c r="BE2" t="n">
         <v>1.63</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -987,123 +987,123 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.43</v>
+        <v>1.83</v>
       </c>
       <c r="Q3" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="R3" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="S3" t="n">
         <v>2.8</v>
       </c>
-      <c r="R3" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1157,22 +1157,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -1181,93 +1181,93 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N4" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1330,7 +1330,7 @@
         <v>0</v>
       </c>
       <c r="BI4" s="3" t="n">
-        <v>46127.41666666666</v>
+        <v>46127.375</v>
       </c>
     </row>
     <row r="5">
@@ -1363,13 +1363,13 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1378,147 +1378,147 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="N5" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="S5" t="n">
-        <v>3.15</v>
+        <v>2.67</v>
       </c>
       <c r="T5" t="n">
-        <v>1.99</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>3.36</v>
+        <v>3.78</v>
       </c>
       <c r="V5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Y5" t="n">
         <v>1.43</v>
       </c>
-      <c r="W5" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="X5" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.33</v>
-      </c>
       <c r="Z5" t="n">
-        <v>7.5</v>
+        <v>5.85</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.78</v>
+        <v>3.58</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.64</v>
+        <v>2.07</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AI5" t="n">
-        <v>7.2</v>
+        <v>4.9</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.86</v>
+        <v>2.15</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.29</v>
+        <v>1.95</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.52</v>
+        <v>1.78</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1560,114 +1560,114 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N6" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="R6" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="S6" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="T6" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="U6" t="n">
-        <v>4.78</v>
+        <v>4.92</v>
       </c>
       <c r="V6" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W6" t="n">
-        <v>3.18</v>
+        <v>2.96</v>
       </c>
       <c r="X6" t="n">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AB6" t="n">
         <v>1.04</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AD6" t="n">
-        <v>4.5</v>
+        <v>3.96</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.46</v>
+        <v>2.77</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="AI6" t="n">
-        <v>4.25</v>
+        <v>4.9</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AQ6" t="n">
         <v>1.8</v>
@@ -1682,7 +1682,7 @@
         <v>4.54</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="AV6" t="n">
         <v>1.91</v>
@@ -1700,22 +1700,22 @@
         <v>1.6</v>
       </c>
       <c r="BA6" t="n">
-        <v>3.18</v>
+        <v>2.68</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1775,39 +1775,39 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R7" t="n">
-        <v>3.63</v>
+        <v>3.45</v>
       </c>
       <c r="S7" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="T7" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="U7" t="n">
         <v>4</v>
       </c>
       <c r="V7" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W7" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="X7" t="n">
         <v>2.67</v>
@@ -1816,7 +1816,7 @@
         <v>1.38</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.6</v>
+        <v>6.65</v>
       </c>
       <c r="AA7" t="n">
         <v>1.05</v>
@@ -1828,7 +1828,7 @@
         <v>1.24</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="AE7" t="n">
         <v>1.9</v>
@@ -1837,22 +1837,22 @@
         <v>1.9</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AI7" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AJ7" t="n">
         <v>1.07</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AM7" t="n">
         <v>1.23</v>
@@ -1870,10 +1870,10 @@
         <v>1.29</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AT7" t="n">
         <v>2.4</v>
@@ -1885,10 +1885,10 @@
         <v>3.07</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AY7" t="n">
         <v>1.49</v>
@@ -1906,13 +1906,13 @@
         <v>2.05</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="BE7" t="n">
         <v>1.67</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,19 +1945,19 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1966,150 +1966,150 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N8" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.6</v>
+        <v>3.77</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="R8" t="n">
-        <v>2.5</v>
+        <v>1.71</v>
       </c>
       <c r="S8" t="n">
-        <v>3.25</v>
+        <v>4.43</v>
       </c>
       <c r="T8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W8" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AW8" t="n">
         <v>1.95</v>
       </c>
-      <c r="U8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="X8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>6.14</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT8" t="n">
+      <c r="AX8" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>3.4</v>
       </c>
-      <c r="AU8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>1.92</v>
-      </c>
       <c r="BA8" t="n">
-        <v>2.12</v>
+        <v>1.53</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.39</v>
+        <v>1.84</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.2</v>
+        <v>4.45</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2142,16 +2142,16 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -2163,150 +2163,150 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N9" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T9" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.01</v>
-      </c>
       <c r="U9" t="n">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="V9" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="W9" t="n">
-        <v>2.67</v>
+        <v>3.07</v>
       </c>
       <c r="X9" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.95</v>
+        <v>5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AB9" t="n">
         <v>1.01</v>
       </c>
       <c r="AC9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>1.26</v>
       </c>
-      <c r="AD9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF9" t="n">
+      <c r="AR9" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AS9" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>1.95</v>
       </c>
       <c r="AT9" t="n">
         <v>2.42</v>
       </c>
       <c r="AU9" t="n">
-        <v>4.54</v>
+        <v>4.88</v>
       </c>
       <c r="AV9" t="n">
-        <v>3.03</v>
+        <v>3.2</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AZ9" t="n">
-        <v>2.13</v>
+        <v>1.41</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.1</v>
+        <v>3.95</v>
       </c>
       <c r="BB9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BF9" t="n">
         <v>1.25</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>1.14</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,25 +2339,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -2366,144 +2366,144 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N10" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3.7</v>
+        <v>4.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.54</v>
+        <v>2.83</v>
       </c>
       <c r="R10" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="S10" t="n">
-        <v>3.95</v>
+        <v>6.29</v>
       </c>
       <c r="T10" t="n">
-        <v>2.11</v>
+        <v>1.77</v>
       </c>
       <c r="U10" t="n">
-        <v>2.4</v>
+        <v>2.59</v>
       </c>
       <c r="V10" t="n">
-        <v>1.35</v>
+        <v>1.62</v>
       </c>
       <c r="W10" t="n">
-        <v>2.79</v>
+        <v>2.13</v>
       </c>
       <c r="X10" t="n">
-        <v>2.72</v>
+        <v>3.92</v>
       </c>
       <c r="Y10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
         <v>1.38</v>
       </c>
-      <c r="Z10" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AJ10" t="n">
+      <c r="BC10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BF10" t="n">
         <v>1.07</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.67</v